--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1520,10 +1520,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C22" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -1571,10 +1569,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C23" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -1608,6 +1604,596 @@
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>1.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2594</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>10016</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>9999</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>263.635</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>268.145</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>105454</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>107258</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>1804</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>300394</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>369.015</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>351.03</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>73803</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>70206</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>-3597</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>-4.87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>300750</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>437.46</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>440.735</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>87492</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>88147</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>655</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>688062</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>19340</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>19070</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>-270</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>-1.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>300750</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>436.75</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>442.85</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>43675</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>44285</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>610</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>300502</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>602.91</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>610.5</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>60291</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>61050</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>759</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>300308</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>895.3099999999999</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>901.42</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>89531</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>90142</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>611</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>278.6778</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>281.4227</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>250810</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>253280.45</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>2470.45</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>688503</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>17942</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>18468</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>526</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>300450</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>11188</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>11446</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>552.4299999999999</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>549.795</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>110486</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>109959</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>-527</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2157,10 +2157,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C35" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -2194,6 +2192,204 @@
       <c r="M35" s="2" t="inlineStr">
         <is>
           <t>-0.48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>300750</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>435.38</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>43800</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>43538</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>-262</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>298.54</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>300.165</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>179124</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>180099</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>975</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>300394</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>323.31</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>325.035</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>32331</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>32503.5</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>103.18</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>20512</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>20636</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>0.60%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2353,10 +2353,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C39" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -2390,6 +2388,261 @@
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>0.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>103.19</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>20502</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>20638</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>311.01</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>31101</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>31337</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>34745.62</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>35009.8</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>264.18</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>87.0729</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>87.4757</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>60951</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>61233</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>427.35</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>430.57</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>42735</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>43057</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>0.75%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2402,10 +2402,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C40" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
@@ -2453,10 +2451,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C41" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
@@ -2504,10 +2500,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C42" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
@@ -2555,10 +2549,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C43" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
@@ -2606,10 +2598,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C44" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
@@ -2643,6 +2633,159 @@
       <c r="M44" s="2" t="inlineStr">
         <is>
           <t>0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>429.89</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>434.06</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>42989</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>43406</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>19516</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>19976</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>278.54</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>278.5295</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>55708</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>55705.9</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2647,10 +2647,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C45" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
@@ -2698,10 +2696,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C46" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
@@ -2749,10 +2745,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C47" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
@@ -2786,6 +2780,57 @@
       <c r="M47" s="2" t="inlineStr">
         <is>
           <t>-0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>厦钨新能源</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>16580</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>16716</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>0.82%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2791,46 +2791,293 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>688503</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>102.783</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>13567.35</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>13728</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>300054</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>30905</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>31190</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2222</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>17484</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>17600</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>688778</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C51" s="2" t="n">
+        <v>688778</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>厦钨新能源</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="H48" s="2" t="n">
+      <c r="E51" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H51" s="2" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>83.58</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>16580</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K51" s="2" t="n">
         <v>16716</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="L51" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>13610</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>13890</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>301183</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东田微</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>180.24</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>17700</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>18024</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>1.83%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2990,10 +2990,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C52" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
@@ -3041,10 +3039,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>301183</t>
-        </is>
+      <c r="C53" s="2" t="n">
+        <v>301183</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
@@ -3078,6 +3074,204 @@
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>1.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>300394</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>32376</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>32990</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>614</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>300450</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>11122</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>11336</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>69602</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>69942</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>48.735</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>9747</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>9882</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>1.39%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3235,10 +3235,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C57" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
@@ -3272,6 +3270,204 @@
       <c r="M57" s="2" t="inlineStr">
         <is>
           <t>1.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>300750</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>448.17</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>450.45</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>44817</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>45045</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2594</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>10030</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>10046</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>336.7967</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>339.57</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>202078</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>203742</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>1664</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>127.26</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>12548</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>12726</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>1.42%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="0000B050"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B050"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -460,6 +460,10 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,10 +524,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>毛盈亏</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>佣金</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>印花税</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>交易成本</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>盈亏金额</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>盈亏比例</t>
         </is>
@@ -570,9 +594,21 @@
         <v>71598</v>
       </c>
       <c r="L2" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P2" s="4" t="n">
         <v>647</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>0.91%</t>
         </is>
@@ -619,9 +655,21 @@
         <v>54746</v>
       </c>
       <c r="L3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>1104</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>2.06%</t>
         </is>
@@ -668,9 +716,21 @@
         <v>47076</v>
       </c>
       <c r="L4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>542</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1.16%</t>
         </is>
@@ -717,9 +777,21 @@
         <v>18098</v>
       </c>
       <c r="L5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P5" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0.67%</t>
         </is>
@@ -766,9 +838,21 @@
         <v>69998</v>
       </c>
       <c r="L6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P6" s="4" t="n">
         <v>605.33</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0.87%</t>
         </is>
@@ -815,9 +899,21 @@
         <v>7223</v>
       </c>
       <c r="L7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P7" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1.89%</t>
         </is>
@@ -864,9 +960,21 @@
         <v>19235</v>
       </c>
       <c r="L8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P8" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0.88%</t>
         </is>
@@ -913,9 +1021,21 @@
         <v>30795.52</v>
       </c>
       <c r="L9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P9" s="4" t="n">
         <v>179.2</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0.59%</t>
         </is>
@@ -962,9 +1082,21 @@
         <v>44756</v>
       </c>
       <c r="L10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P10" s="4" t="n">
         <v>352.5</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0.79%</t>
         </is>
@@ -1011,9 +1143,21 @@
         <v>8985</v>
       </c>
       <c r="L11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P11" s="4" t="n">
         <v>202</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>2.30%</t>
         </is>
@@ -1060,9 +1204,21 @@
         <v>11794</v>
       </c>
       <c r="L12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P12" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1.87%</t>
         </is>
@@ -1109,9 +1265,21 @@
         <v>37697</v>
       </c>
       <c r="L13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P13" s="4" t="n">
         <v>313</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0.84%</t>
         </is>
@@ -1158,9 +1326,21 @@
         <v>53418</v>
       </c>
       <c r="L14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P14" s="4" t="n">
         <v>582</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1.10%</t>
         </is>
@@ -1206,10 +1386,22 @@
       <c r="K15" s="2" t="n">
         <v>52356</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P15" s="3" t="n">
         <v>-572.08</v>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>-1.08%</t>
         </is>
@@ -1256,9 +1448,21 @@
         <v>143601</v>
       </c>
       <c r="L16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P16" s="4" t="n">
         <v>1393</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
@@ -1305,9 +1509,21 @@
         <v>50510</v>
       </c>
       <c r="L17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P17" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0.66%</t>
         </is>
@@ -1354,9 +1570,21 @@
         <v>19520</v>
       </c>
       <c r="L18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P18" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
@@ -1403,9 +1631,21 @@
         <v>26280</v>
       </c>
       <c r="L19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P19" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1.55%</t>
         </is>
@@ -1452,9 +1692,21 @@
         <v>10149</v>
       </c>
       <c r="L20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P20" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0.40%</t>
         </is>
@@ -1501,9 +1753,21 @@
         <v>19866</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P21" s="4" t="n">
         <v>614</v>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>3.19%</t>
         </is>
@@ -1550,9 +1814,21 @@
         <v>121049</v>
       </c>
       <c r="L22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P22" s="4" t="n">
         <v>4182</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>3.58%</t>
         </is>
@@ -1599,9 +1875,21 @@
         <v>67176</v>
       </c>
       <c r="L23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P23" s="4" t="n">
         <v>922</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1.39%</t>
         </is>
@@ -1647,10 +1935,22 @@
       <c r="K24" s="2" t="n">
         <v>9999</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>-17</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>-0.17%</t>
         </is>
@@ -1697,9 +1997,21 @@
         <v>107258</v>
       </c>
       <c r="L25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P25" s="4" t="n">
         <v>1804</v>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1.71%</t>
         </is>
@@ -1745,10 +2057,22 @@
       <c r="K26" s="2" t="n">
         <v>70206</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>-3597</v>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>-4.87%</t>
         </is>
@@ -1795,9 +2119,21 @@
         <v>88147</v>
       </c>
       <c r="L27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P27" s="4" t="n">
         <v>655</v>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
@@ -1843,10 +2179,22 @@
       <c r="K28" s="2" t="n">
         <v>19070</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>-270</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>-1.40%</t>
         </is>
@@ -1893,9 +2241,21 @@
         <v>44285</v>
       </c>
       <c r="L29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P29" s="4" t="n">
         <v>610</v>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>1.40%</t>
         </is>
@@ -1942,9 +2302,21 @@
         <v>61050</v>
       </c>
       <c r="L30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P30" s="4" t="n">
         <v>759</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1.26%</t>
         </is>
@@ -1991,9 +2363,21 @@
         <v>90142</v>
       </c>
       <c r="L31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P31" s="4" t="n">
         <v>611</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
@@ -2040,9 +2424,21 @@
         <v>253280.45</v>
       </c>
       <c r="L32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P32" s="4" t="n">
         <v>2470.45</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
@@ -2089,9 +2485,21 @@
         <v>18468</v>
       </c>
       <c r="L33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P33" s="4" t="n">
         <v>526</v>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>2.93%</t>
         </is>
@@ -2138,9 +2546,21 @@
         <v>11446</v>
       </c>
       <c r="L34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P34" s="4" t="n">
         <v>258</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>2.31%</t>
         </is>
@@ -2186,10 +2606,22 @@
       <c r="K35" s="2" t="n">
         <v>109959</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>-527</v>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>-0.48%</t>
         </is>
@@ -2235,10 +2667,22 @@
       <c r="K36" s="2" t="n">
         <v>43538</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>-262</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>-0.60%</t>
         </is>
@@ -2285,9 +2729,21 @@
         <v>180099</v>
       </c>
       <c r="L37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P37" s="4" t="n">
         <v>975</v>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
@@ -2334,9 +2790,21 @@
         <v>32503.5</v>
       </c>
       <c r="L38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P38" s="4" t="n">
         <v>172.5</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>0.53%</t>
         </is>
@@ -2383,9 +2851,21 @@
         <v>20636</v>
       </c>
       <c r="L39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P39" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>0.60%</t>
         </is>
@@ -2432,9 +2912,21 @@
         <v>20638</v>
       </c>
       <c r="L40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P40" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>0.66%</t>
         </is>
@@ -2481,9 +2973,21 @@
         <v>31337</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P41" s="4" t="n">
         <v>236</v>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>0.76%</t>
         </is>
@@ -2530,9 +3034,21 @@
         <v>35009.8</v>
       </c>
       <c r="L42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P42" s="4" t="n">
         <v>264.18</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>0.76%</t>
         </is>
@@ -2579,9 +3095,21 @@
         <v>61233</v>
       </c>
       <c r="L43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P43" s="4" t="n">
         <v>282</v>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
@@ -2628,9 +3156,21 @@
         <v>43057</v>
       </c>
       <c r="L44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P44" s="4" t="n">
         <v>322</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
@@ -2677,9 +3217,21 @@
         <v>43406</v>
       </c>
       <c r="L45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P45" s="4" t="n">
         <v>417</v>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
@@ -2726,9 +3278,21 @@
         <v>19976</v>
       </c>
       <c r="L46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P46" s="4" t="n">
         <v>460</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>2.36%</t>
         </is>
@@ -2774,10 +3338,22 @@
       <c r="K47" s="2" t="n">
         <v>55705.9</v>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="L47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P47" s="3" t="n">
         <v>-2.1</v>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>-0.00%</t>
         </is>
@@ -2824,9 +3400,21 @@
         <v>13728</v>
       </c>
       <c r="L48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P48" s="4" t="n">
         <v>160.65</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>1.18%</t>
         </is>
@@ -2873,9 +3461,21 @@
         <v>31190</v>
       </c>
       <c r="L49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P49" s="4" t="n">
         <v>285</v>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
@@ -2922,9 +3522,21 @@
         <v>17600</v>
       </c>
       <c r="L50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P50" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>0.66%</t>
         </is>
@@ -2971,9 +3583,21 @@
         <v>16716</v>
       </c>
       <c r="L51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P51" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>0.82%</t>
         </is>
@@ -3020,9 +3644,21 @@
         <v>13890</v>
       </c>
       <c r="L52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P52" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>2.06%</t>
         </is>
@@ -3069,9 +3705,21 @@
         <v>18024</v>
       </c>
       <c r="L53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P53" s="4" t="n">
         <v>324</v>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>1.83%</t>
         </is>
@@ -3118,9 +3766,21 @@
         <v>32990</v>
       </c>
       <c r="L54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P54" s="4" t="n">
         <v>614</v>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>1.90%</t>
         </is>
@@ -3167,9 +3827,21 @@
         <v>11336</v>
       </c>
       <c r="L55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P55" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>1.92%</t>
         </is>
@@ -3216,9 +3888,21 @@
         <v>69942</v>
       </c>
       <c r="L56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P56" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>0.49%</t>
         </is>
@@ -3265,9 +3949,21 @@
         <v>9882</v>
       </c>
       <c r="L57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P57" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>1.39%</t>
         </is>
@@ -3285,11 +3981,11 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>300750</v>
+        <v>2594</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
@@ -3302,23 +3998,35 @@
         <v>100</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>448.17</v>
+        <v>100.3</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>450.45</v>
+        <v>100.46</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>44817</v>
+        <v>10030</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>45045</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>0.51%</t>
+        <v>10046</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
@@ -3334,11 +4042,11 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>2594</v>
+        <v>300750</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
@@ -3351,23 +4059,35 @@
         <v>100</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>100.3</v>
+        <v>448.17</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>100.46</v>
+        <v>450.45</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10030</v>
+        <v>44817</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>10046</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>0.16%</t>
+        <v>45045</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>195.48</v>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -3411,12 +4131,24 @@
       <c r="K60" s="2" t="n">
         <v>203742</v>
       </c>
-      <c r="L60" s="3" t="n">
+      <c r="L60" s="4" t="n">
         <v>1664</v>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>0.82%</t>
+      <c r="M60" s="2" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>101.87</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>142.45</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>1521.55</v>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -3462,12 +4194,24 @@
       <c r="K61" s="2" t="n">
         <v>12726</v>
       </c>
-      <c r="L61" s="3" t="n">
+      <c r="L61" s="4" t="n">
         <v>178</v>
       </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>1.42%</t>
+      <c r="M61" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>161.64</v>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>1.29%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -593,24 +593,24 @@
       <c r="K2" s="2" t="n">
         <v>71598</v>
       </c>
-      <c r="L2" s="3" t="n">
-        <v/>
+      <c r="L2" s="4" t="n">
+        <v>647</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v/>
+        <v>14.25</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v/>
+        <v>35.8</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v/>
+        <v>50.05</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>647</v>
+        <v>596.95</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -654,24 +654,24 @@
       <c r="K3" s="2" t="n">
         <v>54746</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v/>
+      <c r="L3" s="4" t="n">
+        <v>1104</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v/>
+        <v>10.84</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v/>
+        <v>27.37</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v/>
+        <v>38.21</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>1104</v>
+        <v>1065.79</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -715,24 +715,24 @@
       <c r="K4" s="2" t="n">
         <v>47076</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v/>
+      <c r="L4" s="4" t="n">
+        <v>542</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v/>
+        <v>23.54</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v/>
+        <v>33.54</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>542</v>
+        <v>508.46</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       <c r="K5" s="2" t="n">
         <v>18098</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v/>
+      <c r="L5" s="4" t="n">
+        <v>120</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v/>
+        <v>9.050000000000001</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v/>
+        <v>19.05</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>120</v>
+        <v>100.95</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -837,24 +837,24 @@
       <c r="K6" s="2" t="n">
         <v>69998</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v/>
+      <c r="L6" s="4" t="n">
+        <v>605.33</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v/>
+        <v>13.94</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v/>
+        <v>35</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v/>
+        <v>48.94</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>605.33</v>
+        <v>556.39</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -898,24 +898,24 @@
       <c r="K7" s="2" t="n">
         <v>7223</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v/>
+      <c r="L7" s="4" t="n">
+        <v>134</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v/>
+        <v>3.61</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v/>
+        <v>13.61</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>134</v>
+        <v>120.39</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -959,24 +959,24 @@
       <c r="K8" s="2" t="n">
         <v>19235</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v/>
+      <c r="L8" s="4" t="n">
+        <v>167</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v/>
+        <v>9.619999999999999</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v/>
+        <v>19.62</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>167</v>
+        <v>147.38</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1020,24 +1020,24 @@
       <c r="K9" s="2" t="n">
         <v>30795.52</v>
       </c>
-      <c r="L9" s="3" t="n">
-        <v/>
+      <c r="L9" s="4" t="n">
+        <v>179.2</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v/>
+        <v>15.4</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v/>
+        <v>25.4</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>179.2</v>
+        <v>153.8</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1081,24 +1081,24 @@
       <c r="K10" s="2" t="n">
         <v>44756</v>
       </c>
-      <c r="L10" s="3" t="n">
-        <v/>
+      <c r="L10" s="4" t="n">
+        <v>352.5</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v/>
+        <v>22.38</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v/>
+        <v>32.38</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>352.5</v>
+        <v>320.12</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1142,24 +1142,24 @@
       <c r="K11" s="2" t="n">
         <v>8985</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v/>
+      <c r="L11" s="4" t="n">
+        <v>202</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v/>
+        <v>4.49</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v/>
+        <v>14.49</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>202</v>
+        <v>187.51</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1203,24 +1203,24 @@
       <c r="K12" s="2" t="n">
         <v>11794</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v/>
+      <c r="L12" s="4" t="n">
+        <v>216</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v/>
+        <v>5.9</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v/>
+        <v>15.9</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>216</v>
+        <v>200.1</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1264,24 +1264,24 @@
       <c r="K13" s="2" t="n">
         <v>37697</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v/>
+      <c r="L13" s="4" t="n">
+        <v>313</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v/>
+        <v>18.85</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v/>
+        <v>28.85</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>313</v>
+        <v>284.15</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1325,24 +1325,24 @@
       <c r="K14" s="2" t="n">
         <v>53418</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v/>
+      <c r="L14" s="4" t="n">
+        <v>582</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v/>
+        <v>10.63</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v/>
+        <v>26.71</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v/>
+        <v>37.34</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>582</v>
+        <v>544.66</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1387,23 +1387,23 @@
         <v>52356</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v/>
+        <v>-572.08</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v/>
+        <v>10.53</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v/>
+        <v>26.18</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v/>
+        <v>36.71</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-572.08</v>
+        <v>-608.79</v>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>-1.15%</t>
         </is>
       </c>
     </row>
@@ -1447,24 +1447,24 @@
       <c r="K16" s="2" t="n">
         <v>143601</v>
       </c>
-      <c r="L16" s="3" t="n">
-        <v/>
+      <c r="L16" s="4" t="n">
+        <v>1393</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v/>
+        <v>28.58</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v/>
+        <v>71.8</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v/>
+        <v>100.38</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1393</v>
+        <v>1292.62</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1508,24 +1508,24 @@
       <c r="K17" s="2" t="n">
         <v>50510</v>
       </c>
-      <c r="L17" s="3" t="n">
-        <v/>
+      <c r="L17" s="4" t="n">
+        <v>330</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v/>
+        <v>10.07</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v/>
+        <v>25.25</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v/>
+        <v>35.32</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>330</v>
+        <v>294.68</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1569,24 +1569,24 @@
       <c r="K18" s="2" t="n">
         <v>19520</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v/>
+      <c r="L18" s="4" t="n">
+        <v>106</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v/>
+        <v>9.76</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v/>
+        <v>19.76</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>106</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1630,24 +1630,24 @@
       <c r="K19" s="2" t="n">
         <v>26280</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v/>
+      <c r="L19" s="4" t="n">
+        <v>400</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v/>
+        <v>13.14</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v/>
+        <v>23.14</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>400</v>
+        <v>376.86</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1691,24 +1691,24 @@
       <c r="K20" s="2" t="n">
         <v>10149</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v/>
+      <c r="L20" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v/>
+        <v>5.07</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v/>
+        <v>15.07</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>40</v>
+        <v>24.93</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1752,24 +1752,24 @@
       <c r="K21" s="2" t="n">
         <v>19866</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v/>
+      <c r="L21" s="4" t="n">
+        <v>614</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v/>
+        <v>9.93</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v/>
+        <v>19.93</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>614</v>
+        <v>594.0700000000001</v>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -1813,24 +1813,24 @@
       <c r="K22" s="2" t="n">
         <v>121049</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v/>
+      <c r="L22" s="4" t="n">
+        <v>4182</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v/>
+        <v>23.79</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v/>
+        <v>60.52</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v/>
+        <v>84.31</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4182</v>
+        <v>4097.69</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
@@ -1874,24 +1874,24 @@
       <c r="K23" s="2" t="n">
         <v>67176</v>
       </c>
-      <c r="L23" s="3" t="n">
-        <v/>
+      <c r="L23" s="4" t="n">
+        <v>922</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v/>
+        <v>13.34</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v/>
+        <v>33.59</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v/>
+        <v>46.93</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>922</v>
+        <v>875.0700000000001</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1936,23 +1936,23 @@
         <v>9999</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v/>
+        <v>-17</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v/>
+        <v>15</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-17</v>
+        <v>-32</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.32%</t>
         </is>
       </c>
     </row>
@@ -1996,24 +1996,24 @@
       <c r="K25" s="2" t="n">
         <v>107258</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v/>
+      <c r="L25" s="4" t="n">
+        <v>1804</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v/>
+        <v>21.27</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v/>
+        <v>53.63</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v/>
+        <v>74.90000000000001</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1804</v>
+        <v>1729.1</v>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -2058,23 +2058,23 @@
         <v>70206</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v/>
+        <v>-3597</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v/>
+        <v>14.4</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v/>
+        <v>35.1</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v/>
+        <v>49.5</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-3597</v>
+        <v>-3646.5</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>-4.94%</t>
         </is>
       </c>
     </row>
@@ -2118,24 +2118,24 @@
       <c r="K27" s="2" t="n">
         <v>88147</v>
       </c>
-      <c r="L27" s="3" t="n">
-        <v/>
+      <c r="L27" s="4" t="n">
+        <v>655</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v/>
+        <v>17.56</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v/>
+        <v>44.07</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v/>
+        <v>61.63</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>655</v>
+        <v>593.37</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -2180,23 +2180,23 @@
         <v>19070</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v/>
+        <v>-270</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v/>
+        <v>9.539999999999999</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v/>
+        <v>19.54</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-270</v>
+        <v>-289.54</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-1.50%</t>
         </is>
       </c>
     </row>
@@ -2240,24 +2240,24 @@
       <c r="K29" s="2" t="n">
         <v>44285</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v/>
+      <c r="L29" s="4" t="n">
+        <v>610</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v/>
+        <v>22.14</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v/>
+        <v>32.14</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>610</v>
+        <v>577.86</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -2301,24 +2301,24 @@
       <c r="K30" s="2" t="n">
         <v>61050</v>
       </c>
-      <c r="L30" s="3" t="n">
-        <v/>
+      <c r="L30" s="4" t="n">
+        <v>759</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v/>
+        <v>12.13</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v/>
+        <v>30.53</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v/>
+        <v>42.66</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>759</v>
+        <v>716.34</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -2362,24 +2362,24 @@
       <c r="K31" s="2" t="n">
         <v>90142</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v/>
+      <c r="L31" s="4" t="n">
+        <v>611</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v/>
+        <v>17.97</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v/>
+        <v>45.07</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v/>
+        <v>63.04</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>611</v>
+        <v>547.96</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -2423,24 +2423,24 @@
       <c r="K32" s="2" t="n">
         <v>253280.45</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v/>
+      <c r="L32" s="4" t="n">
+        <v>2470.45</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v/>
+        <v>50.41</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v/>
+        <v>126.64</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v/>
+        <v>177.05</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>2470.45</v>
+        <v>2293.4</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -2484,24 +2484,24 @@
       <c r="K33" s="2" t="n">
         <v>18468</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v/>
+      <c r="L33" s="4" t="n">
+        <v>526</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v/>
+        <v>9.23</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v/>
+        <v>19.23</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>526</v>
+        <v>506.77</v>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -2545,24 +2545,24 @@
       <c r="K34" s="2" t="n">
         <v>11446</v>
       </c>
-      <c r="L34" s="3" t="n">
-        <v/>
+      <c r="L34" s="4" t="n">
+        <v>258</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v/>
+        <v>5.72</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v/>
+        <v>15.72</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>258</v>
+        <v>242.28</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -2607,23 +2607,23 @@
         <v>109959</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v/>
+        <v>-527</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v/>
+        <v>22.04</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v/>
+        <v>54.98</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v/>
+        <v>77.02</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-527</v>
+        <v>-604.02</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.55%</t>
         </is>
       </c>
     </row>
@@ -2668,23 +2668,23 @@
         <v>43538</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v/>
+        <v>-262</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v/>
+        <v>21.77</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v/>
+        <v>31.77</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-262</v>
+        <v>-293.77</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.67%</t>
         </is>
       </c>
     </row>
@@ -2728,24 +2728,24 @@
       <c r="K37" s="2" t="n">
         <v>180099</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v/>
+      <c r="L37" s="4" t="n">
+        <v>975</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v/>
+        <v>35.92</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v/>
+        <v>90.05</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v/>
+        <v>125.97</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>975</v>
+        <v>849.03</v>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -2789,24 +2789,24 @@
       <c r="K38" s="2" t="n">
         <v>32503.5</v>
       </c>
-      <c r="L38" s="3" t="n">
-        <v/>
+      <c r="L38" s="4" t="n">
+        <v>172.5</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v/>
+        <v>16.25</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v/>
+        <v>26.25</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>172.5</v>
+        <v>146.25</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -2850,24 +2850,24 @@
       <c r="K39" s="2" t="n">
         <v>20636</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v/>
+      <c r="L39" s="4" t="n">
+        <v>124</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v/>
+        <v>10.32</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v/>
+        <v>20.32</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>124</v>
+        <v>103.68</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -2911,24 +2911,24 @@
       <c r="K40" s="2" t="n">
         <v>20638</v>
       </c>
-      <c r="L40" s="3" t="n">
-        <v/>
+      <c r="L40" s="4" t="n">
+        <v>136</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v/>
+        <v>10.32</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v/>
+        <v>20.32</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>136</v>
+        <v>115.68</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -2972,24 +2972,24 @@
       <c r="K41" s="2" t="n">
         <v>31337</v>
       </c>
-      <c r="L41" s="3" t="n">
-        <v/>
+      <c r="L41" s="4" t="n">
+        <v>236</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v/>
+        <v>15.67</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v/>
+        <v>25.67</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>236</v>
+        <v>210.33</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -3033,24 +3033,24 @@
       <c r="K42" s="2" t="n">
         <v>35009.8</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v/>
+      <c r="L42" s="4" t="n">
+        <v>264.18</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v/>
+        <v>17.5</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v/>
+        <v>27.5</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>264.18</v>
+        <v>236.68</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -3094,24 +3094,24 @@
       <c r="K43" s="2" t="n">
         <v>61233</v>
       </c>
-      <c r="L43" s="3" t="n">
-        <v/>
+      <c r="L43" s="4" t="n">
+        <v>282</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v/>
+        <v>12.22</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v/>
+        <v>30.62</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v/>
+        <v>42.84</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>282</v>
+        <v>239.16</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -3155,24 +3155,24 @@
       <c r="K44" s="2" t="n">
         <v>43057</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v/>
+      <c r="L44" s="4" t="n">
+        <v>322</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v/>
+        <v>21.53</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v/>
+        <v>31.53</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>322</v>
+        <v>290.47</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -3216,24 +3216,24 @@
       <c r="K45" s="2" t="n">
         <v>43406</v>
       </c>
-      <c r="L45" s="3" t="n">
-        <v/>
+      <c r="L45" s="4" t="n">
+        <v>417</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v/>
+        <v>21.7</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v/>
+        <v>31.7</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>417</v>
+        <v>385.3</v>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -3277,24 +3277,24 @@
       <c r="K46" s="2" t="n">
         <v>19976</v>
       </c>
-      <c r="L46" s="3" t="n">
-        <v/>
+      <c r="L46" s="4" t="n">
+        <v>460</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v/>
+        <v>9.99</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v/>
+        <v>19.99</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>460</v>
+        <v>440.01</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -3339,23 +3339,23 @@
         <v>55705.9</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v/>
+        <v>-2.1</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v/>
+        <v>11.14</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v/>
+        <v>27.85</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v/>
+        <v>38.99</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>-2.1</v>
+        <v>-41.09</v>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
     </row>
@@ -3399,24 +3399,24 @@
       <c r="K48" s="2" t="n">
         <v>13728</v>
       </c>
-      <c r="L48" s="3" t="n">
-        <v/>
+      <c r="L48" s="4" t="n">
+        <v>160.65</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v/>
+        <v>6.86</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v/>
+        <v>16.86</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>160.65</v>
+        <v>143.79</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -3460,24 +3460,24 @@
       <c r="K49" s="2" t="n">
         <v>31190</v>
       </c>
-      <c r="L49" s="3" t="n">
-        <v/>
+      <c r="L49" s="4" t="n">
+        <v>285</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v/>
+        <v>15.6</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v/>
+        <v>25.6</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>285</v>
+        <v>259.4</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -3521,24 +3521,24 @@
       <c r="K50" s="2" t="n">
         <v>17600</v>
       </c>
-      <c r="L50" s="3" t="n">
-        <v/>
+      <c r="L50" s="4" t="n">
+        <v>116</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v/>
+        <v>8.800000000000001</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v/>
+        <v>18.8</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>116</v>
+        <v>97.2</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -3582,24 +3582,24 @@
       <c r="K51" s="2" t="n">
         <v>16716</v>
       </c>
-      <c r="L51" s="3" t="n">
-        <v/>
+      <c r="L51" s="4" t="n">
+        <v>136</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v/>
+        <v>8.359999999999999</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v/>
+        <v>18.36</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>136</v>
+        <v>117.64</v>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -3643,24 +3643,24 @@
       <c r="K52" s="2" t="n">
         <v>13890</v>
       </c>
-      <c r="L52" s="3" t="n">
-        <v/>
+      <c r="L52" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v/>
+        <v>6.95</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v/>
+        <v>16.95</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>280</v>
+        <v>263.05</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -3704,24 +3704,24 @@
       <c r="K53" s="2" t="n">
         <v>18024</v>
       </c>
-      <c r="L53" s="3" t="n">
-        <v/>
+      <c r="L53" s="4" t="n">
+        <v>324</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v/>
+        <v>9.01</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v/>
+        <v>19.01</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>324</v>
+        <v>304.99</v>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -3765,24 +3765,24 @@
       <c r="K54" s="2" t="n">
         <v>32990</v>
       </c>
-      <c r="L54" s="3" t="n">
-        <v/>
+      <c r="L54" s="4" t="n">
+        <v>614</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v/>
+        <v>16.5</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v/>
+        <v>26.5</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>614</v>
+        <v>587.5</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -3826,24 +3826,24 @@
       <c r="K55" s="2" t="n">
         <v>11336</v>
       </c>
-      <c r="L55" s="3" t="n">
-        <v/>
+      <c r="L55" s="4" t="n">
+        <v>214</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v/>
+        <v>5.67</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v/>
+        <v>15.67</v>
       </c>
       <c r="P55" s="4" t="n">
-        <v>214</v>
+        <v>198.33</v>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -3887,24 +3887,24 @@
       <c r="K56" s="2" t="n">
         <v>69942</v>
       </c>
-      <c r="L56" s="3" t="n">
-        <v/>
+      <c r="L56" s="4" t="n">
+        <v>340</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v/>
+        <v>13.95</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v/>
+        <v>34.97</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v/>
+        <v>48.92</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>340</v>
+        <v>291.08</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -3948,24 +3948,24 @@
       <c r="K57" s="2" t="n">
         <v>9882</v>
       </c>
-      <c r="L57" s="3" t="n">
-        <v/>
+      <c r="L57" s="4" t="n">
+        <v>135</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v/>
+        <v>4.94</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v/>
+        <v>14.94</v>
       </c>
       <c r="P57" s="4" t="n">
-        <v>135</v>
+        <v>120.06</v>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B050"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="0000B050"/>
     </font>
   </fonts>
   <fills count="3">
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
       <c r="K2" s="2" t="n">
         <v>71598</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="3" t="n">
         <v>647</v>
       </c>
       <c r="M2" s="2" t="n">
@@ -605,7 +605,7 @@
       <c r="O2" s="2" t="n">
         <v>50.05</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="3" t="n">
         <v>596.95</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       <c r="K3" s="2" t="n">
         <v>54746</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="3" t="n">
         <v>1104</v>
       </c>
       <c r="M3" s="2" t="n">
@@ -666,7 +666,7 @@
       <c r="O3" s="2" t="n">
         <v>38.21</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="3" t="n">
         <v>1065.79</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="K4" s="2" t="n">
         <v>47076</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="3" t="n">
         <v>542</v>
       </c>
       <c r="M4" s="2" t="n">
@@ -727,7 +727,7 @@
       <c r="O4" s="2" t="n">
         <v>33.54</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="3" t="n">
         <v>508.46</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       <c r="K5" s="2" t="n">
         <v>18098</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="3" t="n">
         <v>120</v>
       </c>
       <c r="M5" s="2" t="n">
@@ -788,7 +788,7 @@
       <c r="O5" s="2" t="n">
         <v>19.05</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="3" t="n">
         <v>100.95</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="K6" s="2" t="n">
         <v>69998</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="3" t="n">
         <v>605.33</v>
       </c>
       <c r="M6" s="2" t="n">
@@ -849,7 +849,7 @@
       <c r="O6" s="2" t="n">
         <v>48.94</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="3" t="n">
         <v>556.39</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       <c r="K7" s="2" t="n">
         <v>7223</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="3" t="n">
         <v>134</v>
       </c>
       <c r="M7" s="2" t="n">
@@ -910,7 +910,7 @@
       <c r="O7" s="2" t="n">
         <v>13.61</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="3" t="n">
         <v>120.39</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       <c r="K8" s="2" t="n">
         <v>19235</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="3" t="n">
         <v>167</v>
       </c>
       <c r="M8" s="2" t="n">
@@ -971,7 +971,7 @@
       <c r="O8" s="2" t="n">
         <v>19.62</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="3" t="n">
         <v>147.38</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       <c r="K9" s="2" t="n">
         <v>30795.52</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="3" t="n">
         <v>179.2</v>
       </c>
       <c r="M9" s="2" t="n">
@@ -1032,7 +1032,7 @@
       <c r="O9" s="2" t="n">
         <v>25.4</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="P9" s="3" t="n">
         <v>153.8</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       <c r="K10" s="2" t="n">
         <v>44756</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="3" t="n">
         <v>352.5</v>
       </c>
       <c r="M10" s="2" t="n">
@@ -1093,7 +1093,7 @@
       <c r="O10" s="2" t="n">
         <v>32.38</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="3" t="n">
         <v>320.12</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="K11" s="2" t="n">
         <v>8985</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="3" t="n">
         <v>202</v>
       </c>
       <c r="M11" s="2" t="n">
@@ -1154,7 +1154,7 @@
       <c r="O11" s="2" t="n">
         <v>14.49</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="3" t="n">
         <v>187.51</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="K12" s="2" t="n">
         <v>11794</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="3" t="n">
         <v>216</v>
       </c>
       <c r="M12" s="2" t="n">
@@ -1215,7 +1215,7 @@
       <c r="O12" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="P12" s="3" t="n">
         <v>200.1</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="K13" s="2" t="n">
         <v>37697</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="3" t="n">
         <v>313</v>
       </c>
       <c r="M13" s="2" t="n">
@@ -1276,7 +1276,7 @@
       <c r="O13" s="2" t="n">
         <v>28.85</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P13" s="3" t="n">
         <v>284.15</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       <c r="K14" s="2" t="n">
         <v>53418</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="3" t="n">
         <v>582</v>
       </c>
       <c r="M14" s="2" t="n">
@@ -1337,7 +1337,7 @@
       <c r="O14" s="2" t="n">
         <v>37.34</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="3" t="n">
         <v>544.66</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       <c r="K15" s="2" t="n">
         <v>52356</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="4" t="n">
         <v>-572.08</v>
       </c>
       <c r="M15" s="2" t="n">
@@ -1398,7 +1398,7 @@
       <c r="O15" s="2" t="n">
         <v>36.71</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="P15" s="4" t="n">
         <v>-608.79</v>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="K16" s="2" t="n">
         <v>143601</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="3" t="n">
         <v>1393</v>
       </c>
       <c r="M16" s="2" t="n">
@@ -1459,7 +1459,7 @@
       <c r="O16" s="2" t="n">
         <v>100.38</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="P16" s="3" t="n">
         <v>1292.62</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       <c r="K17" s="2" t="n">
         <v>50510</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="3" t="n">
         <v>330</v>
       </c>
       <c r="M17" s="2" t="n">
@@ -1520,7 +1520,7 @@
       <c r="O17" s="2" t="n">
         <v>35.32</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="P17" s="3" t="n">
         <v>294.68</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       <c r="K18" s="2" t="n">
         <v>19520</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="3" t="n">
         <v>106</v>
       </c>
       <c r="M18" s="2" t="n">
@@ -1581,7 +1581,7 @@
       <c r="O18" s="2" t="n">
         <v>19.76</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="P18" s="3" t="n">
         <v>86.23999999999999</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       <c r="K19" s="2" t="n">
         <v>26280</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="3" t="n">
         <v>400</v>
       </c>
       <c r="M19" s="2" t="n">
@@ -1642,7 +1642,7 @@
       <c r="O19" s="2" t="n">
         <v>23.14</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="P19" s="3" t="n">
         <v>376.86</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       <c r="K20" s="2" t="n">
         <v>10149</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="3" t="n">
         <v>40</v>
       </c>
       <c r="M20" s="2" t="n">
@@ -1703,7 +1703,7 @@
       <c r="O20" s="2" t="n">
         <v>15.07</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="P20" s="3" t="n">
         <v>24.93</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       <c r="K21" s="2" t="n">
         <v>19866</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="3" t="n">
         <v>614</v>
       </c>
       <c r="M21" s="2" t="n">
@@ -1764,7 +1764,7 @@
       <c r="O21" s="2" t="n">
         <v>19.93</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="P21" s="3" t="n">
         <v>594.0700000000001</v>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       <c r="K22" s="2" t="n">
         <v>121049</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="3" t="n">
         <v>4182</v>
       </c>
       <c r="M22" s="2" t="n">
@@ -1825,7 +1825,7 @@
       <c r="O22" s="2" t="n">
         <v>84.31</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="P22" s="3" t="n">
         <v>4097.69</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="K23" s="2" t="n">
         <v>67176</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="3" t="n">
         <v>922</v>
       </c>
       <c r="M23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       <c r="O23" s="2" t="n">
         <v>46.93</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="P23" s="3" t="n">
         <v>875.0700000000001</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       <c r="K24" s="2" t="n">
         <v>9999</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="4" t="n">
         <v>-17</v>
       </c>
       <c r="M24" s="2" t="n">
@@ -1947,7 +1947,7 @@
       <c r="O24" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="P24" s="4" t="n">
         <v>-32</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       <c r="K25" s="2" t="n">
         <v>107258</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="3" t="n">
         <v>1804</v>
       </c>
       <c r="M25" s="2" t="n">
@@ -2008,7 +2008,7 @@
       <c r="O25" s="2" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P25" s="3" t="n">
         <v>1729.1</v>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="K26" s="2" t="n">
         <v>70206</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="4" t="n">
         <v>-3597</v>
       </c>
       <c r="M26" s="2" t="n">
@@ -2069,7 +2069,7 @@
       <c r="O26" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="P26" s="4" t="n">
         <v>-3646.5</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       <c r="K27" s="2" t="n">
         <v>88147</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="3" t="n">
         <v>655</v>
       </c>
       <c r="M27" s="2" t="n">
@@ -2130,7 +2130,7 @@
       <c r="O27" s="2" t="n">
         <v>61.63</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="P27" s="3" t="n">
         <v>593.37</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       <c r="K28" s="2" t="n">
         <v>19070</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="4" t="n">
         <v>-270</v>
       </c>
       <c r="M28" s="2" t="n">
@@ -2191,7 +2191,7 @@
       <c r="O28" s="2" t="n">
         <v>19.54</v>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="P28" s="4" t="n">
         <v>-289.54</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       <c r="K29" s="2" t="n">
         <v>44285</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="3" t="n">
         <v>610</v>
       </c>
       <c r="M29" s="2" t="n">
@@ -2252,7 +2252,7 @@
       <c r="O29" s="2" t="n">
         <v>32.14</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="P29" s="3" t="n">
         <v>577.86</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       <c r="K30" s="2" t="n">
         <v>61050</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="3" t="n">
         <v>759</v>
       </c>
       <c r="M30" s="2" t="n">
@@ -2313,7 +2313,7 @@
       <c r="O30" s="2" t="n">
         <v>42.66</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="3" t="n">
         <v>716.34</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       <c r="K31" s="2" t="n">
         <v>90142</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="3" t="n">
         <v>611</v>
       </c>
       <c r="M31" s="2" t="n">
@@ -2374,7 +2374,7 @@
       <c r="O31" s="2" t="n">
         <v>63.04</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="3" t="n">
         <v>547.96</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       <c r="K32" s="2" t="n">
         <v>253280.45</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="3" t="n">
         <v>2470.45</v>
       </c>
       <c r="M32" s="2" t="n">
@@ -2435,7 +2435,7 @@
       <c r="O32" s="2" t="n">
         <v>177.05</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="P32" s="3" t="n">
         <v>2293.4</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       <c r="K33" s="2" t="n">
         <v>18468</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="3" t="n">
         <v>526</v>
       </c>
       <c r="M33" s="2" t="n">
@@ -2496,7 +2496,7 @@
       <c r="O33" s="2" t="n">
         <v>19.23</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="P33" s="3" t="n">
         <v>506.77</v>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       <c r="K34" s="2" t="n">
         <v>11446</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="3" t="n">
         <v>258</v>
       </c>
       <c r="M34" s="2" t="n">
@@ -2557,7 +2557,7 @@
       <c r="O34" s="2" t="n">
         <v>15.72</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="P34" s="3" t="n">
         <v>242.28</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       <c r="K35" s="2" t="n">
         <v>109959</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="4" t="n">
         <v>-527</v>
       </c>
       <c r="M35" s="2" t="n">
@@ -2618,7 +2618,7 @@
       <c r="O35" s="2" t="n">
         <v>77.02</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="P35" s="4" t="n">
         <v>-604.02</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2667,7 +2667,7 @@
       <c r="K36" s="2" t="n">
         <v>43538</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="4" t="n">
         <v>-262</v>
       </c>
       <c r="M36" s="2" t="n">
@@ -2679,7 +2679,7 @@
       <c r="O36" s="2" t="n">
         <v>31.77</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="P36" s="4" t="n">
         <v>-293.77</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       <c r="K37" s="2" t="n">
         <v>180099</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="3" t="n">
         <v>975</v>
       </c>
       <c r="M37" s="2" t="n">
@@ -2740,7 +2740,7 @@
       <c r="O37" s="2" t="n">
         <v>125.97</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="P37" s="3" t="n">
         <v>849.03</v>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       <c r="K38" s="2" t="n">
         <v>32503.5</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="3" t="n">
         <v>172.5</v>
       </c>
       <c r="M38" s="2" t="n">
@@ -2801,7 +2801,7 @@
       <c r="O38" s="2" t="n">
         <v>26.25</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="P38" s="3" t="n">
         <v>146.25</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="K39" s="2" t="n">
         <v>20636</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="3" t="n">
         <v>124</v>
       </c>
       <c r="M39" s="2" t="n">
@@ -2862,7 +2862,7 @@
       <c r="O39" s="2" t="n">
         <v>20.32</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="P39" s="3" t="n">
         <v>103.68</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       <c r="K40" s="2" t="n">
         <v>20638</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="3" t="n">
         <v>136</v>
       </c>
       <c r="M40" s="2" t="n">
@@ -2923,7 +2923,7 @@
       <c r="O40" s="2" t="n">
         <v>20.32</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="P40" s="3" t="n">
         <v>115.68</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="K41" s="2" t="n">
         <v>31337</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="3" t="n">
         <v>236</v>
       </c>
       <c r="M41" s="2" t="n">
@@ -2984,7 +2984,7 @@
       <c r="O41" s="2" t="n">
         <v>25.67</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="P41" s="3" t="n">
         <v>210.33</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       <c r="K42" s="2" t="n">
         <v>35009.8</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="3" t="n">
         <v>264.18</v>
       </c>
       <c r="M42" s="2" t="n">
@@ -3045,7 +3045,7 @@
       <c r="O42" s="2" t="n">
         <v>27.5</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="P42" s="3" t="n">
         <v>236.68</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       <c r="K43" s="2" t="n">
         <v>61233</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="L43" s="3" t="n">
         <v>282</v>
       </c>
       <c r="M43" s="2" t="n">
@@ -3106,7 +3106,7 @@
       <c r="O43" s="2" t="n">
         <v>42.84</v>
       </c>
-      <c r="P43" s="4" t="n">
+      <c r="P43" s="3" t="n">
         <v>239.16</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       <c r="K44" s="2" t="n">
         <v>43057</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="3" t="n">
         <v>322</v>
       </c>
       <c r="M44" s="2" t="n">
@@ -3167,7 +3167,7 @@
       <c r="O44" s="2" t="n">
         <v>31.53</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="P44" s="3" t="n">
         <v>290.47</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       <c r="K45" s="2" t="n">
         <v>43406</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="L45" s="3" t="n">
         <v>417</v>
       </c>
       <c r="M45" s="2" t="n">
@@ -3228,7 +3228,7 @@
       <c r="O45" s="2" t="n">
         <v>31.7</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="P45" s="3" t="n">
         <v>385.3</v>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
       <c r="K46" s="2" t="n">
         <v>19976</v>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="L46" s="3" t="n">
         <v>460</v>
       </c>
       <c r="M46" s="2" t="n">
@@ -3289,7 +3289,7 @@
       <c r="O46" s="2" t="n">
         <v>19.99</v>
       </c>
-      <c r="P46" s="4" t="n">
+      <c r="P46" s="3" t="n">
         <v>440.01</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       <c r="K47" s="2" t="n">
         <v>55705.9</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="L47" s="4" t="n">
         <v>-2.1</v>
       </c>
       <c r="M47" s="2" t="n">
@@ -3350,7 +3350,7 @@
       <c r="O47" s="2" t="n">
         <v>38.99</v>
       </c>
-      <c r="P47" s="3" t="n">
+      <c r="P47" s="4" t="n">
         <v>-41.09</v>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       <c r="K48" s="2" t="n">
         <v>13728</v>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="L48" s="3" t="n">
         <v>160.65</v>
       </c>
       <c r="M48" s="2" t="n">
@@ -3411,7 +3411,7 @@
       <c r="O48" s="2" t="n">
         <v>16.86</v>
       </c>
-      <c r="P48" s="4" t="n">
+      <c r="P48" s="3" t="n">
         <v>143.79</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       <c r="K49" s="2" t="n">
         <v>31190</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="L49" s="3" t="n">
         <v>285</v>
       </c>
       <c r="M49" s="2" t="n">
@@ -3472,7 +3472,7 @@
       <c r="O49" s="2" t="n">
         <v>25.6</v>
       </c>
-      <c r="P49" s="4" t="n">
+      <c r="P49" s="3" t="n">
         <v>259.4</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       <c r="K50" s="2" t="n">
         <v>17600</v>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="L50" s="3" t="n">
         <v>116</v>
       </c>
       <c r="M50" s="2" t="n">
@@ -3533,7 +3533,7 @@
       <c r="O50" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="P50" s="4" t="n">
+      <c r="P50" s="3" t="n">
         <v>97.2</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       <c r="K51" s="2" t="n">
         <v>16716</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="L51" s="3" t="n">
         <v>136</v>
       </c>
       <c r="M51" s="2" t="n">
@@ -3594,7 +3594,7 @@
       <c r="O51" s="2" t="n">
         <v>18.36</v>
       </c>
-      <c r="P51" s="4" t="n">
+      <c r="P51" s="3" t="n">
         <v>117.64</v>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       <c r="K52" s="2" t="n">
         <v>13890</v>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="L52" s="3" t="n">
         <v>280</v>
       </c>
       <c r="M52" s="2" t="n">
@@ -3655,7 +3655,7 @@
       <c r="O52" s="2" t="n">
         <v>16.95</v>
       </c>
-      <c r="P52" s="4" t="n">
+      <c r="P52" s="3" t="n">
         <v>263.05</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       <c r="K53" s="2" t="n">
         <v>18024</v>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="L53" s="3" t="n">
         <v>324</v>
       </c>
       <c r="M53" s="2" t="n">
@@ -3716,7 +3716,7 @@
       <c r="O53" s="2" t="n">
         <v>19.01</v>
       </c>
-      <c r="P53" s="4" t="n">
+      <c r="P53" s="3" t="n">
         <v>304.99</v>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       <c r="K54" s="2" t="n">
         <v>32990</v>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="L54" s="3" t="n">
         <v>614</v>
       </c>
       <c r="M54" s="2" t="n">
@@ -3777,7 +3777,7 @@
       <c r="O54" s="2" t="n">
         <v>26.5</v>
       </c>
-      <c r="P54" s="4" t="n">
+      <c r="P54" s="3" t="n">
         <v>587.5</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       <c r="K55" s="2" t="n">
         <v>11336</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="L55" s="3" t="n">
         <v>214</v>
       </c>
       <c r="M55" s="2" t="n">
@@ -3838,7 +3838,7 @@
       <c r="O55" s="2" t="n">
         <v>15.67</v>
       </c>
-      <c r="P55" s="4" t="n">
+      <c r="P55" s="3" t="n">
         <v>198.33</v>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       <c r="K56" s="2" t="n">
         <v>69942</v>
       </c>
-      <c r="L56" s="4" t="n">
+      <c r="L56" s="3" t="n">
         <v>340</v>
       </c>
       <c r="M56" s="2" t="n">
@@ -3899,7 +3899,7 @@
       <c r="O56" s="2" t="n">
         <v>48.92</v>
       </c>
-      <c r="P56" s="4" t="n">
+      <c r="P56" s="3" t="n">
         <v>291.08</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       <c r="K57" s="2" t="n">
         <v>9882</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="L57" s="3" t="n">
         <v>135</v>
       </c>
       <c r="M57" s="2" t="n">
@@ -3960,7 +3960,7 @@
       <c r="O57" s="2" t="n">
         <v>14.94</v>
       </c>
-      <c r="P57" s="4" t="n">
+      <c r="P57" s="3" t="n">
         <v>120.06</v>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       <c r="K58" s="2" t="n">
         <v>10046</v>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="L58" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M58" s="2" t="n">
@@ -4021,7 +4021,7 @@
       <c r="O58" s="2" t="n">
         <v>15.02</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="P58" s="3" t="n">
         <v>0.98</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       <c r="K59" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="3" t="n">
         <v>228</v>
       </c>
       <c r="M59" s="2" t="n">
@@ -4082,7 +4082,7 @@
       <c r="O59" s="2" t="n">
         <v>32.52</v>
       </c>
-      <c r="P59" s="4" t="n">
+      <c r="P59" s="3" t="n">
         <v>195.48</v>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       <c r="K60" s="2" t="n">
         <v>203742</v>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="L60" s="3" t="n">
         <v>1664</v>
       </c>
       <c r="M60" s="2" t="n">
@@ -4143,7 +4143,7 @@
       <c r="O60" s="2" t="n">
         <v>142.45</v>
       </c>
-      <c r="P60" s="4" t="n">
+      <c r="P60" s="3" t="n">
         <v>1521.55</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -4163,10 +4163,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C61" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
@@ -4194,7 +4192,7 @@
       <c r="K61" s="2" t="n">
         <v>12726</v>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="L61" s="3" t="n">
         <v>178</v>
       </c>
       <c r="M61" s="2" t="n">
@@ -4206,12 +4204,382 @@
       <c r="O61" s="2" t="n">
         <v>16.36</v>
       </c>
-      <c r="P61" s="4" t="n">
+      <c r="P61" s="3" t="n">
         <v>161.64</v>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>1.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2594</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>9997</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>322.0466</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>323.9733</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>193227.99</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>194384</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>1156.01</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>135.95</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>1020.06</v>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2222</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>105.895</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>108.24</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>21179</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>21648</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>469</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>448.18</v>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>601208</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>22945</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>23100</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>875.55</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>886.5599999999999</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>87555</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>88656</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>1039.05</v>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>548.76</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>559.99</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>54876</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>55999</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>1123</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>1083.91</v>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>1.98%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4468,10 +4468,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C66" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
@@ -4531,10 +4529,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C67" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -4580,6 +4576,573 @@
       <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>1.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>348.38</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>69676</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>6.9676</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>-41.81</v>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>18755</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>-14.38</v>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>443.33</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>446.475</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>44333</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>44647.5</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>282.18</v>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>446.475</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>44647.5</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>-27.32</v>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>10275</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>10880</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>-10.44</v>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>542</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>54200</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>55100</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>861.52</v>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>331.205</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>334.31</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>33120.5</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>33431</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>331.205</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>33120.5</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4590,10 +4590,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C68" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
@@ -4653,10 +4651,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
+      <c r="C69" s="2" t="n">
+        <v>688062</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
@@ -4716,10 +4712,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C70" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
@@ -4779,10 +4773,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C71" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
@@ -4842,10 +4834,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>601899</t>
-        </is>
+      <c r="C72" s="2" t="n">
+        <v>601899</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
@@ -4905,10 +4895,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C73" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
@@ -4968,10 +4956,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C74" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
@@ -5031,10 +5017,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C75" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
@@ -5094,10 +5078,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C76" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
@@ -5143,6 +5125,636 @@
       <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>43957</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>105.67</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>10567</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>107.76</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>109.4471</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>75432</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>76613</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1181</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>1127.49</v>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>1014.5</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1017.14</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>101450</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>101714</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>71.18000000000001</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>192.82</v>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>34011</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>-22.01</v>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>5592</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>123269</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>金杨转债</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>161.666</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1616.66</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>344.0049</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>345.736</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>344004.87</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>345736</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>1731.13</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>172.87</v>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>241.84</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>1489.29</v>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>300014</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>13774</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>5440</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5139,10 +5139,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C77" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
@@ -5202,10 +5200,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C78" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
@@ -5265,10 +5261,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C79" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5322,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C80" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
@@ -5391,10 +5383,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C81" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
@@ -5454,10 +5444,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C82" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
@@ -5517,10 +5505,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>123269</t>
-        </is>
+      <c r="C83" s="2" t="n">
+        <v>123269</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
@@ -5580,10 +5566,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C84" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
@@ -5643,10 +5627,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>300014</t>
-        </is>
+      <c r="C85" s="2" t="n">
+        <v>300014</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
@@ -5706,10 +5688,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>300450</t>
-        </is>
+      <c r="C86" s="2" t="n">
+        <v>300450</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
@@ -5753,6 +5733,1077 @@
         <v>-5</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>6077</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>146312</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>14.6312</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>-14.63</v>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>10436</v>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v>-10.22</v>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>111.69</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>116.53</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>11169</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>11653</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>484</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>468.17</v>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>4.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>332.415</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>337.8425</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>132966</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>135137</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>2171</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>2076.62</v>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>337.8425</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>135137</v>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>81.08</v>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v>-81.08</v>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>583.02</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>587.42</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>58302</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>58742</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>398.93</v>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>587.42</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>58742</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="P94" s="4" t="n">
+        <v>-35.24</v>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>5619</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P95" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>14200</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>14330</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>112.83</v>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>35370</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="P97" s="4" t="n">
+        <v>-22.68</v>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>14154</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>14880</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>708.5599999999999</v>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>5.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>36779</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="P99" s="4" t="n">
+        <v>-23.39</v>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>16875</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>17055</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>161.47</v>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>16875</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P101" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>11804</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="P102" s="4" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>12986</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P103" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5749,10 +5749,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C87" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
@@ -5812,10 +5810,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C88" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
@@ -5875,10 +5871,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C89" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
@@ -5938,10 +5932,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C90" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
@@ -6001,10 +5993,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C91" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6054,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C92" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
@@ -6127,10 +6115,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C93" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
@@ -6190,10 +6176,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C94" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
@@ -6253,10 +6237,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C95" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
@@ -6316,10 +6298,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C96" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
@@ -6379,10 +6359,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
+      <c r="C97" s="2" t="n">
+        <v>688062</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
@@ -6442,10 +6420,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C98" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
@@ -6505,10 +6481,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C99" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
@@ -6568,10 +6542,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C100" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
@@ -6631,10 +6603,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C101" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
@@ -6694,10 +6664,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C102" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
@@ -6757,10 +6725,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C103" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
@@ -6806,6 +6772,384 @@
       <c r="Q103" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>384.71</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>152220</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>153884</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>1664</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="O104" s="2" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>1556.45</v>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>68804</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>6.880400000000001</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="P105" s="4" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>115.9725</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>34791.75</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>35070</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>278.25</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="P106" s="3" t="n">
+        <v>250.71</v>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>115.9725</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>11597.25</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P107" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>23080</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>23310</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="O108" s="2" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>208.34</v>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>621.99</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>630</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>62199</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>63000</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>801</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="P109" s="3" t="n">
+        <v>756.98</v>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>1.22%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6786,10 +6786,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C104" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
@@ -6849,10 +6847,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C105" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6908,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C106" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
@@ -6975,10 +6969,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C107" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
@@ -7038,10 +7030,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C108" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
@@ -7101,10 +7091,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C109" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
@@ -7150,6 +7138,825 @@
       <c r="Q109" s="2" t="inlineStr">
         <is>
           <t>1.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>601.13</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>614.79</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>60113</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>61479</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>1366</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="O110" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="P110" s="3" t="n">
+        <v>1323.1</v>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>108.22</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>10563</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>10822</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="O111" s="2" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="P111" s="3" t="n">
+        <v>243.59</v>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>403.7333</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>409.4</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>161493.33</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>163760</v>
+      </c>
+      <c r="L112" s="3" t="n">
+        <v>2266.67</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="O112" s="2" t="n">
+        <v>114.41</v>
+      </c>
+      <c r="P112" s="3" t="n">
+        <v>2152.26</v>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>403.7333</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>80746.67</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="2" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="P113" s="4" t="n">
+        <v>-8.07</v>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>603881</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>数据港</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>12726</v>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="P114" s="4" t="n">
+        <v>-11.36</v>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>302.79</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>304.48</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>60558</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>60896</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="O115" s="2" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="P115" s="3" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>134.16</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>26500</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>26832</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="O116" s="2" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="P116" s="3" t="n">
+        <v>308.58</v>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>199.23</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>19923</v>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="O117" s="2" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="P117" s="4" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>512000</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>券商ETF</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>10180</v>
+      </c>
+      <c r="L118" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="O118" s="2" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="P118" s="4" t="n">
+        <v>-10.09</v>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>55.3933</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>16618</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P119" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>32.195</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>12878</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P120" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>15720</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>16002</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P121" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>聚和材</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>111.42</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>44568</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>44852</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="O122" s="2" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="P122" s="3" t="n">
+        <v>251.57</v>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.56%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q122"/>
+  <dimension ref="A1:Q128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7152,10 +7152,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C110" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
@@ -7215,10 +7213,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C111" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
@@ -7278,10 +7274,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C112" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
@@ -7341,10 +7335,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C113" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
@@ -7404,10 +7396,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>603881</t>
-        </is>
+      <c r="C114" s="2" t="n">
+        <v>603881</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
@@ -7467,10 +7457,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C115" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
@@ -7530,10 +7518,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C116" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
@@ -7593,10 +7579,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C117" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
@@ -7656,10 +7640,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>512000</t>
-        </is>
+      <c r="C118" s="2" t="n">
+        <v>512000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
@@ -7719,10 +7701,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C119" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
@@ -7782,10 +7762,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>601899</t>
-        </is>
+      <c r="C120" s="2" t="n">
+        <v>601899</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
@@ -7845,10 +7823,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>300450</t>
-        </is>
+      <c r="C121" s="2" t="n">
+        <v>300450</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
@@ -7908,10 +7884,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C122" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
@@ -7957,6 +7931,384 @@
       <c r="Q122" s="2" t="inlineStr">
         <is>
           <t>0.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1052.13</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>1043.99</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>105213</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>104399</v>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>-814</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="O123" s="2" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="P123" s="4" t="n">
+        <v>-887.16</v>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>14526</v>
+      </c>
+      <c r="L124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="P124" s="4" t="n">
+        <v>-12.26</v>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>304.035</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>303.19</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>60807</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>60638</v>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>-169</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="O125" s="2" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="P125" s="4" t="n">
+        <v>-211.46</v>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>304.035</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>60807</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="P126" s="4" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>407.07</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>80460</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>81414</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>954</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="O127" s="2" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="P127" s="3" t="n">
+        <v>897.1</v>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>607.16</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>60716</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>61300</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>584</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="P128" s="3" t="n">
+        <v>541.15</v>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.89%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q128"/>
+  <dimension ref="A1:Q130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7942,58 +7942,58 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>两融账户+手机账户</t>
+          <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>300308</t>
+          <t>300054</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>1052.13</v>
+        <v>0</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1043.99</v>
+        <v>72.63</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>105213</v>
+        <v>0</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>104399</v>
+        <v>14526</v>
       </c>
       <c r="L123" s="4" t="n">
-        <v>-814</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>20.96</v>
+        <v>5</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>52.2</v>
+        <v>7.26</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>73.16</v>
+        <v>12.26</v>
       </c>
       <c r="P123" s="4" t="n">
-        <v>-887.16</v>
+        <v>-12.26</v>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>
@@ -8005,58 +8005,58 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>两融账户+手机账户</t>
+          <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>300054</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>200</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>0</v>
+        <v>304.035</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>72.63</v>
+        <v>303.19</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0</v>
+        <v>60807</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>14526</v>
+        <v>60638</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0</v>
+        <v>-169</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5</v>
+        <v>12.14</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>7.26</v>
+        <v>30.32</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>12.26</v>
+        <v>42.46</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>-12.26</v>
+        <v>-211.46</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>-0.35%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>两融账户+手机账户</t>
+          <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -8082,44 +8082,44 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>304.035</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>303.19</v>
+        <v>0</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>60807</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>60638</v>
+        <v>0</v>
       </c>
       <c r="L125" s="4" t="n">
-        <v>-169</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12.14</v>
+        <v>6.08</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>30.32</v>
+        <v>0</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>42.46</v>
+        <v>6.08</v>
       </c>
       <c r="P125" s="4" t="n">
-        <v>-211.46</v>
+        <v>-6.08</v>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>
@@ -8131,58 +8131,58 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>两融账户+手机账户</t>
+          <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>300308</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>304.035</v>
+        <v>1052.13</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
+        <v>1043.99</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>60807</v>
+        <v>105213</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>104399</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>0</v>
+        <v>-814</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>6.08</v>
+        <v>20.96</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0</v>
+        <v>52.2</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>6.08</v>
+        <v>73.16</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>-6.08</v>
+        <v>-887.16</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>⚠️多买未平仓</t>
+          <t>-0.84%</t>
         </is>
       </c>
     </row>
@@ -8194,58 +8194,58 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>两融账户+手机账户</t>
+          <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
         <v>200</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>402.3</v>
+        <v>58.23</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>407.07</v>
+        <v>59.7</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>80460</v>
+        <v>5823</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>81414</v>
+        <v>5970</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>954</v>
+        <v>147</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>16.19</v>
+        <v>10</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>40.71</v>
+        <v>2.98</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>56.9</v>
+        <v>12.98</v>
       </c>
       <c r="P127" s="3" t="n">
-        <v>897.1</v>
+        <v>134.02</v>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -8257,56 +8257,182 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>5823</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P128" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>407.07</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>80460</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>81414</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>954</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="O129" s="2" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="P129" s="3" t="n">
+        <v>897.1</v>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>300502</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>新易盛</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H128" s="2" t="n">
+      <c r="E130" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H130" s="2" t="n">
         <v>607.16</v>
       </c>
-      <c r="I128" s="2" t="n">
+      <c r="I130" s="2" t="n">
         <v>613</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J130" s="2" t="n">
         <v>60716</v>
       </c>
-      <c r="K128" s="2" t="n">
+      <c r="K130" s="2" t="n">
         <v>61300</v>
       </c>
-      <c r="L128" s="3" t="n">
+      <c r="L130" s="3" t="n">
         <v>584</v>
       </c>
-      <c r="M128" s="2" t="n">
+      <c r="M130" s="2" t="n">
         <v>12.2</v>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N130" s="2" t="n">
         <v>30.65</v>
       </c>
-      <c r="O128" s="2" t="n">
+      <c r="O130" s="2" t="n">
         <v>42.85</v>
       </c>
-      <c r="P128" s="3" t="n">
+      <c r="P130" s="3" t="n">
         <v>541.15</v>
       </c>
-      <c r="Q128" s="2" t="inlineStr">
+      <c r="Q130" s="2" t="inlineStr">
         <is>
           <t>0.89%</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q130"/>
+  <dimension ref="A1:Q135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7945,10 +7945,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C123" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
@@ -8008,10 +8006,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C124" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
@@ -8071,10 +8067,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C125" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
@@ -8134,10 +8128,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C126" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
@@ -8197,10 +8189,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C127" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
@@ -8260,10 +8250,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C128" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
@@ -8323,10 +8311,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C129" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
@@ -8386,10 +8372,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C130" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
@@ -8435,6 +8419,321 @@
       <c r="Q130" s="2" t="inlineStr">
         <is>
           <t>0.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>17090</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P131" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>33530</v>
+      </c>
+      <c r="L132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="O132" s="2" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="P132" s="4" t="n">
+        <v>-21.76</v>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>393.9</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>400.48</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>78780</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>80096</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>1316</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="O133" s="2" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>1260.06</v>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>400.48</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>80096</v>
+      </c>
+      <c r="L134" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="P134" s="4" t="n">
+        <v>-48.06</v>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O135" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P135" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q135"/>
+  <dimension ref="A1:Q145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8433,10 +8433,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>688035</t>
-        </is>
+      <c r="C131" s="2" t="n">
+        <v>688035</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8494,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
+      <c r="C132" s="2" t="n">
+        <v>688062</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
@@ -8559,10 +8555,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C133" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
@@ -8622,10 +8616,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C134" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
@@ -8685,10 +8677,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C135" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
@@ -8732,6 +8722,636 @@
         <v>-11.5</v>
       </c>
       <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>317.685</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>316.98</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>63537</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>63396</v>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>-141</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="P136" s="4" t="n">
+        <v>-185.39</v>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>317.685</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>63537</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="P137" s="4" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>587.55</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>590.9</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>58755</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>59090</v>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="O138" s="2" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="P138" s="3" t="n">
+        <v>293.68</v>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>15356</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P139" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>101.51</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>20302</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>20900</v>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>598</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="O140" s="2" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="P140" s="3" t="n">
+        <v>577.55</v>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>396.4767</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>400.97</v>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>158590.67</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>160388</v>
+      </c>
+      <c r="L141" s="3" t="n">
+        <v>1797.33</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="O141" s="2" t="n">
+        <v>112.09</v>
+      </c>
+      <c r="P141" s="3" t="n">
+        <v>1685.24</v>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>396.4767</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>7929.53</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P142" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>11842</v>
+      </c>
+      <c r="L143" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="O143" s="2" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="P143" s="4" t="n">
+        <v>-10.92</v>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>17930</v>
+      </c>
+      <c r="L144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="O144" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="P144" s="4" t="n">
+        <v>-13.96</v>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>16845</v>
+      </c>
+      <c r="L145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="O145" s="2" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="P145" s="4" t="n">
+        <v>-13.42</v>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8738,10 +8738,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C136" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
@@ -8801,10 +8799,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C137" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
@@ -8864,10 +8860,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C138" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
@@ -8927,10 +8921,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C139" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
@@ -8990,10 +8982,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C140" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
@@ -9053,10 +9043,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C141" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
@@ -9116,10 +9104,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C142" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
@@ -9179,10 +9165,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C143" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
@@ -9242,10 +9226,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>688035</t>
-        </is>
+      <c r="C144" s="2" t="n">
+        <v>688035</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
@@ -9305,10 +9287,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C145" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
@@ -9354,6 +9334,699 @@
       <c r="Q145" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>323.273</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>193963.83</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>198756</v>
+      </c>
+      <c r="L146" s="3" t="n">
+        <v>4792.17</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="O146" s="2" t="n">
+        <v>138.65</v>
+      </c>
+      <c r="P146" s="3" t="n">
+        <v>4653.52</v>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>323.273</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>96981.91</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P147" s="4" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>410.57</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>416.97</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>82114</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>83394</v>
+      </c>
+      <c r="L148" s="3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="P148" s="3" t="n">
+        <v>1221.75</v>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>410.57</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>82114</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="P149" s="4" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>16845</v>
+      </c>
+      <c r="L150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="O150" s="2" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="P150" s="4" t="n">
+        <v>-13.42</v>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>587.55</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>590.9</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>58755</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>59090</v>
+      </c>
+      <c r="L151" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="O151" s="2" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="P151" s="3" t="n">
+        <v>293.68</v>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>417.93</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>41793</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P152" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>10476</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P153" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>17858</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P154" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>11842</v>
+      </c>
+      <c r="L155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="O155" s="2" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="P155" s="4" t="n">
+        <v>-10.92</v>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>106.09</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>21218</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P156" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -9350,53 +9350,53 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>300450</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>323.273</v>
+        <v>52.38</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>331.26</v>
+        <v>0</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>193963.83</v>
+        <v>10476</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>198756</v>
-      </c>
-      <c r="L146" s="3" t="n">
-        <v>4792.17</v>
+        <v>0</v>
+      </c>
+      <c r="L146" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="n">
-        <v>39.27</v>
+        <v>5</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>99.38</v>
+        <v>0</v>
       </c>
       <c r="O146" s="2" t="n">
-        <v>138.65</v>
-      </c>
-      <c r="P146" s="3" t="n">
-        <v>4653.52</v>
+        <v>5</v>
+      </c>
+      <c r="P146" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -9413,53 +9413,53 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>300308</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>323.273</v>
+        <v>1035.18</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>0</v>
+        <v>1045</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>96981.91</v>
+        <v>103518</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="n">
-        <v>0</v>
+        <v>104500</v>
+      </c>
+      <c r="L147" s="3" t="n">
+        <v>982</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0</v>
+        <v>52.25</v>
       </c>
       <c r="O147" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="P147" s="4" t="n">
-        <v>-9.699999999999999</v>
+        <v>73.05</v>
+      </c>
+      <c r="P147" s="3" t="n">
+        <v>908.95</v>
       </c>
       <c r="Q147" s="2" t="inlineStr">
         <is>
-          <t>⚠️多买未平仓</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -9476,53 +9476,53 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>410.57</v>
+        <v>56.43</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>416.97</v>
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>82114</v>
+        <v>11286</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>83394</v>
-      </c>
-      <c r="L148" s="3" t="n">
-        <v>1280</v>
+        <v>0</v>
+      </c>
+      <c r="L148" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>16.55</v>
+        <v>5</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="O148" s="2" t="n">
-        <v>58.25</v>
-      </c>
-      <c r="P148" s="3" t="n">
-        <v>1221.75</v>
+        <v>5</v>
+      </c>
+      <c r="P148" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
@@ -9557,13 +9557,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>410.57</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>82114</v>
+        <v>17858</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>0</v>
@@ -9572,20 +9572,20 @@
         <v>0</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>5</v>
       </c>
       <c r="N149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O149" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>5</v>
       </c>
       <c r="P149" s="4" t="n">
-        <v>-8.210000000000001</v>
+        <v>-5</v>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>⚠️多买未平仓</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -9602,53 +9602,53 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>0</v>
+        <v>410.57</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>33.69</v>
+        <v>416.97</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0</v>
+        <v>82114</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>16845</v>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v>0</v>
+        <v>83394</v>
+      </c>
+      <c r="L150" s="3" t="n">
+        <v>1280</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>5</v>
+        <v>16.55</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>8.42</v>
+        <v>41.7</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v>-13.42</v>
+        <v>58.25</v>
+      </c>
+      <c r="P150" s="3" t="n">
+        <v>1221.75</v>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -9665,53 +9665,53 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>587.55</v>
+        <v>410.57</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>590.9</v>
+        <v>0</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>58755</v>
+        <v>82114</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>59090</v>
-      </c>
-      <c r="L151" s="3" t="n">
-        <v>335</v>
+        <v>0</v>
+      </c>
+      <c r="L151" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="n">
-        <v>11.78</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>29.54</v>
+        <v>0</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>41.32</v>
-      </c>
-      <c r="P151" s="3" t="n">
-        <v>293.68</v>
+        <v>8.210000000000001</v>
+      </c>
+      <c r="P151" s="4" t="n">
+        <v>-8.210000000000001</v>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>300450</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="E153" s="2" t="n">
@@ -9809,13 +9809,13 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>52.38</v>
+        <v>106.09</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>10476</v>
+        <v>21218</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>0</v>
@@ -9854,16 +9854,16 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>0</v>
@@ -9872,13 +9872,13 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>89.29000000000001</v>
+        <v>573.5599999999999</v>
       </c>
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>17858</v>
+        <v>57356</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>0</v>
@@ -9887,16 +9887,16 @@
         <v>0</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5</v>
+        <v>5.735600000000001</v>
       </c>
       <c r="N154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>5</v>
+        <v>5.74</v>
       </c>
       <c r="P154" s="4" t="n">
-        <v>-5</v>
+        <v>-5.74</v>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
@@ -9917,53 +9917,53 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>0</v>
+        <v>323.273</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>59.21</v>
+        <v>331.26</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0</v>
+        <v>193963.83</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>11842</v>
-      </c>
-      <c r="L155" s="4" t="n">
-        <v>0</v>
+        <v>198756</v>
+      </c>
+      <c r="L155" s="3" t="n">
+        <v>4792.17</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5</v>
+        <v>39.27</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>5.92</v>
+        <v>99.38</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="P155" s="4" t="n">
-        <v>-10.92</v>
+        <v>138.65</v>
+      </c>
+      <c r="P155" s="3" t="n">
+        <v>4653.52</v>
       </c>
       <c r="Q155" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -9980,16 +9980,16 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>0</v>
@@ -9998,13 +9998,13 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>106.09</v>
+        <v>323.273</v>
       </c>
       <c r="I156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>21218</v>
+        <v>96981.91</v>
       </c>
       <c r="K156" s="2" t="n">
         <v>0</v>
@@ -10013,20 +10013,20 @@
         <v>0</v>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P156" s="4" t="n">
-        <v>-5</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q156"/>
+  <dimension ref="A1:Q166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9348,10 +9348,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>300450</t>
-        </is>
+      <c r="C146" s="2" t="n">
+        <v>300450</v>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
@@ -9411,10 +9409,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C147" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
@@ -9474,10 +9470,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C148" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
@@ -9537,10 +9531,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>688035</t>
-        </is>
+      <c r="C149" s="2" t="n">
+        <v>688035</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
@@ -9600,10 +9592,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C150" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
@@ -9663,10 +9653,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C151" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
@@ -9726,10 +9714,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C152" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
@@ -9789,10 +9775,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C153" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
@@ -9852,10 +9836,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C154" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
@@ -9915,10 +9897,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C155" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
@@ -9978,10 +9958,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C156" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
@@ -10027,6 +10005,636 @@
       <c r="Q156" s="2" t="inlineStr">
         <is>
           <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>25250</v>
+      </c>
+      <c r="L157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="O157" s="2" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="P157" s="4" t="n">
+        <v>-17.62</v>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>1017.06</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>1026.99</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>101706</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>102699</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>993</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="O158" s="2" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="P158" s="3" t="n">
+        <v>921.21</v>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>12642</v>
+      </c>
+      <c r="L159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="O159" s="2" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="P159" s="4" t="n">
+        <v>-11.32</v>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>424.5626</v>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>263228.8</v>
+      </c>
+      <c r="L160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>26.32288</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>131.61</v>
+      </c>
+      <c r="O160" s="2" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="P160" s="4" t="n">
+        <v>-157.93</v>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>300660</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>江苏雷利</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>23970</v>
+      </c>
+      <c r="L161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="O161" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="P161" s="4" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>300014</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>12928</v>
+      </c>
+      <c r="L162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="O162" s="2" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="P162" s="4" t="n">
+        <v>-11.46</v>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>574.025</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>799.2477</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>114805</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>159849.54</v>
+      </c>
+      <c r="L163" s="3" t="n">
+        <v>45044.54</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="O163" s="2" t="n">
+        <v>107.39</v>
+      </c>
+      <c r="P163" s="3" t="n">
+        <v>44937.15</v>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>39.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>799.2477</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>14386.46</v>
+      </c>
+      <c r="L164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="O164" s="2" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="P164" s="4" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>聚和材</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>109.28</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>21856</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P165" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>303.85</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>305.95</v>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>60770</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>61190</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="O166" s="2" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="P166" s="3" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.62%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -10021,53 +10021,53 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>0</v>
+        <v>574.025</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>50.5</v>
+        <v>580.7867</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0</v>
+        <v>114805</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>25250</v>
-      </c>
-      <c r="L157" s="4" t="n">
-        <v>0</v>
+        <v>116157.33</v>
+      </c>
+      <c r="L157" s="3" t="n">
+        <v>1352.33</v>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5</v>
+        <v>23.1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>12.62</v>
+        <v>58.08</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>17.62</v>
-      </c>
-      <c r="P157" s="4" t="n">
-        <v>-17.62</v>
+        <v>81.18000000000001</v>
+      </c>
+      <c r="P157" s="3" t="n">
+        <v>1271.15</v>
       </c>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -10084,53 +10084,53 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>300308</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>100</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>1017.06</v>
+        <v>0</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1026.99</v>
+        <v>580.7867</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>101706</v>
+        <v>0</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>102699</v>
-      </c>
-      <c r="L158" s="3" t="n">
-        <v>993</v>
+        <v>58078.67</v>
+      </c>
+      <c r="L158" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="n">
-        <v>20.44</v>
+        <v>5.81</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>51.35</v>
+        <v>29.04</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="P158" s="3" t="n">
-        <v>921.21</v>
+        <v>34.85</v>
+      </c>
+      <c r="P158" s="4" t="n">
+        <v>-34.85</v>
       </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>
@@ -10147,34 +10147,34 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>688503</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>聚和材</t>
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G159" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>0</v>
+        <v>109.28</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>63.21</v>
+        <v>0</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0</v>
+        <v>21856</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>12642</v>
+        <v>0</v>
       </c>
       <c r="L159" s="4" t="n">
         <v>0</v>
@@ -10183,17 +10183,17 @@
         <v>5</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>6.32</v>
+        <v>0</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>11.32</v>
+        <v>5</v>
       </c>
       <c r="P159" s="4" t="n">
-        <v>-11.32</v>
+        <v>-5</v>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -10210,19 +10210,19 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>300014</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>亿纬锂能</t>
         </is>
       </c>
       <c r="E160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>620</v>
+        <v>200</v>
       </c>
       <c r="G160" s="2" t="n">
         <v>0</v>
@@ -10231,28 +10231,28 @@
         <v>0</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>424.5626</v>
+        <v>64.64</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>263228.8</v>
+        <v>12928</v>
       </c>
       <c r="L160" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M160" s="2" t="n">
-        <v>26.32288</v>
+        <v>5</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>131.61</v>
+        <v>6.46</v>
       </c>
       <c r="O160" s="2" t="n">
-        <v>157.93</v>
+        <v>11.46</v>
       </c>
       <c r="P160" s="4" t="n">
-        <v>-157.93</v>
+        <v>-11.46</v>
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
@@ -10273,53 +10273,53 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>300660</t>
+          <t>300308</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>江苏雷利</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>0</v>
+        <v>1017.06</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>47.94</v>
+        <v>1026.99</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0</v>
+        <v>101706</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>23970</v>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v>0</v>
+        <v>102699</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>993</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5</v>
+        <v>20.44</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>11.98</v>
+        <v>51.35</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v>-16.98</v>
+        <v>71.79000000000001</v>
+      </c>
+      <c r="P161" s="3" t="n">
+        <v>921.21</v>
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -10336,19 +10336,19 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>300014</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>200</v>
+        <v>620</v>
       </c>
       <c r="G162" s="2" t="n">
         <v>0</v>
@@ -10357,28 +10357,28 @@
         <v>0</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>64.64</v>
+        <v>424.5626</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>12928</v>
+        <v>263228.8</v>
       </c>
       <c r="L162" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M162" s="2" t="n">
-        <v>5</v>
+        <v>26.32288</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>6.46</v>
+        <v>131.61</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>11.46</v>
+        <v>157.93</v>
       </c>
       <c r="P162" s="4" t="n">
-        <v>-11.46</v>
+        <v>-157.93</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
@@ -10399,53 +10399,53 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300660</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>江苏雷利</t>
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>218</v>
+        <v>500</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>574.025</v>
+        <v>0</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>799.2477</v>
+        <v>47.94</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>114805</v>
+        <v>0</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>159849.54</v>
-      </c>
-      <c r="L163" s="3" t="n">
-        <v>45044.54</v>
+        <v>23970</v>
+      </c>
+      <c r="L163" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="n">
-        <v>27.47</v>
+        <v>5</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>79.92</v>
+        <v>11.98</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>107.39</v>
-      </c>
-      <c r="P163" s="3" t="n">
-        <v>44937.15</v>
+        <v>16.98</v>
+      </c>
+      <c r="P163" s="4" t="n">
+        <v>-16.98</v>
       </c>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>39.14%</t>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>
@@ -10462,53 +10462,53 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>0</v>
+        <v>303.85</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>799.2477</v>
+        <v>305.95</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0</v>
+        <v>60770</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>14386.46</v>
-      </c>
-      <c r="L164" s="4" t="n">
-        <v>0</v>
+        <v>61190</v>
+      </c>
+      <c r="L164" s="3" t="n">
+        <v>420</v>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5</v>
+        <v>12.2</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>7.19</v>
+        <v>30.6</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="P164" s="4" t="n">
-        <v>-12.19</v>
+        <v>42.8</v>
+      </c>
+      <c r="P164" s="3" t="n">
+        <v>377.2</v>
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>⚠️多卖未平仓</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -10525,34 +10525,34 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>688503</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>聚和材</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>109.28</v>
+        <v>0</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
+        <v>63.21</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>21856</v>
+        <v>0</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0</v>
+        <v>12642</v>
       </c>
       <c r="L165" s="4" t="n">
         <v>0</v>
@@ -10561,17 +10561,17 @@
         <v>5</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>5</v>
+        <v>11.32</v>
       </c>
       <c r="P165" s="4" t="n">
-        <v>-5</v>
+        <v>-11.32</v>
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>
@@ -10588,53 +10588,53 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>601208</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>303.85</v>
+        <v>0</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>305.95</v>
+        <v>50.5</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>60770</v>
+        <v>0</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>61190</v>
-      </c>
-      <c r="L166" s="3" t="n">
-        <v>420</v>
+        <v>25250</v>
+      </c>
+      <c r="L166" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>12.2</v>
+        <v>5</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>30.6</v>
+        <v>12.62</v>
       </c>
       <c r="O166" s="2" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="P166" s="3" t="n">
-        <v>377.2</v>
+        <v>17.62</v>
+      </c>
+      <c r="P166" s="4" t="n">
+        <v>-17.62</v>
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q166"/>
+  <dimension ref="A1:Q175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10019,10 +10019,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C157" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
@@ -10082,10 +10080,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C158" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10141,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C159" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
@@ -10208,10 +10202,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>300014</t>
-        </is>
+      <c r="C160" s="2" t="n">
+        <v>300014</v>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
@@ -10271,10 +10263,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C161" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
@@ -10334,10 +10324,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C162" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
@@ -10397,10 +10385,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>300660</t>
-        </is>
+      <c r="C163" s="2" t="n">
+        <v>300660</v>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
@@ -10460,10 +10446,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C164" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
@@ -10523,10 +10507,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C165" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
@@ -10586,10 +10568,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C166" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
@@ -10635,6 +10615,573 @@
       <c r="Q166" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1092.4</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>108900</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>109240</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="O167" s="2" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="P167" s="3" t="n">
+        <v>263.57</v>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>5351</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P168" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>318.01</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>321.73</v>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>95403</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>96519</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>1116</v>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="O169" s="2" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="P169" s="3" t="n">
+        <v>1048.55</v>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>321.73</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>96519</v>
+      </c>
+      <c r="L170" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="O170" s="2" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="P170" s="4" t="n">
+        <v>-57.91</v>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>438.03</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>87606</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>8.7606</v>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="2" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="P171" s="4" t="n">
+        <v>-8.76</v>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>11394</v>
+      </c>
+      <c r="L172" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O172" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="P172" s="3" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>7596</v>
+      </c>
+      <c r="L173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O173" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P173" s="4" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>16005</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>16140</v>
+      </c>
+      <c r="L174" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="O174" s="2" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="P174" s="3" t="n">
+        <v>116.93</v>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>653.02</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>656.05</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>65302</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>65605</v>
+      </c>
+      <c r="L175" s="3" t="n">
+        <v>303</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="P175" s="3" t="n">
+        <v>257.11</v>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.39%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q175"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10631,53 +10631,53 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>300308</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>1089</v>
+        <v>53.51</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1092.4</v>
+        <v>0</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>108900</v>
+        <v>10702</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>109240</v>
-      </c>
-      <c r="L167" s="3" t="n">
-        <v>340</v>
+        <v>0</v>
+      </c>
+      <c r="L167" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>21.81</v>
+        <v>5</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>54.62</v>
+        <v>0</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>76.43000000000001</v>
-      </c>
-      <c r="P167" s="3" t="n">
-        <v>263.57</v>
+        <v>5</v>
+      </c>
+      <c r="P167" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q167" s="2" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -10694,53 +10694,53 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E168" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>53.51</v>
+        <v>653.02</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
+        <v>656.05</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>5351</v>
+        <v>65302</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="n">
-        <v>0</v>
+        <v>65605</v>
+      </c>
+      <c r="L168" s="3" t="n">
+        <v>303</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5</v>
+        <v>13.09</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="O168" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P168" s="4" t="n">
-        <v>-5</v>
+        <v>45.89</v>
+      </c>
+      <c r="P168" s="3" t="n">
+        <v>257.11</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -10757,53 +10757,53 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>002436</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>318.01</v>
+        <v>37.39</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>321.73</v>
+        <v>37.98</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>95403</v>
+        <v>18695</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>96519</v>
+        <v>18990</v>
       </c>
       <c r="L169" s="3" t="n">
-        <v>1116</v>
+        <v>295</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>19.19</v>
+        <v>10</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>48.26</v>
+        <v>9.5</v>
       </c>
       <c r="O169" s="2" t="n">
-        <v>67.45</v>
+        <v>19.5</v>
       </c>
       <c r="P169" s="3" t="n">
-        <v>1048.55</v>
+        <v>275.5</v>
       </c>
       <c r="Q169" s="2" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -10820,53 +10820,53 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688062</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>0</v>
+        <v>32.01</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>321.73</v>
+        <v>32.28</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0</v>
+        <v>16005</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>96519</v>
-      </c>
-      <c r="L170" s="4" t="n">
-        <v>0</v>
+        <v>16140</v>
+      </c>
+      <c r="L170" s="3" t="n">
+        <v>135</v>
       </c>
       <c r="M170" s="2" t="n">
-        <v>9.65</v>
+        <v>10</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>48.26</v>
+        <v>8.07</v>
       </c>
       <c r="O170" s="2" t="n">
-        <v>57.91</v>
-      </c>
-      <c r="P170" s="4" t="n">
-        <v>-57.91</v>
+        <v>18.07</v>
+      </c>
+      <c r="P170" s="3" t="n">
+        <v>116.93</v>
       </c>
       <c r="Q170" s="2" t="inlineStr">
         <is>
-          <t>⚠️多卖未平仓</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -10883,53 +10883,53 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>438.03</v>
+        <v>318.01</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>0</v>
+        <v>321.73</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>87606</v>
+        <v>95403</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="4" t="n">
-        <v>0</v>
+        <v>96519</v>
+      </c>
+      <c r="L171" s="3" t="n">
+        <v>1116</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8.7606</v>
+        <v>19.19</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0</v>
+        <v>48.26</v>
       </c>
       <c r="O171" s="2" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="P171" s="4" t="n">
-        <v>-8.76</v>
+        <v>67.45</v>
+      </c>
+      <c r="P171" s="3" t="n">
+        <v>1048.55</v>
       </c>
       <c r="Q171" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -10946,53 +10946,53 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F172" s="2" t="n">
-        <v>500</v>
-      </c>
       <c r="G172" s="2" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>37.39</v>
+        <v>0</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>37.98</v>
+        <v>321.73</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>11217</v>
+        <v>0</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>11394</v>
-      </c>
-      <c r="L172" s="3" t="n">
-        <v>177</v>
+        <v>96519</v>
+      </c>
+      <c r="L172" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>10</v>
+        <v>9.65</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>5.7</v>
+        <v>48.26</v>
       </c>
       <c r="O172" s="2" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="P172" s="3" t="n">
-        <v>161.3</v>
+        <v>57.91</v>
+      </c>
+      <c r="P172" s="4" t="n">
+        <v>-57.91</v>
       </c>
       <c r="Q172" s="2" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>
@@ -11009,179 +11009,53 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G173" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>0</v>
+        <v>438.03</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>37.98</v>
+        <v>0</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0</v>
+        <v>87606</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>7596</v>
+        <v>0</v>
       </c>
       <c r="L173" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5</v>
+        <v>8.7606</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="P173" s="4" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.76</v>
       </c>
       <c r="Q173" s="2" t="inlineStr">
         <is>
-          <t>⚠️多卖未平仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>两融账户+手机账户</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>迈威生物</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="F174" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="G174" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="H174" s="2" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="I174" s="2" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>16005</v>
-      </c>
-      <c r="K174" s="2" t="n">
-        <v>16140</v>
-      </c>
-      <c r="L174" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="M174" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N174" s="2" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="O174" s="2" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="P174" s="3" t="n">
-        <v>116.93</v>
-      </c>
-      <c r="Q174" s="2" t="inlineStr">
-        <is>
-          <t>0.73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>两融账户+手机账户</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>新易盛</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F175" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G175" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H175" s="2" t="n">
-        <v>653.02</v>
-      </c>
-      <c r="I175" s="2" t="n">
-        <v>656.05</v>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>65302</v>
-      </c>
-      <c r="K175" s="2" t="n">
-        <v>65605</v>
-      </c>
-      <c r="L175" s="3" t="n">
-        <v>303</v>
-      </c>
-      <c r="M175" s="2" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="N175" s="2" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="O175" s="2" t="n">
-        <v>45.89</v>
-      </c>
-      <c r="P175" s="3" t="n">
-        <v>257.11</v>
-      </c>
-      <c r="Q175" s="2" t="inlineStr">
-        <is>
-          <t>0.39%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q173"/>
+  <dimension ref="A1:Q174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10631,53 +10631,53 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>53.51</v>
+        <v>653.02</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>0</v>
+        <v>656.05</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>10702</v>
+        <v>65302</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="4" t="n">
-        <v>0</v>
+        <v>65605</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>303</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5</v>
+        <v>13.09</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P167" s="4" t="n">
-        <v>-5</v>
+        <v>45.89</v>
+      </c>
+      <c r="P167" s="3" t="n">
+        <v>257.11</v>
       </c>
       <c r="Q167" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>300308</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="E168" s="2" t="n">
@@ -10712,35 +10712,35 @@
         <v>100</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>653.02</v>
+        <v>1089</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>656.05</v>
+        <v>1092.4</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>65302</v>
+        <v>108900</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>65605</v>
+        <v>109240</v>
       </c>
       <c r="L168" s="3" t="n">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>13.09</v>
+        <v>21.81</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>32.8</v>
+        <v>54.62</v>
       </c>
       <c r="O168" s="2" t="n">
-        <v>45.89</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="P168" s="3" t="n">
-        <v>257.11</v>
+        <v>263.57</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -10757,12 +10757,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>688062</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="E169" s="2" t="n">
@@ -10775,35 +10775,35 @@
         <v>500</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>37.39</v>
+        <v>32.01</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>37.98</v>
+        <v>32.28</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>18695</v>
+        <v>16005</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>18990</v>
+        <v>16140</v>
       </c>
       <c r="L169" s="3" t="n">
-        <v>295</v>
+        <v>135</v>
       </c>
       <c r="M169" s="2" t="n">
         <v>10</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>9.5</v>
+        <v>8.07</v>
       </c>
       <c r="O169" s="2" t="n">
-        <v>19.5</v>
+        <v>18.07</v>
       </c>
       <c r="P169" s="3" t="n">
-        <v>275.5</v>
+        <v>116.93</v>
       </c>
       <c r="Q169" s="2" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -10820,12 +10820,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>688062</t>
+          <t>002436</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>迈威生物</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="E170" s="2" t="n">
@@ -10838,35 +10838,35 @@
         <v>500</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>32.01</v>
+        <v>37.39</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>32.28</v>
+        <v>37.98</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>16005</v>
+        <v>18695</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>16140</v>
+        <v>18990</v>
       </c>
       <c r="L170" s="3" t="n">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="M170" s="2" t="n">
         <v>10</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>8.07</v>
+        <v>9.5</v>
       </c>
       <c r="O170" s="2" t="n">
-        <v>18.07</v>
+        <v>19.5</v>
       </c>
       <c r="P170" s="3" t="n">
-        <v>116.93</v>
+        <v>275.5</v>
       </c>
       <c r="Q170" s="2" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -10883,53 +10883,53 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>318.01</v>
+        <v>53.51</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>321.73</v>
+        <v>0</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>95403</v>
+        <v>10702</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>96519</v>
-      </c>
-      <c r="L171" s="3" t="n">
-        <v>1116</v>
+        <v>0</v>
+      </c>
+      <c r="L171" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>19.19</v>
+        <v>5</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>48.26</v>
+        <v>0</v>
       </c>
       <c r="O171" s="2" t="n">
-        <v>67.45</v>
-      </c>
-      <c r="P171" s="3" t="n">
-        <v>1048.55</v>
+        <v>5</v>
+      </c>
+      <c r="P171" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q171" s="2" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -10946,53 +10946,53 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>0</v>
+        <v>438.03</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>321.73</v>
+        <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0</v>
+        <v>87606</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>96519</v>
+        <v>0</v>
       </c>
       <c r="L172" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>9.65</v>
+        <v>8.7606</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>48.26</v>
+        <v>0</v>
       </c>
       <c r="O172" s="2" t="n">
-        <v>57.91</v>
+        <v>8.76</v>
       </c>
       <c r="P172" s="4" t="n">
-        <v>-57.91</v>
+        <v>-8.76</v>
       </c>
       <c r="Q172" s="2" t="inlineStr">
         <is>
-          <t>⚠️多卖未平仓</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -11009,53 +11009,116 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>438.03</v>
+        <v>318.01</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>0</v>
+        <v>321.73</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>87606</v>
+        <v>95403</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="4" t="n">
-        <v>0</v>
+        <v>96519</v>
+      </c>
+      <c r="L173" s="3" t="n">
+        <v>1116</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8.7606</v>
+        <v>19.19</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0</v>
+        <v>48.26</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="P173" s="4" t="n">
-        <v>-8.76</v>
+        <v>67.45</v>
+      </c>
+      <c r="P173" s="3" t="n">
+        <v>1048.55</v>
       </c>
       <c r="Q173" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>1.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>321.73</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>96519</v>
+      </c>
+      <c r="L174" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="O174" s="2" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="P174" s="4" t="n">
+        <v>-57.91</v>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q174"/>
+  <dimension ref="A1:Q184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10629,10 +10629,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C167" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
@@ -10692,10 +10690,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C168" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
@@ -10755,10 +10751,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
+      <c r="C169" s="2" t="n">
+        <v>688062</v>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
@@ -10818,10 +10812,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C170" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
@@ -10881,10 +10873,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C171" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
@@ -10944,10 +10934,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C172" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
@@ -11007,10 +10995,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C173" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
@@ -11070,10 +11056,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C174" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
@@ -11119,6 +11103,636 @@
       <c r="Q174" s="2" t="inlineStr">
         <is>
           <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>19195</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P175" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>聚和材</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>109.3218</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>21864.36</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>22220</v>
+      </c>
+      <c r="L176" s="3" t="n">
+        <v>355.64</v>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="O176" s="2" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="P176" s="3" t="n">
+        <v>334.53</v>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>聚和材</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>109.3218</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>27221.13</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P177" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>450.12</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>460.99</v>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>90024</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>92198</v>
+      </c>
+      <c r="L178" s="3" t="n">
+        <v>2174</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="O178" s="2" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P178" s="3" t="n">
+        <v>2109.68</v>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>1085.05</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>1090.28</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>108505</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>109028</v>
+      </c>
+      <c r="L179" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="O179" s="2" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="P179" s="3" t="n">
+        <v>446.74</v>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>91.1033</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>18220.67</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>17800</v>
+      </c>
+      <c r="L180" s="4" t="n">
+        <v>-420.67</v>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O180" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="P180" s="4" t="n">
+        <v>-439.57</v>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>-2.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>91.1033</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>36441.33</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P181" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>686.51</v>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>690.235</v>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>137302</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>138047</v>
+      </c>
+      <c r="L182" s="3" t="n">
+        <v>745</v>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>69.02</v>
+      </c>
+      <c r="O182" s="2" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="P182" s="3" t="n">
+        <v>648.45</v>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>10222</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P183" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>325.5856</v>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>328.3078</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>293027</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>295477</v>
+      </c>
+      <c r="L184" s="3" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>147.74</v>
+      </c>
+      <c r="O184" s="2" t="n">
+        <v>206.59</v>
+      </c>
+      <c r="P184" s="3" t="n">
+        <v>2243.41</v>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.77%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -11187,11 +11187,11 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>聚和材</t>
+          <t>聚和材料</t>
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>449</v>
+        <v>400</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>200</v>
@@ -11200,19 +11200,19 @@
         <v>200</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>109.3218</v>
+        <v>109.36</v>
       </c>
       <c r="I176" s="2" t="n">
         <v>111.1</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>21864.36</v>
+        <v>21872</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>22220</v>
       </c>
       <c r="L176" s="3" t="n">
-        <v>355.64</v>
+        <v>348</v>
       </c>
       <c r="M176" s="2" t="n">
         <v>10</v>
@@ -11224,11 +11224,11 @@
         <v>21.11</v>
       </c>
       <c r="P176" s="3" t="n">
-        <v>334.53</v>
+        <v>326.89</v>
       </c>
       <c r="Q176" s="2" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -11250,11 +11250,11 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>聚和材</t>
+          <t>聚和材料</t>
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>0</v>
@@ -11263,13 +11263,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>109.3218</v>
+        <v>109.36</v>
       </c>
       <c r="I177" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>27221.13</v>
+        <v>21872</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>0</v>
@@ -11308,12 +11308,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E178" s="2" t="n">
@@ -11326,35 +11326,35 @@
         <v>200</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>450.12</v>
+        <v>686.51</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>460.99</v>
+        <v>690.235</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>90024</v>
+        <v>137302</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>92198</v>
+        <v>138047</v>
       </c>
       <c r="L178" s="3" t="n">
-        <v>2174</v>
+        <v>745</v>
       </c>
       <c r="M178" s="2" t="n">
-        <v>18.22</v>
+        <v>27.53</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>46.1</v>
+        <v>69.02</v>
       </c>
       <c r="O178" s="2" t="n">
-        <v>64.31999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="P178" s="3" t="n">
-        <v>2109.68</v>
+        <v>648.45</v>
       </c>
       <c r="Q178" s="2" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -11434,16 +11434,16 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F180" s="2" t="n">
         <v>200</v>
@@ -11452,35 +11452,35 @@
         <v>200</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>91.1033</v>
+        <v>450.12</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>89</v>
+        <v>460.99</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>18220.67</v>
+        <v>90024</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>17800</v>
-      </c>
-      <c r="L180" s="4" t="n">
-        <v>-420.67</v>
+        <v>92198</v>
+      </c>
+      <c r="L180" s="3" t="n">
+        <v>2174</v>
       </c>
       <c r="M180" s="2" t="n">
-        <v>10</v>
+        <v>18.22</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>8.9</v>
+        <v>46.1</v>
       </c>
       <c r="O180" s="2" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="P180" s="4" t="n">
-        <v>-439.57</v>
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P180" s="3" t="n">
+        <v>2109.68</v>
       </c>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -11497,53 +11497,53 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>91.1033</v>
+        <v>325.5856</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>0</v>
+        <v>328.3078</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>36441.33</v>
+        <v>293027</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="4" t="n">
-        <v>0</v>
+        <v>295477</v>
+      </c>
+      <c r="L181" s="3" t="n">
+        <v>2450</v>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5</v>
+        <v>58.85</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0</v>
+        <v>147.74</v>
       </c>
       <c r="O181" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P181" s="4" t="n">
-        <v>-5</v>
+        <v>206.59</v>
+      </c>
+      <c r="P181" s="3" t="n">
+        <v>2243.41</v>
       </c>
       <c r="Q181" s="2" t="inlineStr">
         <is>
-          <t>⚠️多买未平仓</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -11560,16 +11560,16 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>200</v>
@@ -11578,35 +11578,35 @@
         <v>200</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>686.51</v>
+        <v>91.1033</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>690.235</v>
+        <v>89</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>137302</v>
+        <v>18220.67</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>138047</v>
-      </c>
-      <c r="L182" s="3" t="n">
-        <v>745</v>
+        <v>17800</v>
+      </c>
+      <c r="L182" s="4" t="n">
+        <v>-420.67</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>27.53</v>
+        <v>10</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>69.02</v>
+        <v>8.9</v>
       </c>
       <c r="O182" s="2" t="n">
-        <v>96.55</v>
-      </c>
-      <c r="P182" s="3" t="n">
-        <v>648.45</v>
+        <v>18.9</v>
+      </c>
+      <c r="P182" s="4" t="n">
+        <v>-439.57</v>
       </c>
       <c r="Q182" s="2" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>-2.41%</t>
         </is>
       </c>
     </row>
@@ -11623,16 +11623,16 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>0</v>
@@ -11641,13 +11641,13 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>51.11</v>
+        <v>91.1033</v>
       </c>
       <c r="I183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>10222</v>
+        <v>36441.33</v>
       </c>
       <c r="K183" s="2" t="n">
         <v>0</v>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="Q183" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>
@@ -11686,53 +11686,53 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>325.5856</v>
+        <v>51.11</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>328.3078</v>
+        <v>0</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>293027</v>
+        <v>10222</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>295477</v>
-      </c>
-      <c r="L184" s="3" t="n">
-        <v>2450</v>
+        <v>0</v>
+      </c>
+      <c r="L184" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>58.85</v>
+        <v>5</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>147.74</v>
+        <v>0</v>
       </c>
       <c r="O184" s="2" t="n">
-        <v>206.59</v>
-      </c>
-      <c r="P184" s="3" t="n">
-        <v>2243.41</v>
+        <v>5</v>
+      </c>
+      <c r="P184" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q184"/>
+  <dimension ref="A1:Q188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11117,10 +11117,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C175" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
@@ -11180,10 +11178,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C176" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
@@ -11243,10 +11239,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C177" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
@@ -11306,10 +11300,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C178" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
@@ -11369,10 +11361,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C179" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
@@ -11432,10 +11422,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C180" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
@@ -11495,10 +11483,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C181" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
@@ -11558,10 +11544,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>688035</t>
-        </is>
+      <c r="C182" s="2" t="n">
+        <v>688035</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
@@ -11621,10 +11605,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>688035</t>
-        </is>
+      <c r="C183" s="2" t="n">
+        <v>688035</v>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
@@ -11684,10 +11666,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C184" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
@@ -11733,6 +11713,258 @@
       <c r="Q184" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>1139.99</v>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>113100</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>113999</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>899</v>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="O185" s="2" t="n">
+        <v>79.70999999999999</v>
+      </c>
+      <c r="P185" s="3" t="n">
+        <v>819.29</v>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>429.01</v>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>85802</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>88200</v>
+      </c>
+      <c r="L186" s="3" t="n">
+        <v>2398</v>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="O186" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="P186" s="3" t="n">
+        <v>2336.5</v>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>327.94</v>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>65588</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>6.558800000000001</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P187" s="4" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>418.01</v>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>41801</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>42700</v>
+      </c>
+      <c r="L188" s="3" t="n">
+        <v>899</v>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="O188" s="2" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="P188" s="3" t="n">
+        <v>867.65</v>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>2.08%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q188"/>
+  <dimension ref="A1:Q192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11727,10 +11727,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C185" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
@@ -11790,10 +11788,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C186" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
@@ -11853,10 +11849,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C187" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
@@ -11916,10 +11910,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C188" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
@@ -11965,6 +11957,258 @@
       <c r="Q188" s="2" t="inlineStr">
         <is>
           <t>2.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>309.508</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>312.036</v>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>154754</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>156018</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>1264</v>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="O189" s="2" t="n">
+        <v>109.09</v>
+      </c>
+      <c r="P189" s="3" t="n">
+        <v>1154.91</v>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>405.05</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>411.79</v>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>81010</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>82358</v>
+      </c>
+      <c r="L190" s="3" t="n">
+        <v>1348</v>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="N190" s="2" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="O190" s="2" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="P190" s="3" t="n">
+        <v>1290.48</v>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>德邦科技</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>84.14</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>16828</v>
+      </c>
+      <c r="L191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="P191" s="4" t="n">
+        <v>-13.41</v>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>107.96</v>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>21592</v>
+      </c>
+      <c r="L192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O192" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P192" s="4" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q192"/>
+  <dimension ref="A1:Q195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11971,10 +11971,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C189" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
@@ -12034,10 +12032,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C190" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
@@ -12097,10 +12093,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>688035</t>
-        </is>
+      <c r="C191" s="2" t="n">
+        <v>688035</v>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
@@ -12160,10 +12154,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C192" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
@@ -12209,6 +12201,195 @@
       <c r="Q192" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>88.76000000000001</v>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>17752</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>18608</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>856</v>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N193" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O193" s="2" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="P193" s="3" t="n">
+        <v>836.7</v>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>1138.65</v>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>1148.99</v>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>113865</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>114899</v>
+      </c>
+      <c r="L194" s="3" t="n">
+        <v>1034</v>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="N194" s="2" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="O194" s="2" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="P194" s="3" t="n">
+        <v>953.67</v>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>39.655</v>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>38670</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>39655</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>985</v>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="O195" s="2" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="P195" s="3" t="n">
+        <v>955.17</v>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>2.47%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q195"/>
+  <dimension ref="A1:Q199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12215,10 +12215,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C193" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
@@ -12278,10 +12276,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C194" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
@@ -12341,10 +12337,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C195" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
@@ -12390,6 +12384,258 @@
       <c r="Q195" s="2" t="inlineStr">
         <is>
           <t>2.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>1193.95</v>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>1197.57</v>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>119395</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>119757</v>
+      </c>
+      <c r="L196" s="3" t="n">
+        <v>362</v>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="N196" s="2" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="O196" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="P196" s="3" t="n">
+        <v>278.2</v>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>719.01</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>722.8150000000001</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>71901</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>72281.5</v>
+      </c>
+      <c r="L197" s="3" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="O197" s="2" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="P197" s="3" t="n">
+        <v>329.94</v>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>722.8150000000001</v>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="2" t="n">
+        <v>72281.5</v>
+      </c>
+      <c r="L198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="O198" s="2" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="P198" s="4" t="n">
+        <v>-43.37</v>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>19755</v>
+      </c>
+      <c r="L199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="O199" s="2" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="P199" s="4" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q199"/>
+  <dimension ref="A1:Q205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12398,10 +12398,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C196" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
@@ -12461,10 +12459,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C197" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
@@ -12524,10 +12520,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C198" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
@@ -12587,10 +12581,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C199" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
@@ -12636,6 +12628,384 @@
       <c r="Q199" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>284.41</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>288.03</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>56882</v>
+      </c>
+      <c r="K200" s="2" t="n">
+        <v>57606</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>724</v>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="N200" s="2" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O200" s="2" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="P200" s="3" t="n">
+        <v>683.75</v>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>288.03</v>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" s="2" t="n">
+        <v>86409</v>
+      </c>
+      <c r="L201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="N201" s="2" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="O201" s="2" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="P201" s="4" t="n">
+        <v>-51.84</v>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>杰普特</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>404.59</v>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>407.85</v>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v>80918</v>
+      </c>
+      <c r="K202" s="2" t="n">
+        <v>81570</v>
+      </c>
+      <c r="L202" s="3" t="n">
+        <v>652</v>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="O202" s="2" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="P202" s="3" t="n">
+        <v>594.96</v>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>256.76</v>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>51352</v>
+      </c>
+      <c r="K203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>5.1352</v>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="P203" s="4" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v>18964</v>
+      </c>
+      <c r="K204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P204" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="I205" s="2" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>17643</v>
+      </c>
+      <c r="K205" s="2" t="n">
+        <v>17889</v>
+      </c>
+      <c r="L205" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="O205" s="2" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="P205" s="3" t="n">
+        <v>227.06</v>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>1.29%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q205"/>
+  <dimension ref="A1:Q208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12639,58 +12639,58 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G200" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>284.41</v>
+        <v>490.06</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>288.03</v>
+        <v>0</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>56882</v>
+        <v>49006</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>57606</v>
-      </c>
-      <c r="L200" s="3" t="n">
-        <v>724</v>
+        <v>0</v>
+      </c>
+      <c r="L200" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>11.45</v>
+        <v>5</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="P200" s="3" t="n">
-        <v>683.75</v>
+        <v>5</v>
+      </c>
+      <c r="P200" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q200" s="2" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -12702,58 +12702,58 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688025</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>0</v>
+        <v>404.59</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>288.03</v>
+        <v>407.85</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0</v>
+        <v>80918</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>86409</v>
-      </c>
-      <c r="L201" s="4" t="n">
-        <v>0</v>
+        <v>81570</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>652</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>16.25</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>43.2</v>
+        <v>40.79</v>
       </c>
       <c r="O201" s="2" t="n">
-        <v>51.84</v>
-      </c>
-      <c r="P201" s="4" t="n">
-        <v>-51.84</v>
+        <v>57.04</v>
+      </c>
+      <c r="P201" s="3" t="n">
+        <v>594.96</v>
       </c>
       <c r="Q201" s="2" t="inlineStr">
         <is>
-          <t>⚠️多卖未平仓</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -12765,58 +12765,58 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>688025</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E202" s="2" t="n">
         <v>200</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G202" s="2" t="n">
         <v>200</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>404.59</v>
+        <v>284.41</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>407.85</v>
+        <v>288.03</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>80918</v>
+        <v>56882</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>81570</v>
+        <v>57606</v>
       </c>
       <c r="L202" s="3" t="n">
-        <v>652</v>
+        <v>724</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>16.25</v>
+        <v>11.45</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>40.79</v>
+        <v>28.8</v>
       </c>
       <c r="O202" s="2" t="n">
-        <v>57.04</v>
+        <v>40.25</v>
       </c>
       <c r="P202" s="3" t="n">
-        <v>594.96</v>
+        <v>683.75</v>
       </c>
       <c r="Q202" s="2" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -12828,58 +12828,58 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>688008</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G203" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>256.76</v>
+        <v>0</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>0</v>
+        <v>288.03</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>51352</v>
+        <v>0</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>0</v>
+        <v>86409</v>
       </c>
       <c r="L203" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5.1352</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0</v>
+        <v>43.2</v>
       </c>
       <c r="O203" s="2" t="n">
-        <v>5.14</v>
+        <v>51.84</v>
       </c>
       <c r="P203" s="4" t="n">
-        <v>-5.14</v>
+        <v>-51.84</v>
       </c>
       <c r="Q203" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>
@@ -12891,58 +12891,58 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>002594</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>0</v>
+        <v>782.6799999999999</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>18964</v>
+        <v>77356</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" s="4" t="n">
-        <v>0</v>
+        <v>78268</v>
+      </c>
+      <c r="L204" s="3" t="n">
+        <v>912</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>5</v>
+        <v>15.56</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>0</v>
+        <v>39.13</v>
       </c>
       <c r="O204" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P204" s="4" t="n">
-        <v>-5</v>
+        <v>54.69</v>
+      </c>
+      <c r="P204" s="3" t="n">
+        <v>857.3099999999999</v>
       </c>
       <c r="Q204" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -13006,6 +13006,195 @@
       <c r="Q205" s="2" t="inlineStr">
         <is>
           <t>1.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I206" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>20805</v>
+      </c>
+      <c r="K206" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="L206" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O206" s="2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="P206" s="3" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="I207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>18964</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P207" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>256.76</v>
+      </c>
+      <c r="I208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v>51352</v>
+      </c>
+      <c r="K208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>5.1352</v>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="P208" s="4" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q208"/>
+  <dimension ref="A1:Q210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12642,10 +12642,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C200" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
@@ -12705,10 +12703,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>688025</t>
-        </is>
+      <c r="C201" s="2" t="n">
+        <v>688025</v>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
@@ -12768,10 +12764,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C202" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
@@ -12831,10 +12825,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C203" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
@@ -12894,10 +12886,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C204" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
@@ -12957,10 +12947,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C205" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
@@ -13020,10 +13008,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C206" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
@@ -13083,10 +13069,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C207" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
@@ -13146,10 +13130,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C208" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
@@ -13193,6 +13175,132 @@
         <v>-5.14</v>
       </c>
       <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="I209" s="2" t="n">
+        <v>262.92</v>
+      </c>
+      <c r="J209" s="2" t="n">
+        <v>51820</v>
+      </c>
+      <c r="K209" s="2" t="n">
+        <v>52584</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>764</v>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="N209" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="O209" s="2" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="P209" s="3" t="n">
+        <v>727.27</v>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="I210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="2" t="n">
+        <v>19378</v>
+      </c>
+      <c r="K210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P210" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q210"/>
+  <dimension ref="A1:Q214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13191,10 +13191,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C209" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
@@ -13254,10 +13252,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C210" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
@@ -13301,6 +13297,258 @@
         <v>-5</v>
       </c>
       <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>274.19</v>
+      </c>
+      <c r="I211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="2" t="n">
+        <v>82257</v>
+      </c>
+      <c r="K211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>8.2257</v>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" s="2" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="P211" s="4" t="n">
+        <v>-8.23</v>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="I212" s="2" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="J212" s="2" t="n">
+        <v>19256</v>
+      </c>
+      <c r="K212" s="2" t="n">
+        <v>19734</v>
+      </c>
+      <c r="L212" s="3" t="n">
+        <v>478</v>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N212" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="O212" s="2" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="P212" s="3" t="n">
+        <v>458.13</v>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="I213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="2" t="n">
+        <v>18712</v>
+      </c>
+      <c r="K213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P213" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>246.38</v>
+      </c>
+      <c r="I214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="2" t="n">
+        <v>98552</v>
+      </c>
+      <c r="K214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>9.8552</v>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" s="2" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="P214" s="4" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q214"/>
+  <dimension ref="A1:Q226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13313,10 +13313,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C211" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
@@ -13376,10 +13374,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C212" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
@@ -13439,10 +13435,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C213" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
@@ -13502,10 +13496,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C214" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
@@ -13551,6 +13543,762 @@
       <c r="Q214" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" s="2" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="J215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="2" t="n">
+        <v>17727</v>
+      </c>
+      <c r="L215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N215" s="2" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="O215" s="2" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="P215" s="4" t="n">
+        <v>-13.86</v>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="2" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="J216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="2" t="n">
+        <v>26370</v>
+      </c>
+      <c r="L216" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N216" s="2" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="O216" s="2" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="P216" s="4" t="n">
+        <v>-18.18</v>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="I217" s="2" t="n">
+        <v>37.535</v>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>18520</v>
+      </c>
+      <c r="K217" s="2" t="n">
+        <v>18767.5</v>
+      </c>
+      <c r="L217" s="3" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="O217" s="2" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="P217" s="3" t="n">
+        <v>228.12</v>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="2" t="n">
+        <v>37.535</v>
+      </c>
+      <c r="J218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="2" t="n">
+        <v>56302.5</v>
+      </c>
+      <c r="L218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="N218" s="2" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="O218" s="2" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="P218" s="4" t="n">
+        <v>-33.78</v>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G219" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>436.525</v>
+      </c>
+      <c r="I219" s="2" t="n">
+        <v>439.725</v>
+      </c>
+      <c r="J219" s="2" t="n">
+        <v>87305</v>
+      </c>
+      <c r="K219" s="2" t="n">
+        <v>87945</v>
+      </c>
+      <c r="L219" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="O219" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="P219" s="3" t="n">
+        <v>578.5</v>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="2" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="J220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="2" t="n">
+        <v>22155</v>
+      </c>
+      <c r="L220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N220" s="2" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="O220" s="2" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="P220" s="4" t="n">
+        <v>-16.08</v>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G221" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>765.38</v>
+      </c>
+      <c r="I221" s="2" t="n">
+        <v>770.0700000000001</v>
+      </c>
+      <c r="J221" s="2" t="n">
+        <v>76538</v>
+      </c>
+      <c r="K221" s="2" t="n">
+        <v>77007</v>
+      </c>
+      <c r="L221" s="3" t="n">
+        <v>469</v>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="O221" s="2" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="P221" s="3" t="n">
+        <v>415.15</v>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>770.0700000000001</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>77007</v>
+      </c>
+      <c r="L222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="O222" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="P222" s="4" t="n">
+        <v>-46.2</v>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="J223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="2" t="n">
+        <v>28230</v>
+      </c>
+      <c r="L223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="O223" s="2" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="P223" s="4" t="n">
+        <v>-19.12</v>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" s="2" t="n">
+        <v>90.79000000000001</v>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="2" t="n">
+        <v>45395</v>
+      </c>
+      <c r="L224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O224" s="2" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="P224" s="4" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" s="2" t="n">
+        <v>155.06</v>
+      </c>
+      <c r="J225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" s="2" t="n">
+        <v>15506</v>
+      </c>
+      <c r="L225" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O225" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="P225" s="4" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G226" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I226" s="2" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="J226" s="2" t="n">
+        <v>18088</v>
+      </c>
+      <c r="K226" s="2" t="n">
+        <v>18300</v>
+      </c>
+      <c r="L226" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O226" s="2" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="P226" s="3" t="n">
+        <v>192.85</v>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>1.07%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q226"/>
+  <dimension ref="A1:Q228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13557,10 +13557,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C215" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
@@ -13620,10 +13618,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
+      <c r="C216" s="2" t="n">
+        <v>688062</v>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
@@ -13683,10 +13679,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C217" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
@@ -13746,10 +13740,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C218" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
@@ -13809,10 +13801,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C219" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13862,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>300450</t>
-        </is>
+      <c r="C220" s="2" t="n">
+        <v>300450</v>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
@@ -13935,10 +13923,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C221" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
@@ -13998,10 +13984,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C222" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
@@ -14061,10 +14045,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>601899</t>
-        </is>
+      <c r="C223" s="2" t="n">
+        <v>601899</v>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
@@ -14124,10 +14106,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C224" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
@@ -14187,10 +14167,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C225" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
@@ -14250,10 +14228,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C226" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
@@ -14299,6 +14275,132 @@
       <c r="Q226" s="2" t="inlineStr">
         <is>
           <t>1.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G227" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>290.5712</v>
+      </c>
+      <c r="I227" s="2" t="n">
+        <v>291.24</v>
+      </c>
+      <c r="J227" s="2" t="n">
+        <v>232457</v>
+      </c>
+      <c r="K227" s="2" t="n">
+        <v>232992</v>
+      </c>
+      <c r="L227" s="3" t="n">
+        <v>535</v>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="O227" s="2" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="P227" s="3" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="I228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="2" t="n">
+        <v>94000</v>
+      </c>
+      <c r="K228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" s="2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P228" s="4" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q228"/>
+  <dimension ref="A1:Q237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14289,10 +14289,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C227" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14350,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C228" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
@@ -14401,6 +14397,573 @@
       <c r="Q228" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" s="2" t="n">
+        <v>418.59</v>
+      </c>
+      <c r="J229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="2" t="n">
+        <v>41859</v>
+      </c>
+      <c r="L229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="O229" s="2" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="P229" s="4" t="n">
+        <v>-25.93</v>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G230" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>528.61</v>
+      </c>
+      <c r="I230" s="2" t="n">
+        <v>525.67</v>
+      </c>
+      <c r="J230" s="2" t="n">
+        <v>52861</v>
+      </c>
+      <c r="K230" s="2" t="n">
+        <v>52567</v>
+      </c>
+      <c r="L230" s="4" t="n">
+        <v>-294</v>
+      </c>
+      <c r="M230" s="2" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="O230" s="2" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="P230" s="4" t="n">
+        <v>-330.82</v>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" s="2" t="n">
+        <v>74.9633</v>
+      </c>
+      <c r="J231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="2" t="n">
+        <v>22489</v>
+      </c>
+      <c r="L231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N231" s="2" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="O231" s="2" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="P231" s="4" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G232" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="I232" s="2" t="n">
+        <v>226.38</v>
+      </c>
+      <c r="J232" s="2" t="n">
+        <v>45004</v>
+      </c>
+      <c r="K232" s="2" t="n">
+        <v>45276</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="M232" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="O232" s="2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="P232" s="3" t="n">
+        <v>239.36</v>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G233" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="I233" s="2" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="J233" s="2" t="n">
+        <v>24096</v>
+      </c>
+      <c r="K233" s="2" t="n">
+        <v>24508</v>
+      </c>
+      <c r="L233" s="3" t="n">
+        <v>412</v>
+      </c>
+      <c r="M233" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="O233" s="2" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="P233" s="3" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>1150.28</v>
+      </c>
+      <c r="I234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="2" t="n">
+        <v>115028</v>
+      </c>
+      <c r="K234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" s="2" t="n">
+        <v>11.5028</v>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P234" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" s="2" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O235" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="P235" s="4" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="I236" s="2" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J236" s="2" t="n">
+        <v>30785</v>
+      </c>
+      <c r="K236" s="2" t="n">
+        <v>31050</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="M236" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="O236" s="2" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="P236" s="3" t="n">
+        <v>239.48</v>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G237" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="I237" s="2" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="J237" s="2" t="n">
+        <v>36512</v>
+      </c>
+      <c r="K237" s="2" t="n">
+        <v>36940</v>
+      </c>
+      <c r="L237" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="M237" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="O237" s="2" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="P237" s="3" t="n">
+        <v>399.53</v>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>1.09%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q237"/>
+  <dimension ref="A1:Q253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14411,10 +14411,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C229" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
@@ -14474,10 +14472,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C230" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
@@ -14537,10 +14533,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C231" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
@@ -14600,10 +14594,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C232" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
@@ -14663,10 +14655,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C233" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
@@ -14726,10 +14716,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C234" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
@@ -14789,10 +14777,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C235" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
@@ -14852,10 +14838,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C236" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
@@ -14915,10 +14899,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C237" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
@@ -14964,6 +14946,1014 @@
       <c r="Q237" s="2" t="inlineStr">
         <is>
           <t>1.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>288.6414</v>
+      </c>
+      <c r="I238" s="2" t="n">
+        <v>292.044</v>
+      </c>
+      <c r="J238" s="2" t="n">
+        <v>144320.71</v>
+      </c>
+      <c r="K238" s="2" t="n">
+        <v>146022</v>
+      </c>
+      <c r="L238" s="3" t="n">
+        <v>1701.29</v>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="O238" s="2" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="P238" s="3" t="n">
+        <v>1599.25</v>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>288.6414</v>
+      </c>
+      <c r="I239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="2" t="n">
+        <v>57728.29</v>
+      </c>
+      <c r="K239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="P239" s="4" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="I240" s="2" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="J240" s="2" t="n">
+        <v>12498</v>
+      </c>
+      <c r="K240" s="2" t="n">
+        <v>12816</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="O240" s="2" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="P240" s="3" t="n">
+        <v>301.59</v>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="I241" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="2" t="n">
+        <v>12498</v>
+      </c>
+      <c r="K241" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N241" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P241" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G242" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="I242" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="J242" s="2" t="n">
+        <v>18905</v>
+      </c>
+      <c r="K242" s="2" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L242" s="3" t="n">
+        <v>595</v>
+      </c>
+      <c r="M242" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N242" s="2" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O242" s="2" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="P242" s="3" t="n">
+        <v>575.25</v>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>3.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="2" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="J243" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" s="2" t="n">
+        <v>43660</v>
+      </c>
+      <c r="L243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N243" s="2" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="O243" s="2" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="P243" s="4" t="n">
+        <v>-26.83</v>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I244" s="2" t="n">
+        <v>152.86</v>
+      </c>
+      <c r="J244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" s="2" t="n">
+        <v>15286</v>
+      </c>
+      <c r="L244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="O244" s="2" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="P244" s="4" t="n">
+        <v>-12.64</v>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>519.15</v>
+      </c>
+      <c r="I245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" s="2" t="n">
+        <v>51915</v>
+      </c>
+      <c r="K245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>5.1915</v>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="P245" s="4" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G246" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="I246" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="J246" s="2" t="n">
+        <v>25400</v>
+      </c>
+      <c r="K246" s="2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L246" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O246" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="P246" s="3" t="n">
+        <v>577</v>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G247" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>232.8271</v>
+      </c>
+      <c r="I247" s="2" t="n">
+        <v>235.53</v>
+      </c>
+      <c r="J247" s="2" t="n">
+        <v>69848.14</v>
+      </c>
+      <c r="K247" s="2" t="n">
+        <v>70659</v>
+      </c>
+      <c r="L247" s="3" t="n">
+        <v>810.86</v>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="O247" s="2" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="P247" s="3" t="n">
+        <v>761.48</v>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>232.8271</v>
+      </c>
+      <c r="I248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" s="2" t="n">
+        <v>93130.86</v>
+      </c>
+      <c r="K248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" s="2" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" s="2" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="P248" s="4" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G249" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>1160.19</v>
+      </c>
+      <c r="I249" s="2" t="n">
+        <v>1168.46</v>
+      </c>
+      <c r="J249" s="2" t="n">
+        <v>116019</v>
+      </c>
+      <c r="K249" s="2" t="n">
+        <v>116846</v>
+      </c>
+      <c r="L249" s="3" t="n">
+        <v>827</v>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="N249" s="2" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="O249" s="2" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="P249" s="3" t="n">
+        <v>745.29</v>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" s="2" t="n">
+        <v>5261</v>
+      </c>
+      <c r="K250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P250" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="I251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" s="2" t="n">
+        <v>43385</v>
+      </c>
+      <c r="K251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P251" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>先导智能</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G252" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" s="2" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="J252" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" s="2" t="n">
+        <v>21010</v>
+      </c>
+      <c r="L252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N252" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O252" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="P252" s="4" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="I253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" s="2" t="n">
+        <v>8951</v>
+      </c>
+      <c r="K253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P253" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q253"/>
+  <dimension ref="A1:Q266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14960,10 +14960,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C238" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
@@ -15023,10 +15021,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C239" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
@@ -15086,10 +15082,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C240" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
@@ -15149,10 +15143,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C241" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
@@ -15212,10 +15204,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C242" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
@@ -15275,10 +15265,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C243" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
@@ -15338,10 +15326,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C244" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
@@ -15401,10 +15387,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C245" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
@@ -15464,10 +15448,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C246" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
@@ -15527,10 +15509,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C247" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
@@ -15590,10 +15570,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C248" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
@@ -15653,10 +15631,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C249" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
@@ -15716,10 +15692,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C250" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
@@ -15779,10 +15753,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C251" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
@@ -15842,10 +15814,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>300450</t>
-        </is>
+      <c r="C252" s="2" t="n">
+        <v>300450</v>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
@@ -15905,10 +15875,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C253" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
@@ -15954,6 +15922,825 @@
       <c r="Q253" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F254" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G254" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="I254" s="2" t="n">
+        <v>39.875</v>
+      </c>
+      <c r="J254" s="2" t="n">
+        <v>19735</v>
+      </c>
+      <c r="K254" s="2" t="n">
+        <v>19937.5</v>
+      </c>
+      <c r="L254" s="3" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="M254" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="O254" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="P254" s="3" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" s="2" t="n">
+        <v>39.875</v>
+      </c>
+      <c r="J255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" s="2" t="n">
+        <v>19937.5</v>
+      </c>
+      <c r="L255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N255" s="2" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="O255" s="2" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="P255" s="4" t="n">
+        <v>-14.97</v>
+      </c>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" s="2" t="n">
+        <v>234.23</v>
+      </c>
+      <c r="J256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" s="2" t="n">
+        <v>93692</v>
+      </c>
+      <c r="L256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>9.369200000000001</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="O256" s="2" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="P256" s="4" t="n">
+        <v>-56.22</v>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>002922</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>伊戈尔</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G257" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="I257" s="2" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="J257" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="K257" s="2" t="n">
+        <v>10986</v>
+      </c>
+      <c r="L257" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="M257" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="O257" s="2" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="P257" s="3" t="n">
+        <v>125.51</v>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G258" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>147.87</v>
+      </c>
+      <c r="I258" s="2" t="n">
+        <v>149.21</v>
+      </c>
+      <c r="J258" s="2" t="n">
+        <v>14787</v>
+      </c>
+      <c r="K258" s="2" t="n">
+        <v>14921</v>
+      </c>
+      <c r="L258" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M258" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="O258" s="2" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="P258" s="3" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G259" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="I259" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="J259" s="2" t="n">
+        <v>80420</v>
+      </c>
+      <c r="K259" s="2" t="n">
+        <v>81500</v>
+      </c>
+      <c r="L259" s="3" t="n">
+        <v>1080</v>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="O259" s="2" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="P259" s="3" t="n">
+        <v>1023.06</v>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G260" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>1214.16</v>
+      </c>
+      <c r="I260" s="2" t="n">
+        <v>1219.08</v>
+      </c>
+      <c r="J260" s="2" t="n">
+        <v>121416</v>
+      </c>
+      <c r="K260" s="2" t="n">
+        <v>121908</v>
+      </c>
+      <c r="L260" s="3" t="n">
+        <v>492</v>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="O260" s="2" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="P260" s="3" t="n">
+        <v>406.72</v>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="J261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" s="2" t="n">
+        <v>52500</v>
+      </c>
+      <c r="L261" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O261" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="P261" s="4" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G262" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>295.57</v>
+      </c>
+      <c r="I262" s="2" t="n">
+        <v>292.995</v>
+      </c>
+      <c r="J262" s="2" t="n">
+        <v>59114</v>
+      </c>
+      <c r="K262" s="2" t="n">
+        <v>58599</v>
+      </c>
+      <c r="L262" s="4" t="n">
+        <v>-515</v>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="N262" s="2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="O262" s="2" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="P262" s="4" t="n">
+        <v>-556.0700000000001</v>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>-0.94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G263" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" s="2" t="n">
+        <v>292.995</v>
+      </c>
+      <c r="J263" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" s="2" t="n">
+        <v>58599</v>
+      </c>
+      <c r="L263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="O263" s="2" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="P263" s="4" t="n">
+        <v>-35.16</v>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="I264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="2" t="n">
+        <v>18160</v>
+      </c>
+      <c r="K264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P264" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G265" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" s="2" t="n">
+        <v>98.11499999999999</v>
+      </c>
+      <c r="J265" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" s="2" t="n">
+        <v>19623</v>
+      </c>
+      <c r="L265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="O265" s="2" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="P265" s="4" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" s="2" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="J266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" s="2" t="n">
+        <v>12974</v>
+      </c>
+      <c r="L266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="O266" s="2" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="P266" s="4" t="n">
+        <v>-11.49</v>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q266"/>
+  <dimension ref="A1:Q273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15936,10 +15936,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C254" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
@@ -15999,10 +15997,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C255" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
@@ -16062,10 +16058,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C256" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
@@ -16125,10 +16119,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>002922</t>
-        </is>
+      <c r="C257" s="2" t="n">
+        <v>2922</v>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
@@ -16188,10 +16180,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>300274</t>
-        </is>
+      <c r="C258" s="2" t="n">
+        <v>300274</v>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
@@ -16251,10 +16241,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C259" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
@@ -16314,10 +16302,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C260" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
@@ -16377,10 +16363,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C261" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
@@ -16440,10 +16424,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C262" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
@@ -16503,10 +16485,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C263" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
@@ -16566,10 +16546,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C264" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
@@ -16629,10 +16607,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C265" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
@@ -16692,10 +16668,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C266" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
@@ -16741,6 +16715,447 @@
       <c r="Q266" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G267" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>244.598</v>
+      </c>
+      <c r="I267" s="2" t="n">
+        <v>245.964</v>
+      </c>
+      <c r="J267" s="2" t="n">
+        <v>122299</v>
+      </c>
+      <c r="K267" s="2" t="n">
+        <v>122982</v>
+      </c>
+      <c r="L267" s="3" t="n">
+        <v>683</v>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="O267" s="2" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="P267" s="3" t="n">
+        <v>596.98</v>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G268" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>319.295</v>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>319.05</v>
+      </c>
+      <c r="J268" s="2" t="n">
+        <v>31929.5</v>
+      </c>
+      <c r="K268" s="2" t="n">
+        <v>31905</v>
+      </c>
+      <c r="L268" s="4" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="O268" s="2" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="P268" s="4" t="n">
+        <v>-50.45</v>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>319.295</v>
+      </c>
+      <c r="I269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" s="2" t="n">
+        <v>31929.5</v>
+      </c>
+      <c r="K269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P269" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G270" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>164.56</v>
+      </c>
+      <c r="I270" s="2" t="n">
+        <v>165.62</v>
+      </c>
+      <c r="J270" s="2" t="n">
+        <v>16456</v>
+      </c>
+      <c r="K270" s="2" t="n">
+        <v>16562</v>
+      </c>
+      <c r="L270" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="O270" s="2" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="P270" s="3" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G271" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>1240.3</v>
+      </c>
+      <c r="I271" s="2" t="n">
+        <v>1258.65</v>
+      </c>
+      <c r="J271" s="2" t="n">
+        <v>124030</v>
+      </c>
+      <c r="K271" s="2" t="n">
+        <v>125865</v>
+      </c>
+      <c r="L271" s="3" t="n">
+        <v>1835</v>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="O271" s="2" t="n">
+        <v>87.92</v>
+      </c>
+      <c r="P271" s="3" t="n">
+        <v>1747.08</v>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>1.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G272" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>549.21</v>
+      </c>
+      <c r="I272" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="J272" s="2" t="n">
+        <v>54921</v>
+      </c>
+      <c r="K272" s="2" t="n">
+        <v>55400</v>
+      </c>
+      <c r="L272" s="3" t="n">
+        <v>479</v>
+      </c>
+      <c r="M272" s="2" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="O272" s="2" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="P272" s="3" t="n">
+        <v>440.27</v>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G273" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="I273" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="J273" s="2" t="n">
+        <v>10443</v>
+      </c>
+      <c r="K273" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="L273" s="3" t="n">
+        <v>357</v>
+      </c>
+      <c r="M273" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O273" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="P273" s="3" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>3.27%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q273"/>
+  <dimension ref="A1:Q294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16729,10 +16729,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C267" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
@@ -16792,10 +16790,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C268" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
@@ -16855,10 +16851,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C269" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
@@ -16918,10 +16912,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C270" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
@@ -16981,10 +16973,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C271" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
@@ -17044,10 +17034,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C272" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
@@ -17107,10 +17095,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C273" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
@@ -17156,6 +17142,1329 @@
       <c r="Q273" s="2" t="inlineStr">
         <is>
           <t>3.27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G274" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>549.35</v>
+      </c>
+      <c r="I274" s="2" t="n">
+        <v>554.58</v>
+      </c>
+      <c r="J274" s="2" t="n">
+        <v>54935</v>
+      </c>
+      <c r="K274" s="2" t="n">
+        <v>55458</v>
+      </c>
+      <c r="L274" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="M274" s="2" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="O274" s="2" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="P274" s="3" t="n">
+        <v>484.23</v>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="2" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="J275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" s="2" t="n">
+        <v>19206</v>
+      </c>
+      <c r="L275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O275" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="P275" s="4" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>300516</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>久之洋</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>37.062</v>
+      </c>
+      <c r="I276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" s="2" t="n">
+        <v>18531</v>
+      </c>
+      <c r="K276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P276" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G277" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="I277" s="2" t="n">
+        <v>149.46</v>
+      </c>
+      <c r="J277" s="2" t="n">
+        <v>14830</v>
+      </c>
+      <c r="K277" s="2" t="n">
+        <v>14946</v>
+      </c>
+      <c r="L277" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="M277" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="O277" s="2" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="P277" s="3" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G278" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>256.43</v>
+      </c>
+      <c r="I278" s="2" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="J278" s="2" t="n">
+        <v>51286</v>
+      </c>
+      <c r="K278" s="2" t="n">
+        <v>50660</v>
+      </c>
+      <c r="L278" s="4" t="n">
+        <v>-626</v>
+      </c>
+      <c r="M278" s="2" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="O278" s="2" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="P278" s="4" t="n">
+        <v>-661.52</v>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" s="2" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="J279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" s="2" t="n">
+        <v>50660</v>
+      </c>
+      <c r="L279" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="O279" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="P279" s="4" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>002922</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>伊戈尔</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="2" t="n">
+        <v>22362</v>
+      </c>
+      <c r="K280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P280" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>274.25</v>
+      </c>
+      <c r="I281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" s="2" t="n">
+        <v>27425</v>
+      </c>
+      <c r="K281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P281" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G282" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="I282" s="2" t="n">
+        <v>169.36</v>
+      </c>
+      <c r="J282" s="2" t="n">
+        <v>16810</v>
+      </c>
+      <c r="K282" s="2" t="n">
+        <v>16936</v>
+      </c>
+      <c r="L282" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N282" s="2" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="O282" s="2" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="P282" s="3" t="n">
+        <v>107.53</v>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G283" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="2" t="n">
+        <v>90.17</v>
+      </c>
+      <c r="J283" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" s="2" t="n">
+        <v>18034</v>
+      </c>
+      <c r="L283" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N283" s="2" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="O283" s="2" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="P283" s="4" t="n">
+        <v>-14.02</v>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G284" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>77.66</v>
+      </c>
+      <c r="I284" s="2" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="J284" s="2" t="n">
+        <v>31064</v>
+      </c>
+      <c r="K284" s="2" t="n">
+        <v>31268</v>
+      </c>
+      <c r="L284" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="M284" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="O284" s="2" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="P284" s="3" t="n">
+        <v>178.37</v>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G285" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" s="2" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="J285" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" s="2" t="n">
+        <v>19497</v>
+      </c>
+      <c r="L285" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N285" s="2" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O285" s="2" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="P285" s="4" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="I286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" s="2" t="n">
+        <v>8747</v>
+      </c>
+      <c r="K286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P286" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G287" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>304.405</v>
+      </c>
+      <c r="I287" s="2" t="n">
+        <v>305.985</v>
+      </c>
+      <c r="J287" s="2" t="n">
+        <v>121762</v>
+      </c>
+      <c r="K287" s="2" t="n">
+        <v>122394</v>
+      </c>
+      <c r="L287" s="3" t="n">
+        <v>632</v>
+      </c>
+      <c r="M287" s="2" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O287" s="2" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="P287" s="3" t="n">
+        <v>546.38</v>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G288" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>73.434</v>
+      </c>
+      <c r="I288" s="2" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="J288" s="2" t="n">
+        <v>36717</v>
+      </c>
+      <c r="K288" s="2" t="n">
+        <v>37680</v>
+      </c>
+      <c r="L288" s="3" t="n">
+        <v>963</v>
+      </c>
+      <c r="M288" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N288" s="2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="O288" s="2" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="P288" s="3" t="n">
+        <v>934.16</v>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="I289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" s="2" t="n">
+        <v>8582</v>
+      </c>
+      <c r="K289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P289" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G290" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>322.8</v>
+      </c>
+      <c r="I290" s="2" t="n">
+        <v>327.235</v>
+      </c>
+      <c r="J290" s="2" t="n">
+        <v>32280</v>
+      </c>
+      <c r="K290" s="2" t="n">
+        <v>32723.5</v>
+      </c>
+      <c r="L290" s="3" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="M290" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N290" s="2" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="O290" s="2" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="P290" s="3" t="n">
+        <v>417.14</v>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G291" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" s="2" t="n">
+        <v>327.235</v>
+      </c>
+      <c r="J291" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" s="2" t="n">
+        <v>32723.5</v>
+      </c>
+      <c r="L291" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="O291" s="2" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="P291" s="4" t="n">
+        <v>-21.36</v>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>688676</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>金盘科技</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="I292" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="K292" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N292" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P292" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>中国稀士</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G293" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>59.405</v>
+      </c>
+      <c r="I293" s="2" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="J293" s="2" t="n">
+        <v>11881</v>
+      </c>
+      <c r="K293" s="2" t="n">
+        <v>12190</v>
+      </c>
+      <c r="L293" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="M293" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O293" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="P293" s="3" t="n">
+        <v>292.9</v>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>2.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>中国稀士</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>59.405</v>
+      </c>
+      <c r="I294" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" s="2" t="n">
+        <v>11881</v>
+      </c>
+      <c r="K294" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N294" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P294" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q294"/>
+  <dimension ref="A1:Q315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17156,10 +17156,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C274" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
@@ -17219,10 +17217,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>688503</t>
-        </is>
+      <c r="C275" s="2" t="n">
+        <v>688503</v>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
@@ -17282,10 +17278,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>300516</t>
-        </is>
+      <c r="C276" s="2" t="n">
+        <v>300516</v>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
@@ -17345,10 +17339,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>300274</t>
-        </is>
+      <c r="C277" s="2" t="n">
+        <v>300274</v>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
@@ -17408,10 +17400,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C278" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
@@ -17471,10 +17461,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C279" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
@@ -17534,10 +17522,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>002922</t>
-        </is>
+      <c r="C280" s="2" t="n">
+        <v>2922</v>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
@@ -17597,10 +17583,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C281" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
@@ -17660,10 +17644,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C282" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
@@ -17723,10 +17705,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C283" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
@@ -17786,10 +17766,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C284" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
@@ -17849,10 +17827,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C285" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
@@ -17912,10 +17888,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C286" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
@@ -17975,10 +17949,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C287" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
@@ -18038,10 +18010,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C288" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
@@ -18101,10 +18071,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C289" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
@@ -18164,10 +18132,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C290" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
@@ -18227,10 +18193,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C291" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
@@ -18290,10 +18254,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>688676</t>
-        </is>
+      <c r="C292" s="2" t="n">
+        <v>688676</v>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
@@ -18353,10 +18315,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C293" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
@@ -18416,10 +18376,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C294" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
@@ -18465,6 +18423,1329 @@
       <c r="Q294" s="2" t="inlineStr">
         <is>
           <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F295" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G295" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H295" s="2" t="n">
+        <v>574</v>
+      </c>
+      <c r="I295" s="2" t="n">
+        <v>577.99</v>
+      </c>
+      <c r="J295" s="2" t="n">
+        <v>57400</v>
+      </c>
+      <c r="K295" s="2" t="n">
+        <v>57799</v>
+      </c>
+      <c r="L295" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="M295" s="2" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="N295" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="O295" s="2" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="P295" s="3" t="n">
+        <v>358.58</v>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" s="2" t="n">
+        <v>265.82</v>
+      </c>
+      <c r="I296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" s="2" t="n">
+        <v>53164</v>
+      </c>
+      <c r="K296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="2" t="n">
+        <v>5.316400000000001</v>
+      </c>
+      <c r="N296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="P296" s="4" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>300516</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>久之洋</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="I297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="2" t="n">
+        <v>7268</v>
+      </c>
+      <c r="K297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M297" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P297" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G298" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" s="2" t="n">
+        <v>1344.84</v>
+      </c>
+      <c r="J298" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" s="2" t="n">
+        <v>134484</v>
+      </c>
+      <c r="L298" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" s="2" t="n">
+        <v>13.4484</v>
+      </c>
+      <c r="N298" s="2" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="O298" s="2" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="P298" s="4" t="n">
+        <v>-80.69</v>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G299" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H299" s="2" t="n">
+        <v>330.23</v>
+      </c>
+      <c r="I299" s="2" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="J299" s="2" t="n">
+        <v>132092</v>
+      </c>
+      <c r="K299" s="2" t="n">
+        <v>132664</v>
+      </c>
+      <c r="L299" s="3" t="n">
+        <v>572</v>
+      </c>
+      <c r="M299" s="2" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="N299" s="2" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="O299" s="2" t="n">
+        <v>92.81</v>
+      </c>
+      <c r="P299" s="3" t="n">
+        <v>479.19</v>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G300" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="I300" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="J300" s="2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K300" s="2" t="n">
+        <v>23500</v>
+      </c>
+      <c r="L300" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="M300" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N300" s="2" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="O300" s="2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="P300" s="3" t="n">
+        <v>478.25</v>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G301" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>269.8</v>
+      </c>
+      <c r="I301" s="2" t="n">
+        <v>272.59</v>
+      </c>
+      <c r="J301" s="2" t="n">
+        <v>26980</v>
+      </c>
+      <c r="K301" s="2" t="n">
+        <v>27259</v>
+      </c>
+      <c r="L301" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="M301" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N301" s="2" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="O301" s="2" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="P301" s="3" t="n">
+        <v>255.37</v>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>269.8</v>
+      </c>
+      <c r="I302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" s="2" t="n">
+        <v>26980</v>
+      </c>
+      <c r="K302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P302" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G303" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="I303" s="2" t="n">
+        <v>102.815</v>
+      </c>
+      <c r="J303" s="2" t="n">
+        <v>10159</v>
+      </c>
+      <c r="K303" s="2" t="n">
+        <v>10281.5</v>
+      </c>
+      <c r="L303" s="3" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N303" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="O303" s="2" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="P303" s="3" t="n">
+        <v>107.36</v>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G304" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" s="2" t="n">
+        <v>102.815</v>
+      </c>
+      <c r="J304" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" s="2" t="n">
+        <v>10281.5</v>
+      </c>
+      <c r="L304" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N304" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="O304" s="2" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="P304" s="4" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" s="2" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="J305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" s="2" t="n">
+        <v>18358</v>
+      </c>
+      <c r="L305" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N305" s="2" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="O305" s="2" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="P305" s="4" t="n">
+        <v>-14.18</v>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G306" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H306" s="2" t="n">
+        <v>266.5475</v>
+      </c>
+      <c r="I306" s="2" t="n">
+        <v>268.02</v>
+      </c>
+      <c r="J306" s="2" t="n">
+        <v>159928.5</v>
+      </c>
+      <c r="K306" s="2" t="n">
+        <v>160812</v>
+      </c>
+      <c r="L306" s="3" t="n">
+        <v>883.5</v>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="N306" s="2" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="O306" s="2" t="n">
+        <v>112.48</v>
+      </c>
+      <c r="P306" s="3" t="n">
+        <v>771.02</v>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>266.5475</v>
+      </c>
+      <c r="I307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="2" t="n">
+        <v>53309.5</v>
+      </c>
+      <c r="K307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L307" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="N307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" s="2" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="P307" s="4" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="2" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="J308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" s="2" t="n">
+        <v>37415</v>
+      </c>
+      <c r="L308" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N308" s="2" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="O308" s="2" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="P308" s="4" t="n">
+        <v>-23.71</v>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G309" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H309" s="2" t="n">
+        <v>113.96</v>
+      </c>
+      <c r="I309" s="2" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="J309" s="2" t="n">
+        <v>11396</v>
+      </c>
+      <c r="K309" s="2" t="n">
+        <v>11575</v>
+      </c>
+      <c r="L309" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N309" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="O309" s="2" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="P309" s="3" t="n">
+        <v>163.21</v>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G310" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" s="2" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="J310" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" s="2" t="n">
+        <v>11575</v>
+      </c>
+      <c r="L310" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N310" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="O310" s="2" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="P310" s="4" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" s="2" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="J311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" s="2" t="n">
+        <v>24088</v>
+      </c>
+      <c r="L311" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N311" s="2" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="O311" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="P311" s="4" t="n">
+        <v>-17.04</v>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G312" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="I312" s="2" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>8594</v>
+      </c>
+      <c r="K312" s="2" t="n">
+        <v>8698</v>
+      </c>
+      <c r="L312" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N312" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O312" s="2" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="P312" s="3" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="I313" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" s="2" t="n">
+        <v>12891</v>
+      </c>
+      <c r="K313" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N313" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P313" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G314" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" s="2" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="J314" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" s="2" t="n">
+        <v>12348</v>
+      </c>
+      <c r="L314" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N314" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="O314" s="2" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="P314" s="4" t="n">
+        <v>-11.17</v>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="I315" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" s="2" t="n">
+        <v>7667</v>
+      </c>
+      <c r="K315" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M315" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N315" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P315" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q315"/>
+  <dimension ref="A1:Q327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18437,10 +18437,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C295" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C295" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
@@ -18500,10 +18498,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C296" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
@@ -18563,10 +18559,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>300516</t>
-        </is>
+      <c r="C297" s="2" t="n">
+        <v>300516</v>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
@@ -18626,10 +18620,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C298" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
@@ -18689,10 +18681,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C299" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
@@ -18752,10 +18742,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C300" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
@@ -18815,10 +18803,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C301" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
@@ -18878,10 +18864,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C302" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
@@ -18941,10 +18925,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C303" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
@@ -19004,10 +18986,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C304" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
@@ -19067,10 +19047,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C305" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
@@ -19130,10 +19108,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C306" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
@@ -19193,10 +19169,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C307" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
@@ -19256,10 +19230,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C308" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
@@ -19319,10 +19291,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C309" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
@@ -19382,10 +19352,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C310" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
@@ -19445,10 +19413,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>688778</t>
-        </is>
+      <c r="C311" s="2" t="n">
+        <v>688778</v>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
@@ -19508,10 +19474,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C312" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
@@ -19571,10 +19535,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C313" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
@@ -19634,10 +19596,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C314" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
@@ -19697,10 +19657,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C315" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
@@ -19746,6 +19704,762 @@
       <c r="Q315" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G316" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="I316" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="J316" s="2" t="n">
+        <v>11700</v>
+      </c>
+      <c r="K316" s="2" t="n">
+        <v>11900</v>
+      </c>
+      <c r="L316" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M316" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="O316" s="2" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="P316" s="3" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G317" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H317" s="2" t="n">
+        <v>298.085</v>
+      </c>
+      <c r="I317" s="2" t="n">
+        <v>299.985</v>
+      </c>
+      <c r="J317" s="2" t="n">
+        <v>59617</v>
+      </c>
+      <c r="K317" s="2" t="n">
+        <v>59997</v>
+      </c>
+      <c r="L317" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="M317" s="2" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="N317" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O317" s="2" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="P317" s="3" t="n">
+        <v>338.04</v>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>298.085</v>
+      </c>
+      <c r="I318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" s="2" t="n">
+        <v>59617</v>
+      </c>
+      <c r="K318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="N318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="P318" s="4" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G319" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>62.16</v>
+      </c>
+      <c r="I319" s="2" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="J319" s="2" t="n">
+        <v>12432</v>
+      </c>
+      <c r="K319" s="2" t="n">
+        <v>12682</v>
+      </c>
+      <c r="L319" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="M319" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N319" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="O319" s="2" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="P319" s="3" t="n">
+        <v>233.66</v>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>272.81</v>
+      </c>
+      <c r="I320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="2" t="n">
+        <v>27281</v>
+      </c>
+      <c r="K320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P320" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G321" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="I321" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="J321" s="2" t="n">
+        <v>22725</v>
+      </c>
+      <c r="K321" s="2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L321" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="M321" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N321" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O321" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="P321" s="3" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I322" s="2" t="n">
+        <v>579.11</v>
+      </c>
+      <c r="J322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" s="2" t="n">
+        <v>81075.39999999999</v>
+      </c>
+      <c r="L322" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" s="2" t="n">
+        <v>8.10754</v>
+      </c>
+      <c r="N322" s="2" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="O322" s="2" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="P322" s="4" t="n">
+        <v>-48.65</v>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F323" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G323" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H323" s="2" t="n">
+        <v>274.885</v>
+      </c>
+      <c r="I323" s="2" t="n">
+        <v>280.2633</v>
+      </c>
+      <c r="J323" s="2" t="n">
+        <v>109954</v>
+      </c>
+      <c r="K323" s="2" t="n">
+        <v>112105.33</v>
+      </c>
+      <c r="L323" s="3" t="n">
+        <v>2151.33</v>
+      </c>
+      <c r="M323" s="2" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="N323" s="2" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="O323" s="2" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="P323" s="3" t="n">
+        <v>2073.07</v>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G324" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" s="2" t="n">
+        <v>280.2633</v>
+      </c>
+      <c r="J324" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" s="2" t="n">
+        <v>56052.67</v>
+      </c>
+      <c r="L324" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" s="2" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="N324" s="2" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="O324" s="2" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="P324" s="4" t="n">
+        <v>-33.64</v>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G325" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="I325" s="2" t="n">
+        <v>323.98</v>
+      </c>
+      <c r="J325" s="2" t="n">
+        <v>33333</v>
+      </c>
+      <c r="K325" s="2" t="n">
+        <v>32398</v>
+      </c>
+      <c r="L325" s="4" t="n">
+        <v>-935</v>
+      </c>
+      <c r="M325" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N325" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="O325" s="2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="P325" s="4" t="n">
+        <v>-961.2</v>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>-2.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" s="2" t="n">
+        <v>323.98</v>
+      </c>
+      <c r="J326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" s="2" t="n">
+        <v>12959.2</v>
+      </c>
+      <c r="L326" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N326" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="O326" s="2" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="P326" s="4" t="n">
+        <v>-11.48</v>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G327" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H327" s="2" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="I327" s="2" t="n">
+        <v>329.035</v>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>131000</v>
+      </c>
+      <c r="K327" s="2" t="n">
+        <v>131614</v>
+      </c>
+      <c r="L327" s="3" t="n">
+        <v>614</v>
+      </c>
+      <c r="M327" s="2" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="N327" s="2" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="O327" s="2" t="n">
+        <v>92.06999999999999</v>
+      </c>
+      <c r="P327" s="3" t="n">
+        <v>521.9299999999999</v>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>0.40%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q327"/>
+  <dimension ref="A1:Q333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19718,10 +19718,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C316" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
@@ -19781,10 +19779,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C317" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C317" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
@@ -19844,10 +19840,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C318" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C318" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
@@ -19907,10 +19901,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C319" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C319" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
@@ -19970,10 +19962,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C320" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C320" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
@@ -20033,10 +20023,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C321" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
@@ -20096,10 +20084,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C322" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C322" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
@@ -20159,10 +20145,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C323" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
@@ -20222,10 +20206,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C324" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C324" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
@@ -20285,10 +20267,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C325" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C325" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
@@ -20348,10 +20328,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C326" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C326" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
@@ -20411,10 +20389,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C327" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C327" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
@@ -20460,6 +20436,384 @@
       <c r="Q327" s="2" t="inlineStr">
         <is>
           <t>0.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>1340.04</v>
+      </c>
+      <c r="I328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" s="2" t="n">
+        <v>134004</v>
+      </c>
+      <c r="K328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" s="2" t="n">
+        <v>13.4004</v>
+      </c>
+      <c r="N328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P328" s="4" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G329" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>308.91</v>
+      </c>
+      <c r="I329" s="2" t="n">
+        <v>311.38</v>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>30891</v>
+      </c>
+      <c r="K329" s="2" t="n">
+        <v>31138</v>
+      </c>
+      <c r="L329" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="M329" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="O329" s="2" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P329" s="3" t="n">
+        <v>221.43</v>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>82.97329999999999</v>
+      </c>
+      <c r="I330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>24892</v>
+      </c>
+      <c r="K330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L330" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P330" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="I331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" s="2" t="n">
+        <v>9782</v>
+      </c>
+      <c r="K331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M331" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P331" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>290.51</v>
+      </c>
+      <c r="I332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" s="2" t="n">
+        <v>29051</v>
+      </c>
+      <c r="K332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P332" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="I333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" s="2" t="n">
+        <v>56501</v>
+      </c>
+      <c r="K333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L333" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" s="2" t="n">
+        <v>5.6501</v>
+      </c>
+      <c r="N333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="P333" s="4" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q333"/>
+  <dimension ref="A1:Q338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20450,10 +20450,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C328" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
@@ -20513,10 +20511,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C329" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
@@ -20576,10 +20572,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C330" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C330" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
@@ -20639,10 +20633,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C331" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C331" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
@@ -20702,10 +20694,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C332" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
@@ -20765,10 +20755,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C333" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C333" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
@@ -20814,6 +20802,321 @@
       <c r="Q333" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" s="2" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="J334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" s="2" t="n">
+        <v>4702</v>
+      </c>
+      <c r="L334" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N334" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O334" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="P334" s="4" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="I335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>7221</v>
+      </c>
+      <c r="K335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P335" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>300516</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>久之洋</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="G336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" s="2" t="n">
+        <v>33.2329</v>
+      </c>
+      <c r="J336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" s="2" t="n">
+        <v>23263</v>
+      </c>
+      <c r="L336" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M336" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="O336" s="2" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="P336" s="4" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F337" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G337" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H337" s="2" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="I337" s="2" t="n">
+        <v>72.435</v>
+      </c>
+      <c r="J337" s="2" t="n">
+        <v>14244</v>
+      </c>
+      <c r="K337" s="2" t="n">
+        <v>14487</v>
+      </c>
+      <c r="L337" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="M337" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N337" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="O337" s="2" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="P337" s="3" t="n">
+        <v>225.76</v>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G338" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" s="2" t="n">
+        <v>72.435</v>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" s="2" t="n">
+        <v>14487</v>
+      </c>
+      <c r="L338" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M338" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N338" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="O338" s="2" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="P338" s="4" t="n">
+        <v>-12.24</v>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q338"/>
+  <dimension ref="A1:Q345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20813,7 +20813,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>平安账户</t>
+          <t>平安账户+手机账户</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -20876,58 +20876,58 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>平安账户</t>
+          <t>平安账户+手机账户</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F335" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G335" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H335" s="2" t="n">
-        <v>72.20999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>0</v>
+        <v>84.48</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>7221</v>
+        <v>16420</v>
       </c>
       <c r="K335" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L335" s="4" t="n">
-        <v>0</v>
+        <v>16896</v>
+      </c>
+      <c r="L335" s="3" t="n">
+        <v>476</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N335" s="2" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P335" s="4" t="n">
-        <v>-5</v>
+        <v>18.45</v>
+      </c>
+      <c r="P335" s="3" t="n">
+        <v>457.55</v>
       </c>
       <c r="Q335" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -20939,58 +20939,58 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>平安账户</t>
+          <t>平安账户+手机账户</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>300516</t>
+          <t>300548</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>久之洋</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F336" s="2" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="G336" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H336" s="2" t="n">
-        <v>0</v>
+        <v>285.01</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>33.2329</v>
+        <v>295.83</v>
       </c>
       <c r="J336" s="2" t="n">
-        <v>0</v>
+        <v>28501</v>
       </c>
       <c r="K336" s="2" t="n">
-        <v>23263</v>
-      </c>
-      <c r="L336" s="4" t="n">
-        <v>0</v>
+        <v>29583</v>
+      </c>
+      <c r="L336" s="3" t="n">
+        <v>1082</v>
       </c>
       <c r="M336" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N336" s="2" t="n">
-        <v>11.63</v>
+        <v>14.79</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="P336" s="4" t="n">
-        <v>-16.63</v>
+        <v>24.79</v>
+      </c>
+      <c r="P336" s="3" t="n">
+        <v>1057.21</v>
       </c>
       <c r="Q336" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅卖出未平仓</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -21002,58 +21002,58 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>平安账户</t>
+          <t>平安账户+手机账户</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300548</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F337" s="2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G337" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H337" s="2" t="n">
-        <v>71.22</v>
+        <v>285.01</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>72.435</v>
+        <v>0</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>14244</v>
+        <v>28501</v>
       </c>
       <c r="K337" s="2" t="n">
-        <v>14487</v>
-      </c>
-      <c r="L337" s="3" t="n">
-        <v>243</v>
+        <v>0</v>
+      </c>
+      <c r="L337" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M337" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N337" s="2" t="n">
-        <v>7.24</v>
+        <v>0</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="P337" s="3" t="n">
-        <v>225.76</v>
+        <v>5</v>
+      </c>
+      <c r="P337" s="4" t="n">
+        <v>-5</v>
       </c>
       <c r="Q337" s="2" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>
@@ -21065,24 +21065,24 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>平安账户</t>
+          <t>平安账户+手机账户</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>300516</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>久之洋</t>
         </is>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F338" s="2" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="G338" s="2" t="n">
         <v>0</v>
@@ -21091,13 +21091,13 @@
         <v>0</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>72.435</v>
+        <v>33.2329</v>
       </c>
       <c r="J338" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K338" s="2" t="n">
-        <v>14487</v>
+        <v>23263</v>
       </c>
       <c r="L338" s="4" t="n">
         <v>0</v>
@@ -21106,17 +21106,458 @@
         <v>5</v>
       </c>
       <c r="N338" s="2" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="O338" s="2" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="P338" s="4" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="I339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>7221</v>
+      </c>
+      <c r="K339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L339" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M339" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P339" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>308.62</v>
+      </c>
+      <c r="I340" s="2" t="n">
+        <v>312.99</v>
+      </c>
+      <c r="J340" s="2" t="n">
+        <v>30862</v>
+      </c>
+      <c r="K340" s="2" t="n">
+        <v>31299</v>
+      </c>
+      <c r="L340" s="3" t="n">
+        <v>437</v>
+      </c>
+      <c r="M340" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="O340" s="2" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="P340" s="3" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G341" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>1310.01</v>
+      </c>
+      <c r="I341" s="2" t="n">
+        <v>1320.57</v>
+      </c>
+      <c r="J341" s="2" t="n">
+        <v>131001</v>
+      </c>
+      <c r="K341" s="2" t="n">
+        <v>132057</v>
+      </c>
+      <c r="L341" s="3" t="n">
+        <v>1056</v>
+      </c>
+      <c r="M341" s="2" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="N341" s="2" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="O341" s="2" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="P341" s="3" t="n">
+        <v>963.66</v>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G342" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="I342" s="2" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="J342" s="2" t="n">
+        <v>4961</v>
+      </c>
+      <c r="K342" s="2" t="n">
+        <v>5007</v>
+      </c>
+      <c r="L342" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M342" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N342" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O342" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P342" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G343" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="I343" s="2" t="n">
+        <v>72.435</v>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>14244</v>
+      </c>
+      <c r="K343" s="2" t="n">
+        <v>14487</v>
+      </c>
+      <c r="L343" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="M343" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N343" s="2" t="n">
         <v>7.24</v>
       </c>
-      <c r="O338" s="2" t="n">
+      <c r="O343" s="2" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="P343" s="3" t="n">
+        <v>225.76</v>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" s="2" t="n">
+        <v>72.435</v>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" s="2" t="n">
+        <v>14487</v>
+      </c>
+      <c r="L344" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M344" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N344" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="O344" s="2" t="n">
         <v>12.24</v>
       </c>
-      <c r="P338" s="4" t="n">
+      <c r="P344" s="4" t="n">
         <v>-12.24</v>
       </c>
-      <c r="Q338" s="2" t="inlineStr">
+      <c r="Q344" s="2" t="inlineStr">
         <is>
           <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>562.04</v>
+      </c>
+      <c r="I345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" s="2" t="n">
+        <v>56204</v>
+      </c>
+      <c r="K345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L345" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M345" s="2" t="n">
+        <v>5.6204</v>
+      </c>
+      <c r="N345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O345" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="P345" s="4" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q345"/>
+  <dimension ref="A1:Q361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20816,10 +20816,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C334" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C334" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
@@ -20879,10 +20877,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C335" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C335" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
@@ -20942,10 +20938,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C336" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C336" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
@@ -21005,10 +20999,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C337" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C337" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
@@ -21068,10 +21060,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C338" s="2" t="inlineStr">
-        <is>
-          <t>300516</t>
-        </is>
+      <c r="C338" s="2" t="n">
+        <v>300516</v>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
@@ -21131,10 +21121,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C339" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C339" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
@@ -21194,10 +21182,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C340" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C340" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
@@ -21257,10 +21243,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C341" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C341" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
@@ -21320,10 +21304,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C342" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C342" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
@@ -21383,10 +21365,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C343" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C343" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
@@ -21446,10 +21426,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C344" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C344" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
@@ -21509,10 +21487,8 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C345" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C345" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
@@ -21558,6 +21534,1014 @@
       <c r="Q345" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G346" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H346" s="2" t="n">
+        <v>270.095</v>
+      </c>
+      <c r="I346" s="2" t="n">
+        <v>273.8233</v>
+      </c>
+      <c r="J346" s="2" t="n">
+        <v>54019</v>
+      </c>
+      <c r="K346" s="2" t="n">
+        <v>54764.67</v>
+      </c>
+      <c r="L346" s="3" t="n">
+        <v>745.67</v>
+      </c>
+      <c r="M346" s="2" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="O346" s="2" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="P346" s="3" t="n">
+        <v>707.41</v>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I347" s="2" t="n">
+        <v>273.8233</v>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K347" s="2" t="n">
+        <v>27382.33</v>
+      </c>
+      <c r="L347" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N347" s="2" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="O347" s="2" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="P347" s="4" t="n">
+        <v>-18.69</v>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" s="2" t="n">
+        <v>401.65</v>
+      </c>
+      <c r="J348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" s="2" t="n">
+        <v>40165</v>
+      </c>
+      <c r="L348" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M348" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N348" s="2" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="O348" s="2" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="P348" s="4" t="n">
+        <v>-25.08</v>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" s="2" t="n">
+        <v>95.91</v>
+      </c>
+      <c r="J349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" s="2" t="n">
+        <v>9591</v>
+      </c>
+      <c r="L349" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O349" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P349" s="4" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G350" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="I350" s="2" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>10728</v>
+      </c>
+      <c r="K350" s="2" t="n">
+        <v>10644</v>
+      </c>
+      <c r="L350" s="4" t="n">
+        <v>-84</v>
+      </c>
+      <c r="M350" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N350" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="O350" s="2" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="P350" s="4" t="n">
+        <v>-99.31999999999999</v>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G351" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H351" s="2" t="n">
+        <v>352.2475</v>
+      </c>
+      <c r="I351" s="2" t="n">
+        <v>352.605</v>
+      </c>
+      <c r="J351" s="2" t="n">
+        <v>281798</v>
+      </c>
+      <c r="K351" s="2" t="n">
+        <v>282084</v>
+      </c>
+      <c r="L351" s="3" t="n">
+        <v>286</v>
+      </c>
+      <c r="M351" s="2" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="O351" s="2" t="n">
+        <v>197.43</v>
+      </c>
+      <c r="P351" s="3" t="n">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G352" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H352" s="2" t="n">
+        <v>587.35</v>
+      </c>
+      <c r="I352" s="2" t="n">
+        <v>594.835</v>
+      </c>
+      <c r="J352" s="2" t="n">
+        <v>58735</v>
+      </c>
+      <c r="K352" s="2" t="n">
+        <v>59483.5</v>
+      </c>
+      <c r="L352" s="3" t="n">
+        <v>748.5</v>
+      </c>
+      <c r="M352" s="2" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="N352" s="2" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="P352" s="3" t="n">
+        <v>706.9400000000001</v>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I353" s="2" t="n">
+        <v>594.835</v>
+      </c>
+      <c r="J353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" s="2" t="n">
+        <v>59483.5</v>
+      </c>
+      <c r="L353" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M353" s="2" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="N353" s="2" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="O353" s="2" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="P353" s="4" t="n">
+        <v>-35.69</v>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G354" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>280.385</v>
+      </c>
+      <c r="I354" s="2" t="n">
+        <v>283.77</v>
+      </c>
+      <c r="J354" s="2" t="n">
+        <v>56077</v>
+      </c>
+      <c r="K354" s="2" t="n">
+        <v>56754</v>
+      </c>
+      <c r="L354" s="3" t="n">
+        <v>677</v>
+      </c>
+      <c r="M354" s="2" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="N354" s="2" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="O354" s="2" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="P354" s="3" t="n">
+        <v>637.34</v>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>002922</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>伊戈尔</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" s="2" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="J355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" s="2" t="n">
+        <v>20244</v>
+      </c>
+      <c r="L355" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M355" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N355" s="2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="O355" s="2" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="P355" s="4" t="n">
+        <v>-15.12</v>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G356" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>104.99</v>
+      </c>
+      <c r="I356" s="2" t="n">
+        <v>106.26</v>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>10499</v>
+      </c>
+      <c r="K356" s="2" t="n">
+        <v>10626</v>
+      </c>
+      <c r="L356" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="M356" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N356" s="2" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="O356" s="2" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="P356" s="3" t="n">
+        <v>111.69</v>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G357" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>276.41</v>
+      </c>
+      <c r="I357" s="2" t="n">
+        <v>278.88</v>
+      </c>
+      <c r="J357" s="2" t="n">
+        <v>55282</v>
+      </c>
+      <c r="K357" s="2" t="n">
+        <v>55776</v>
+      </c>
+      <c r="L357" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="N357" s="2" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="O357" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="P357" s="3" t="n">
+        <v>455</v>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" s="2" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="J358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" s="2" t="n">
+        <v>13860</v>
+      </c>
+      <c r="L358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="O358" s="2" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="P358" s="4" t="n">
+        <v>-11.93</v>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I359" s="2" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" s="2" t="n">
+        <v>10428</v>
+      </c>
+      <c r="L359" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N359" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="O359" s="2" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="P359" s="4" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G360" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>1318.05</v>
+      </c>
+      <c r="I360" s="2" t="n">
+        <v>1331.86</v>
+      </c>
+      <c r="J360" s="2" t="n">
+        <v>131805</v>
+      </c>
+      <c r="K360" s="2" t="n">
+        <v>133186</v>
+      </c>
+      <c r="L360" s="3" t="n">
+        <v>1381</v>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N360" s="2" t="n">
+        <v>66.59</v>
+      </c>
+      <c r="O360" s="2" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="P360" s="3" t="n">
+        <v>1287.91</v>
+      </c>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I361" s="2" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="J361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" s="2" t="n">
+        <v>8472</v>
+      </c>
+      <c r="L361" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N361" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="O361" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="P361" s="4" t="n">
+        <v>-9.24</v>
+      </c>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q361"/>
+  <dimension ref="A1:Q364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4253,7 +4253,7 @@
       <c r="K62" s="2" t="n">
         <v>10002</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="L62" s="4" t="n">
         <v>5</v>
       </c>
       <c r="M62" s="2" t="n">
@@ -21548,10 +21548,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C346" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C346" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
@@ -21611,10 +21609,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C347" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C347" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
@@ -21674,10 +21670,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C348" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C348" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
@@ -21737,10 +21731,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C349" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C349" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
@@ -21800,10 +21792,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C350" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C350" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
@@ -21863,10 +21853,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C351" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C351" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
@@ -21926,10 +21914,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C352" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C352" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
@@ -21989,10 +21975,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C353" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C353" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
@@ -22052,10 +22036,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C354" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C354" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
@@ -22115,10 +22097,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C355" s="2" t="inlineStr">
-        <is>
-          <t>002922</t>
-        </is>
+      <c r="C355" s="2" t="n">
+        <v>2922</v>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
@@ -22178,10 +22158,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C356" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C356" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
@@ -22241,10 +22219,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C357" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C357" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
@@ -22304,10 +22280,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C358" s="2" t="inlineStr">
-        <is>
-          <t>688062</t>
-        </is>
+      <c r="C358" s="2" t="n">
+        <v>688062</v>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
@@ -22367,10 +22341,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C359" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C359" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
@@ -22430,10 +22402,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C360" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C360" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
@@ -22493,10 +22463,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C361" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C361" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
@@ -22542,6 +22510,195 @@
       <c r="Q361" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F362" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" s="2" t="n">
+        <v>580.7</v>
+      </c>
+      <c r="I362" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" s="2" t="n">
+        <v>58070</v>
+      </c>
+      <c r="K362" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="N362" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="P362" s="4" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G363" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="I363" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>32917</v>
+      </c>
+      <c r="K363" s="2" t="n">
+        <v>31800</v>
+      </c>
+      <c r="L363" s="4" t="n">
+        <v>-1117</v>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N363" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="O363" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="P363" s="4" t="n">
+        <v>-1142.9</v>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>-3.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>手机账户</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>1280.84</v>
+      </c>
+      <c r="I364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" s="2" t="n">
+        <v>128084</v>
+      </c>
+      <c r="K364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" s="2" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="P364" s="4" t="n">
+        <v>-12.81</v>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q364"/>
+  <dimension ref="A1:Q373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4253,7 +4253,7 @@
       <c r="K62" s="2" t="n">
         <v>10002</v>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="L62" s="3" t="n">
         <v>5</v>
       </c>
       <c r="M62" s="2" t="n">
@@ -22524,10 +22524,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C362" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C362" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
@@ -22587,10 +22585,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C363" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C363" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
@@ -22650,10 +22646,8 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C364" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C364" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
@@ -22699,6 +22693,573 @@
       <c r="Q364" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>300660</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>江苏雷利</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" s="2" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="J365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" s="2" t="n">
+        <v>12655</v>
+      </c>
+      <c r="L365" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N365" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="O365" s="2" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="P365" s="4" t="n">
+        <v>-11.33</v>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F366" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G366" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H366" s="2" t="n">
+        <v>389.23</v>
+      </c>
+      <c r="I366" s="2" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="J366" s="2" t="n">
+        <v>38923</v>
+      </c>
+      <c r="K366" s="2" t="n">
+        <v>39134</v>
+      </c>
+      <c r="L366" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="O366" s="2" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="P366" s="3" t="n">
+        <v>181.43</v>
+      </c>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G367" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>56.3867</v>
+      </c>
+      <c r="I367" s="2" t="n">
+        <v>58.57</v>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>16916</v>
+      </c>
+      <c r="K367" s="2" t="n">
+        <v>17571</v>
+      </c>
+      <c r="L367" s="3" t="n">
+        <v>655</v>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N367" s="2" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="O367" s="2" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="P367" s="3" t="n">
+        <v>636.21</v>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G368" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>286.155</v>
+      </c>
+      <c r="I368" s="2" t="n">
+        <v>286.705</v>
+      </c>
+      <c r="J368" s="2" t="n">
+        <v>114462</v>
+      </c>
+      <c r="K368" s="2" t="n">
+        <v>114682</v>
+      </c>
+      <c r="L368" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="N368" s="2" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="O368" s="2" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="P368" s="3" t="n">
+        <v>139.75</v>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I369" s="2" t="n">
+        <v>286.705</v>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" s="2" t="n">
+        <v>114682</v>
+      </c>
+      <c r="L369" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N369" s="2" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="O369" s="2" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="P369" s="4" t="n">
+        <v>-68.81</v>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G370" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="I370" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>19068</v>
+      </c>
+      <c r="K370" s="2" t="n">
+        <v>19400</v>
+      </c>
+      <c r="L370" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N370" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O370" s="2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P370" s="3" t="n">
+        <v>312.3</v>
+      </c>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" s="2" t="n">
+        <v>9630</v>
+      </c>
+      <c r="K371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L371" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O371" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P371" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G372" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>346.59</v>
+      </c>
+      <c r="I372" s="2" t="n">
+        <v>351.14</v>
+      </c>
+      <c r="J372" s="2" t="n">
+        <v>69318</v>
+      </c>
+      <c r="K372" s="2" t="n">
+        <v>70228</v>
+      </c>
+      <c r="L372" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="O372" s="2" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="P372" s="3" t="n">
+        <v>860.9400000000001</v>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I373" s="2" t="n">
+        <v>351.14</v>
+      </c>
+      <c r="J373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" s="2" t="n">
+        <v>70228</v>
+      </c>
+      <c r="L373" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="O373" s="2" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="P373" s="4" t="n">
+        <v>-42.13</v>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q373"/>
+  <dimension ref="A1:Q380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22707,10 +22707,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C365" s="2" t="inlineStr">
-        <is>
-          <t>300660</t>
-        </is>
+      <c r="C365" s="2" t="n">
+        <v>300660</v>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
@@ -22770,10 +22768,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C366" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C366" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
@@ -22833,10 +22829,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C367" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C367" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22890,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C368" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C368" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
@@ -22959,10 +22951,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C369" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C369" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
@@ -23022,10 +23012,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C370" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C370" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
@@ -23085,10 +23073,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C371" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C371" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
@@ -23148,10 +23134,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C372" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C372" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
@@ -23211,10 +23195,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C373" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C373" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
@@ -23260,6 +23242,447 @@
       <c r="Q373" s="2" t="inlineStr">
         <is>
           <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G374" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>305.1</v>
+      </c>
+      <c r="I374" s="2" t="n">
+        <v>305.82</v>
+      </c>
+      <c r="J374" s="2" t="n">
+        <v>61020</v>
+      </c>
+      <c r="K374" s="2" t="n">
+        <v>61164</v>
+      </c>
+      <c r="L374" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="N374" s="2" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="O374" s="2" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="P374" s="3" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="I375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" s="2" t="n">
+        <v>7084</v>
+      </c>
+      <c r="K375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L375" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P375" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F376" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G376" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H376" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="I376" s="2" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="J376" s="2" t="n">
+        <v>7114</v>
+      </c>
+      <c r="K376" s="2" t="n">
+        <v>7299</v>
+      </c>
+      <c r="L376" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N376" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O376" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="P376" s="3" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I377" s="2" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="J377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" s="2" t="n">
+        <v>26910</v>
+      </c>
+      <c r="L377" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O377" s="2" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="P377" s="4" t="n">
+        <v>-18.46</v>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I378" s="2" t="n">
+        <v>594.405</v>
+      </c>
+      <c r="J378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" s="2" t="n">
+        <v>118881</v>
+      </c>
+      <c r="L378" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>11.8881</v>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="O378" s="2" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="P378" s="4" t="n">
+        <v>-71.33</v>
+      </c>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" s="2" t="n">
+        <v>158.75</v>
+      </c>
+      <c r="J379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" s="2" t="n">
+        <v>31750</v>
+      </c>
+      <c r="L379" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="O379" s="2" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="P379" s="4" t="n">
+        <v>-20.88</v>
+      </c>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(平安账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F380" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G380" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>183.79</v>
+      </c>
+      <c r="I380" s="2" t="n">
+        <v>184.99</v>
+      </c>
+      <c r="J380" s="2" t="n">
+        <v>55137</v>
+      </c>
+      <c r="K380" s="2" t="n">
+        <v>55497</v>
+      </c>
+      <c r="L380" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="O380" s="2" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="P380" s="3" t="n">
+        <v>321.19</v>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>0.58%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q380"/>
+  <dimension ref="A1:Q385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23256,10 +23256,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C374" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C374" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
@@ -23319,10 +23317,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C375" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C375" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
@@ -23382,10 +23378,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C376" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C376" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
@@ -23445,10 +23439,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C377" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C377" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
@@ -23508,10 +23500,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C378" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C378" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
@@ -23571,10 +23561,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C379" s="2" t="inlineStr">
-        <is>
-          <t>300274</t>
-        </is>
+      <c r="C379" s="2" t="n">
+        <v>300274</v>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
@@ -23634,10 +23622,8 @@
           <t>跨账户(平安账户+手机账户)</t>
         </is>
       </c>
-      <c r="C380" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C380" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
@@ -23683,6 +23669,321 @@
       <c r="Q380" s="2" t="inlineStr">
         <is>
           <t>0.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G381" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>306.33</v>
+      </c>
+      <c r="I381" s="2" t="n">
+        <v>308.6267</v>
+      </c>
+      <c r="J381" s="2" t="n">
+        <v>183798</v>
+      </c>
+      <c r="K381" s="2" t="n">
+        <v>185176</v>
+      </c>
+      <c r="L381" s="3" t="n">
+        <v>1378</v>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="O381" s="2" t="n">
+        <v>129.49</v>
+      </c>
+      <c r="P381" s="3" t="n">
+        <v>1248.51</v>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G382" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>1304.11</v>
+      </c>
+      <c r="I382" s="2" t="n">
+        <v>1311.97</v>
+      </c>
+      <c r="J382" s="2" t="n">
+        <v>130411</v>
+      </c>
+      <c r="K382" s="2" t="n">
+        <v>131197</v>
+      </c>
+      <c r="L382" s="3" t="n">
+        <v>786</v>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="O382" s="2" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="P382" s="3" t="n">
+        <v>694.24</v>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F383" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="G383" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>364.9925</v>
+      </c>
+      <c r="I383" s="2" t="n">
+        <v>368.7544</v>
+      </c>
+      <c r="J383" s="2" t="n">
+        <v>328493.25</v>
+      </c>
+      <c r="K383" s="2" t="n">
+        <v>331879</v>
+      </c>
+      <c r="L383" s="3" t="n">
+        <v>3385.75</v>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>165.94</v>
+      </c>
+      <c r="O383" s="2" t="n">
+        <v>231.98</v>
+      </c>
+      <c r="P383" s="3" t="n">
+        <v>3153.77</v>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>364.9925</v>
+      </c>
+      <c r="I384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" s="2" t="n">
+        <v>109497.75</v>
+      </c>
+      <c r="K384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L384" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="P384" s="4" t="n">
+        <v>-10.95</v>
+      </c>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>602</v>
+      </c>
+      <c r="I385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" s="2" t="n">
+        <v>60200</v>
+      </c>
+      <c r="K385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L385" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="P385" s="4" t="n">
+        <v>-6.02</v>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q385"/>
+  <dimension ref="A1:Q389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23683,10 +23683,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C381" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C381" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
@@ -23746,10 +23744,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C382" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C382" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
@@ -23809,10 +23805,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C383" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C383" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
@@ -23872,10 +23866,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C384" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C384" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
@@ -23935,10 +23927,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C385" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C385" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
@@ -23984,6 +23974,258 @@
       <c r="Q385" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G386" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>281.1457</v>
+      </c>
+      <c r="I386" s="2" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="J386" s="2" t="n">
+        <v>140572.86</v>
+      </c>
+      <c r="K386" s="2" t="n">
+        <v>146475</v>
+      </c>
+      <c r="L386" s="3" t="n">
+        <v>5902.14</v>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="O386" s="2" t="n">
+        <v>101.94</v>
+      </c>
+      <c r="P386" s="3" t="n">
+        <v>5800.2</v>
+      </c>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" s="2" t="n">
+        <v>281.1457</v>
+      </c>
+      <c r="I387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" s="2" t="n">
+        <v>56229.14</v>
+      </c>
+      <c r="K387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="P387" s="4" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="I388" s="2" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="J388" s="2" t="n">
+        <v>167905</v>
+      </c>
+      <c r="K388" s="2" t="n">
+        <v>169760</v>
+      </c>
+      <c r="L388" s="3" t="n">
+        <v>1855</v>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="O388" s="2" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="P388" s="3" t="n">
+        <v>1736.35</v>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="I389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" s="2" t="n">
+        <v>235067</v>
+      </c>
+      <c r="K389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L389" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" s="2" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="P389" s="4" t="n">
+        <v>-23.51</v>
+      </c>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q389"/>
+  <dimension ref="A1:Q394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23988,10 +23988,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C386" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C386" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
@@ -24051,10 +24049,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C387" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C387" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
@@ -24114,10 +24110,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C388" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C388" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
@@ -24177,10 +24171,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C389" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C389" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
@@ -24224,6 +24216,321 @@
         <v>-23.51</v>
       </c>
       <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F390" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G390" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="I390" s="2" t="n">
+        <v>510.99</v>
+      </c>
+      <c r="J390" s="2" t="n">
+        <v>50700</v>
+      </c>
+      <c r="K390" s="2" t="n">
+        <v>51099</v>
+      </c>
+      <c r="L390" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="O390" s="2" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="P390" s="3" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G391" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>337.4433</v>
+      </c>
+      <c r="I391" s="2" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="J391" s="2" t="n">
+        <v>202466</v>
+      </c>
+      <c r="K391" s="2" t="n">
+        <v>204144</v>
+      </c>
+      <c r="L391" s="3" t="n">
+        <v>1678</v>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>102.07</v>
+      </c>
+      <c r="O391" s="2" t="n">
+        <v>142.73</v>
+      </c>
+      <c r="P391" s="3" t="n">
+        <v>1535.27</v>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I392" s="2" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="J392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K392" s="2" t="n">
+        <v>68048</v>
+      </c>
+      <c r="L392" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="O392" s="2" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="P392" s="4" t="n">
+        <v>-40.82</v>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>265.2125</v>
+      </c>
+      <c r="I393" s="2" t="n">
+        <v>267.6567</v>
+      </c>
+      <c r="J393" s="2" t="n">
+        <v>159127.5</v>
+      </c>
+      <c r="K393" s="2" t="n">
+        <v>160594</v>
+      </c>
+      <c r="L393" s="3" t="n">
+        <v>1466.5</v>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="O393" s="2" t="n">
+        <v>112.27</v>
+      </c>
+      <c r="P393" s="3" t="n">
+        <v>1354.23</v>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>265.2125</v>
+      </c>
+      <c r="I394" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" s="2" t="n">
+        <v>53042.5</v>
+      </c>
+      <c r="K394" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P394" s="4" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
         <is>
           <t>⚠️多买未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q394"/>
+  <dimension ref="A1:Q397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24232,10 +24232,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C390" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C390" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
@@ -24295,10 +24293,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C391" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C391" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
@@ -24358,10 +24354,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C392" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C392" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
@@ -24421,10 +24415,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C393" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C393" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
@@ -24484,10 +24476,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C394" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C394" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
@@ -24533,6 +24523,195 @@
       <c r="Q394" s="2" t="inlineStr">
         <is>
           <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G395" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>509.04</v>
+      </c>
+      <c r="I395" s="2" t="n">
+        <v>511.94</v>
+      </c>
+      <c r="J395" s="2" t="n">
+        <v>50904</v>
+      </c>
+      <c r="K395" s="2" t="n">
+        <v>51194</v>
+      </c>
+      <c r="L395" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="M395" s="2" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O395" s="2" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="P395" s="3" t="n">
+        <v>254.19</v>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>253.93</v>
+      </c>
+      <c r="I396" s="2" t="n">
+        <v>255.14</v>
+      </c>
+      <c r="J396" s="2" t="n">
+        <v>50786</v>
+      </c>
+      <c r="K396" s="2" t="n">
+        <v>51028</v>
+      </c>
+      <c r="L396" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="M396" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="O396" s="2" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="P396" s="3" t="n">
+        <v>206.31</v>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>349.175</v>
+      </c>
+      <c r="I397" s="2" t="n">
+        <v>352.295</v>
+      </c>
+      <c r="J397" s="2" t="n">
+        <v>139670</v>
+      </c>
+      <c r="K397" s="2" t="n">
+        <v>140918</v>
+      </c>
+      <c r="L397" s="3" t="n">
+        <v>1248</v>
+      </c>
+      <c r="M397" s="2" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="N397" s="2" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="O397" s="2" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="P397" s="3" t="n">
+        <v>1149.48</v>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>0.82%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q397"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24537,10 +24537,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C395" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C395" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
@@ -24600,10 +24598,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C396" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
@@ -24663,10 +24659,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C397" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C397" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
@@ -24712,6 +24706,258 @@
       <c r="Q397" s="2" t="inlineStr">
         <is>
           <t>0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>251.135</v>
+      </c>
+      <c r="I398" s="2" t="n">
+        <v>252.435</v>
+      </c>
+      <c r="J398" s="2" t="n">
+        <v>100454</v>
+      </c>
+      <c r="K398" s="2" t="n">
+        <v>100974</v>
+      </c>
+      <c r="L398" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="M398" s="2" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="O398" s="2" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="P398" s="3" t="n">
+        <v>449.37</v>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G399" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H399" s="2" t="n">
+        <v>345.5621</v>
+      </c>
+      <c r="I399" s="2" t="n">
+        <v>349.0878</v>
+      </c>
+      <c r="J399" s="2" t="n">
+        <v>483786.96</v>
+      </c>
+      <c r="K399" s="2" t="n">
+        <v>488722.89</v>
+      </c>
+      <c r="L399" s="3" t="n">
+        <v>4935.93</v>
+      </c>
+      <c r="M399" s="2" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="N399" s="2" t="n">
+        <v>244.36</v>
+      </c>
+      <c r="O399" s="2" t="n">
+        <v>341.61</v>
+      </c>
+      <c r="P399" s="3" t="n">
+        <v>4594.32</v>
+      </c>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I400" s="2" t="n">
+        <v>349.0878</v>
+      </c>
+      <c r="J400" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K400" s="2" t="n">
+        <v>139635.11</v>
+      </c>
+      <c r="L400" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M400" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="O400" s="2" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="P400" s="4" t="n">
+        <v>-83.78</v>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>244.24</v>
+      </c>
+      <c r="I401" s="2" t="n">
+        <v>248.98</v>
+      </c>
+      <c r="J401" s="2" t="n">
+        <v>24424</v>
+      </c>
+      <c r="K401" s="2" t="n">
+        <v>24898</v>
+      </c>
+      <c r="L401" s="3" t="n">
+        <v>474</v>
+      </c>
+      <c r="M401" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="O401" s="2" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="P401" s="3" t="n">
+        <v>451.55</v>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>1.85%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q401"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24720,10 +24720,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C398" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C398" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
@@ -24783,10 +24781,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C399" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C399" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
@@ -24846,10 +24842,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C400" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C400" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
@@ -24909,10 +24903,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C401" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C401" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
@@ -24958,6 +24950,384 @@
       <c r="Q401" s="2" t="inlineStr">
         <is>
           <t>1.85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>344.7179</v>
+      </c>
+      <c r="I402" s="2" t="n">
+        <v>347.518</v>
+      </c>
+      <c r="J402" s="2" t="n">
+        <v>206830.76</v>
+      </c>
+      <c r="K402" s="2" t="n">
+        <v>208510.8</v>
+      </c>
+      <c r="L402" s="3" t="n">
+        <v>1680.04</v>
+      </c>
+      <c r="M402" s="2" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>104.26</v>
+      </c>
+      <c r="O402" s="2" t="n">
+        <v>145.79</v>
+      </c>
+      <c r="P402" s="3" t="n">
+        <v>1534.25</v>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I403" s="2" t="n">
+        <v>347.518</v>
+      </c>
+      <c r="J403" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K403" s="2" t="n">
+        <v>139007.2</v>
+      </c>
+      <c r="L403" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M403" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="O403" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="P403" s="4" t="n">
+        <v>-83.40000000000001</v>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>363.4567</v>
+      </c>
+      <c r="I404" s="2" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="J404" s="2" t="n">
+        <v>109037</v>
+      </c>
+      <c r="K404" s="2" t="n">
+        <v>109362</v>
+      </c>
+      <c r="L404" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="M404" s="2" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="N404" s="2" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="O404" s="2" t="n">
+        <v>76.52</v>
+      </c>
+      <c r="P404" s="3" t="n">
+        <v>248.48</v>
+      </c>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>256.1099</v>
+      </c>
+      <c r="I405" s="2" t="n">
+        <v>260.4367</v>
+      </c>
+      <c r="J405" s="2" t="n">
+        <v>102443.96</v>
+      </c>
+      <c r="K405" s="2" t="n">
+        <v>104174.67</v>
+      </c>
+      <c r="L405" s="3" t="n">
+        <v>1730.71</v>
+      </c>
+      <c r="M405" s="2" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="O405" s="2" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="P405" s="3" t="n">
+        <v>1657.96</v>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I406" s="2" t="n">
+        <v>260.4367</v>
+      </c>
+      <c r="J406" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" s="2" t="n">
+        <v>52087.33</v>
+      </c>
+      <c r="L406" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M406" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="O406" s="2" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="P406" s="4" t="n">
+        <v>-31.25</v>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G407" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I407" s="2" t="n">
+        <v>95.47</v>
+      </c>
+      <c r="J407" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" s="2" t="n">
+        <v>47735</v>
+      </c>
+      <c r="L407" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="O407" s="2" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="P407" s="4" t="n">
+        <v>-28.87</v>
+      </c>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q407"/>
+  <dimension ref="A1:Q411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24964,10 +24964,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C402" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C402" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
@@ -25027,10 +25025,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C403" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C403" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
@@ -25090,10 +25086,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C404" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C404" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
@@ -25153,10 +25147,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C405" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C405" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
@@ -25216,10 +25208,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C406" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C406" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
@@ -25279,10 +25269,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C407" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C407" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
@@ -25328,6 +25316,258 @@
       <c r="Q407" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G408" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I408" s="2" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="J408" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K408" s="2" t="n">
+        <v>8929</v>
+      </c>
+      <c r="L408" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M408" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="O408" s="2" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="P408" s="4" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G409" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I409" s="2" t="n">
+        <v>260.8267</v>
+      </c>
+      <c r="J409" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K409" s="2" t="n">
+        <v>156496</v>
+      </c>
+      <c r="L409" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M409" s="2" t="n">
+        <v>15.6496</v>
+      </c>
+      <c r="N409" s="2" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="O409" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="P409" s="4" t="n">
+        <v>-93.90000000000001</v>
+      </c>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G410" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H410" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I410" s="2" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="J410" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" s="2" t="n">
+        <v>36226</v>
+      </c>
+      <c r="L410" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M410" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="O410" s="2" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="P410" s="4" t="n">
+        <v>-23.11</v>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="G411" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>335.7953</v>
+      </c>
+      <c r="I411" s="2" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="J411" s="2" t="n">
+        <v>302215.8</v>
+      </c>
+      <c r="K411" s="2" t="n">
+        <v>304983</v>
+      </c>
+      <c r="L411" s="3" t="n">
+        <v>2767.2</v>
+      </c>
+      <c r="M411" s="2" t="n">
+        <v>60.72</v>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>152.49</v>
+      </c>
+      <c r="O411" s="2" t="n">
+        <v>213.21</v>
+      </c>
+      <c r="P411" s="3" t="n">
+        <v>2553.99</v>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>0.85%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q411"/>
+  <dimension ref="A1:Q423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25330,10 +25330,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C408" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C408" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
@@ -25393,10 +25391,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C409" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C409" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
@@ -25456,10 +25452,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C410" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C410" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
@@ -25519,10 +25513,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C411" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C411" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
@@ -25568,6 +25560,762 @@
       <c r="Q411" s="2" t="inlineStr">
         <is>
           <t>0.85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G412" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>255.828</v>
+      </c>
+      <c r="I412" s="2" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="J412" s="2" t="n">
+        <v>51165.6</v>
+      </c>
+      <c r="K412" s="2" t="n">
+        <v>52120</v>
+      </c>
+      <c r="L412" s="3" t="n">
+        <v>954.4</v>
+      </c>
+      <c r="M412" s="2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="O412" s="2" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="P412" s="3" t="n">
+        <v>918.01</v>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>1.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>255.828</v>
+      </c>
+      <c r="I413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" s="2" t="n">
+        <v>76748.39999999999</v>
+      </c>
+      <c r="K413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L413" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M413" s="2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" s="2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="P413" s="4" t="n">
+        <v>-7.67</v>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G414" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>269.35</v>
+      </c>
+      <c r="I414" s="2" t="n">
+        <v>272.785</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>107740</v>
+      </c>
+      <c r="K414" s="2" t="n">
+        <v>109114</v>
+      </c>
+      <c r="L414" s="3" t="n">
+        <v>1374</v>
+      </c>
+      <c r="M414" s="2" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="O414" s="2" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="P414" s="3" t="n">
+        <v>1297.75</v>
+      </c>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="I415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>97614</v>
+      </c>
+      <c r="K415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>9.7614</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" s="2" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="P415" s="4" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G416" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>1173.49</v>
+      </c>
+      <c r="I416" s="2" t="n">
+        <v>1189.3</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>117349</v>
+      </c>
+      <c r="K416" s="2" t="n">
+        <v>118930</v>
+      </c>
+      <c r="L416" s="3" t="n">
+        <v>1581</v>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="O416" s="2" t="n">
+        <v>83.09</v>
+      </c>
+      <c r="P416" s="3" t="n">
+        <v>1497.91</v>
+      </c>
+      <c r="Q416" s="2" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I417" s="2" t="n">
+        <v>1189.3</v>
+      </c>
+      <c r="J417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" s="2" t="n">
+        <v>118930</v>
+      </c>
+      <c r="L417" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="O417" s="2" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="P417" s="4" t="n">
+        <v>-71.34999999999999</v>
+      </c>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G418" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H418" s="2" t="n">
+        <v>78.642</v>
+      </c>
+      <c r="I418" s="2" t="n">
+        <v>80.655</v>
+      </c>
+      <c r="J418" s="2" t="n">
+        <v>31456.8</v>
+      </c>
+      <c r="K418" s="2" t="n">
+        <v>32262</v>
+      </c>
+      <c r="L418" s="3" t="n">
+        <v>805.2</v>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="O418" s="2" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="P418" s="3" t="n">
+        <v>779.0700000000001</v>
+      </c>
+      <c r="Q418" s="2" t="inlineStr">
+        <is>
+          <t>2.48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>78.642</v>
+      </c>
+      <c r="I419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" s="2" t="n">
+        <v>7864.2</v>
+      </c>
+      <c r="K419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P419" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F420" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I420" s="2" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="J420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" s="2" t="n">
+        <v>37757</v>
+      </c>
+      <c r="L420" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M420" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N420" s="2" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="O420" s="2" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="P420" s="4" t="n">
+        <v>-23.88</v>
+      </c>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G421" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>220.06</v>
+      </c>
+      <c r="I421" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J421" s="2" t="n">
+        <v>22006</v>
+      </c>
+      <c r="K421" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L421" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P421" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q421" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H422" s="2" t="n">
+        <v>259.59</v>
+      </c>
+      <c r="I422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" s="2" t="n">
+        <v>25959</v>
+      </c>
+      <c r="K422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L422" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P422" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q422" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G423" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>560.99</v>
+      </c>
+      <c r="I423" s="2" t="n">
+        <v>562.99</v>
+      </c>
+      <c r="J423" s="2" t="n">
+        <v>56099</v>
+      </c>
+      <c r="K423" s="2" t="n">
+        <v>56299</v>
+      </c>
+      <c r="L423" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="O423" s="2" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="P423" s="3" t="n">
+        <v>160.61</v>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>0.29%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q423"/>
+  <dimension ref="A1:Q431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25574,10 +25574,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C412" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C412" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
@@ -25637,10 +25635,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C413" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C413" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
@@ -25700,10 +25696,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C414" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C414" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
@@ -25763,10 +25757,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C415" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C415" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
@@ -25826,10 +25818,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C416" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C416" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
@@ -25889,10 +25879,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C417" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C417" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
@@ -25952,10 +25940,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C418" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C418" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
@@ -26015,10 +26001,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C419" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C419" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
@@ -26078,10 +26062,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C420" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C420" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
@@ -26141,10 +26123,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C421" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C421" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
@@ -26204,10 +26184,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C422" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C422" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
@@ -26267,10 +26245,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C423" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C423" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
@@ -26316,6 +26292,510 @@
       <c r="Q423" s="2" t="inlineStr">
         <is>
           <t>0.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" s="2" t="n">
+        <v>4850</v>
+      </c>
+      <c r="K424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L424" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P424" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G425" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>269.81</v>
+      </c>
+      <c r="I425" s="2" t="n">
+        <v>272.49</v>
+      </c>
+      <c r="J425" s="2" t="n">
+        <v>53962</v>
+      </c>
+      <c r="K425" s="2" t="n">
+        <v>54498</v>
+      </c>
+      <c r="L425" s="3" t="n">
+        <v>536</v>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="O425" s="2" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="P425" s="3" t="n">
+        <v>497.9</v>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="I426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J426" s="2" t="n">
+        <v>6599</v>
+      </c>
+      <c r="K426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P426" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q426" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I427" s="2" t="n">
+        <v>334.19</v>
+      </c>
+      <c r="J427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" s="2" t="n">
+        <v>100257</v>
+      </c>
+      <c r="L427" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>10.0257</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="O427" s="2" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="P427" s="4" t="n">
+        <v>-60.16</v>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F428" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G428" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="I428" s="2" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="J428" s="2" t="n">
+        <v>15132</v>
+      </c>
+      <c r="K428" s="2" t="n">
+        <v>15890</v>
+      </c>
+      <c r="L428" s="3" t="n">
+        <v>758</v>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="O428" s="2" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="P428" s="3" t="n">
+        <v>740.0599999999999</v>
+      </c>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F429" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I429" s="2" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="J429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" s="2" t="n">
+        <v>7945</v>
+      </c>
+      <c r="L429" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O429" s="2" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="P429" s="4" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" s="2" t="n">
+        <v>8660</v>
+      </c>
+      <c r="K430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P430" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>214.8</v>
+      </c>
+      <c r="I431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>42960</v>
+      </c>
+      <c r="K431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P431" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q431"/>
+  <dimension ref="A1:Q433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26306,10 +26306,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C424" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C424" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
@@ -26369,10 +26367,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C425" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C425" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
@@ -26432,10 +26428,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C426" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C426" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
@@ -26495,10 +26489,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C427" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C427" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
@@ -26558,10 +26550,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C428" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C428" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
@@ -26621,10 +26611,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C429" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C429" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
@@ -26684,10 +26672,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C430" s="2" t="inlineStr">
-        <is>
-          <t>000021</t>
-        </is>
+      <c r="C430" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
@@ -26747,10 +26733,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C431" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C431" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
@@ -26796,6 +26780,132 @@
       <c r="Q431" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F432" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G432" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>309.078</v>
+      </c>
+      <c r="I432" s="2" t="n">
+        <v>310.859</v>
+      </c>
+      <c r="J432" s="2" t="n">
+        <v>309078</v>
+      </c>
+      <c r="K432" s="2" t="n">
+        <v>310859</v>
+      </c>
+      <c r="L432" s="3" t="n">
+        <v>1781</v>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="O432" s="2" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="P432" s="3" t="n">
+        <v>1563.58</v>
+      </c>
+      <c r="Q432" s="2" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F433" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" s="2" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K433" s="2" t="n">
+        <v>36825</v>
+      </c>
+      <c r="L433" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="O433" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="P433" s="4" t="n">
+        <v>-23.41</v>
+      </c>
+      <c r="Q433" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q433"/>
+  <dimension ref="A1:Q437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26794,10 +26794,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C432" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C432" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
@@ -26857,10 +26855,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C433" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C433" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
@@ -26906,6 +26902,258 @@
       <c r="Q433" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="J434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K434" s="2" t="n">
+        <v>36800</v>
+      </c>
+      <c r="L434" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O434" s="2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="P434" s="4" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="Q434" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G435" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>182.02</v>
+      </c>
+      <c r="I435" s="2" t="n">
+        <v>183.605</v>
+      </c>
+      <c r="J435" s="2" t="n">
+        <v>145616</v>
+      </c>
+      <c r="K435" s="2" t="n">
+        <v>146884</v>
+      </c>
+      <c r="L435" s="3" t="n">
+        <v>1268</v>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="O435" s="2" t="n">
+        <v>102.69</v>
+      </c>
+      <c r="P435" s="3" t="n">
+        <v>1165.31</v>
+      </c>
+      <c r="Q435" s="2" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F436" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G436" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>302.05</v>
+      </c>
+      <c r="I436" s="2" t="n">
+        <v>306.6533</v>
+      </c>
+      <c r="J436" s="2" t="n">
+        <v>120820</v>
+      </c>
+      <c r="K436" s="2" t="n">
+        <v>122661.33</v>
+      </c>
+      <c r="L436" s="3" t="n">
+        <v>1841.33</v>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="O436" s="2" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="P436" s="3" t="n">
+        <v>1755.65</v>
+      </c>
+      <c r="Q436" s="2" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F437" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" s="2" t="n">
+        <v>306.6533</v>
+      </c>
+      <c r="J437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" s="2" t="n">
+        <v>61330.67</v>
+      </c>
+      <c r="L437" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="O437" s="2" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="P437" s="4" t="n">
+        <v>-36.8</v>
+      </c>
+      <c r="Q437" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q437"/>
+  <dimension ref="A1:Q444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26916,10 +26916,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C434" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C434" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
@@ -26979,10 +26977,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C435" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C435" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
@@ -27042,10 +27038,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C436" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
@@ -27105,10 +27099,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C437" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C437" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
@@ -27152,6 +27144,447 @@
         <v>-36.8</v>
       </c>
       <c r="Q437" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" s="2" t="n">
+        <v>174.98</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" s="2" t="n">
+        <v>17498</v>
+      </c>
+      <c r="L438" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O438" s="2" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="P438" s="4" t="n">
+        <v>-13.75</v>
+      </c>
+      <c r="Q438" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" s="2" t="n">
+        <v>209.39</v>
+      </c>
+      <c r="J439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" s="2" t="n">
+        <v>83756</v>
+      </c>
+      <c r="L439" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" s="2" t="n">
+        <v>8.3756</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="O439" s="2" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="P439" s="4" t="n">
+        <v>-50.26</v>
+      </c>
+      <c r="Q439" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" s="2" t="n">
+        <v>231.12</v>
+      </c>
+      <c r="J440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" s="2" t="n">
+        <v>23112</v>
+      </c>
+      <c r="L440" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="O440" s="2" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="P440" s="4" t="n">
+        <v>-16.56</v>
+      </c>
+      <c r="Q440" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F441" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G441" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H441" s="2" t="n">
+        <v>317.02</v>
+      </c>
+      <c r="I441" s="2" t="n">
+        <v>330.4033</v>
+      </c>
+      <c r="J441" s="2" t="n">
+        <v>63404</v>
+      </c>
+      <c r="K441" s="2" t="n">
+        <v>66080.67</v>
+      </c>
+      <c r="L441" s="3" t="n">
+        <v>2676.67</v>
+      </c>
+      <c r="M441" s="2" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="O441" s="2" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="P441" s="3" t="n">
+        <v>2630.68</v>
+      </c>
+      <c r="Q441" s="2" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F442" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" s="2" t="n">
+        <v>330.4033</v>
+      </c>
+      <c r="J442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K442" s="2" t="n">
+        <v>132161.33</v>
+      </c>
+      <c r="L442" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M442" s="2" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="O442" s="2" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="P442" s="4" t="n">
+        <v>-79.3</v>
+      </c>
+      <c r="Q442" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F443" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G443" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H443" s="2" t="n">
+        <v>545.11</v>
+      </c>
+      <c r="I443" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="J443" s="2" t="n">
+        <v>54511</v>
+      </c>
+      <c r="K443" s="2" t="n">
+        <v>55000</v>
+      </c>
+      <c r="L443" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="M443" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O443" s="2" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="P443" s="3" t="n">
+        <v>450.55</v>
+      </c>
+      <c r="Q443" s="2" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F444" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I444" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="J444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K444" s="2" t="n">
+        <v>55000</v>
+      </c>
+      <c r="L444" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M444" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O444" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="P444" s="4" t="n">
+        <v>-33</v>
+      </c>
+      <c r="Q444" s="2" t="inlineStr">
         <is>
           <t>⚠️多卖未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q444"/>
+  <dimension ref="A1:Q447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27160,10 +27160,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C438" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C438" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
@@ -27223,10 +27221,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C439" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C439" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
@@ -27286,10 +27282,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C440" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C440" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
@@ -27349,10 +27343,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C441" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C441" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
@@ -27412,10 +27404,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C442" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C442" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
@@ -27475,10 +27465,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C443" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
@@ -27538,10 +27526,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C444" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C444" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
@@ -27587,6 +27573,195 @@
       <c r="Q444" s="2" t="inlineStr">
         <is>
           <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F445" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G445" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H445" s="2" t="n">
+        <v>332.765</v>
+      </c>
+      <c r="I445" s="2" t="n">
+        <v>334.14</v>
+      </c>
+      <c r="J445" s="2" t="n">
+        <v>199659</v>
+      </c>
+      <c r="K445" s="2" t="n">
+        <v>200484</v>
+      </c>
+      <c r="L445" s="3" t="n">
+        <v>825</v>
+      </c>
+      <c r="M445" s="2" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="O445" s="2" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="P445" s="3" t="n">
+        <v>684.75</v>
+      </c>
+      <c r="Q445" s="2" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" s="2" t="n">
+        <v>332.765</v>
+      </c>
+      <c r="I446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" s="2" t="n">
+        <v>66553</v>
+      </c>
+      <c r="K446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="P446" s="4" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="Q446" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" s="2" t="n">
+        <v>541</v>
+      </c>
+      <c r="I447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" s="2" t="n">
+        <v>54100</v>
+      </c>
+      <c r="K447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M447" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="P447" s="4" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="Q447" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q447"/>
+  <dimension ref="A1:Q449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27587,10 +27587,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C445" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C445" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
@@ -27650,10 +27648,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C446" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C446" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
@@ -27713,10 +27709,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C447" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C447" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
@@ -27760,6 +27754,132 @@
         <v>-5.41</v>
       </c>
       <c r="Q447" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F448" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G448" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H448" s="2" t="n">
+        <v>224.62</v>
+      </c>
+      <c r="I448" s="2" t="n">
+        <v>226.675</v>
+      </c>
+      <c r="J448" s="2" t="n">
+        <v>179696</v>
+      </c>
+      <c r="K448" s="2" t="n">
+        <v>181340</v>
+      </c>
+      <c r="L448" s="3" t="n">
+        <v>1644</v>
+      </c>
+      <c r="M448" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="O448" s="2" t="n">
+        <v>126.77</v>
+      </c>
+      <c r="P448" s="3" t="n">
+        <v>1517.23</v>
+      </c>
+      <c r="Q448" s="2" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H449" s="2" t="n">
+        <v>501.01</v>
+      </c>
+      <c r="I449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" s="2" t="n">
+        <v>100202</v>
+      </c>
+      <c r="K449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M449" s="2" t="n">
+        <v>10.0202</v>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="P449" s="4" t="n">
+        <v>-10.02</v>
+      </c>
+      <c r="Q449" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q449"/>
+  <dimension ref="A1:Q452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27770,10 +27770,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C448" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C448" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
@@ -27833,10 +27831,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C449" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C449" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
@@ -27880,6 +27876,195 @@
         <v>-10.02</v>
       </c>
       <c r="Q449" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>688676</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>金盘科技</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F450" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" s="2" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="J450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" s="2" t="n">
+        <v>26788</v>
+      </c>
+      <c r="L450" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="O450" s="2" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="P450" s="4" t="n">
+        <v>-18.39</v>
+      </c>
+      <c r="Q450" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F451" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" s="2" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="J451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" s="2" t="n">
+        <v>16355</v>
+      </c>
+      <c r="L451" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M451" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="O451" s="2" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="P451" s="4" t="n">
+        <v>-13.18</v>
+      </c>
+      <c r="Q451" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>平安账户</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H452" s="2" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="I452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" s="2" t="n">
+        <v>23396</v>
+      </c>
+      <c r="K452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L452" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M452" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O452" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P452" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q452" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q452"/>
+  <dimension ref="A1:Q455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27892,10 +27892,8 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C450" s="2" t="inlineStr">
-        <is>
-          <t>688676</t>
-        </is>
+      <c r="C450" s="2" t="n">
+        <v>688676</v>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
@@ -27955,10 +27953,8 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C451" s="2" t="inlineStr">
-        <is>
-          <t>603920</t>
-        </is>
+      <c r="C451" s="2" t="n">
+        <v>603920</v>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
@@ -28018,10 +28014,8 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C452" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C452" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
@@ -28067,6 +28061,195 @@
       <c r="Q452" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F453" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I453" s="2" t="n">
+        <v>411.37</v>
+      </c>
+      <c r="J453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" s="2" t="n">
+        <v>41137</v>
+      </c>
+      <c r="L453" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M453" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="O453" s="2" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P453" s="4" t="n">
+        <v>-25.57</v>
+      </c>
+      <c r="Q453" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F454" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G454" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H454" s="2" t="n">
+        <v>280.01</v>
+      </c>
+      <c r="I454" s="2" t="n">
+        <v>287.715</v>
+      </c>
+      <c r="J454" s="2" t="n">
+        <v>56002</v>
+      </c>
+      <c r="K454" s="2" t="n">
+        <v>57543</v>
+      </c>
+      <c r="L454" s="3" t="n">
+        <v>1541</v>
+      </c>
+      <c r="M454" s="2" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="O454" s="2" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="P454" s="3" t="n">
+        <v>1500.88</v>
+      </c>
+      <c r="Q454" s="2" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F455" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I455" s="2" t="n">
+        <v>287.715</v>
+      </c>
+      <c r="J455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" s="2" t="n">
+        <v>57543</v>
+      </c>
+      <c r="L455" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M455" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="O455" s="2" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="P455" s="4" t="n">
+        <v>-34.52</v>
+      </c>
+      <c r="Q455" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q455"/>
+  <dimension ref="A1:Q457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28075,10 +28075,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C453" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C453" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
@@ -28138,10 +28136,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C454" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C454" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
@@ -28201,10 +28197,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C455" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C455" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
@@ -28250,6 +28244,132 @@
       <c r="Q455" s="2" t="inlineStr">
         <is>
           <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F456" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I456" s="2" t="n">
+        <v>270.09</v>
+      </c>
+      <c r="J456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" s="2" t="n">
+        <v>108036</v>
+      </c>
+      <c r="L456" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M456" s="2" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="O456" s="2" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="P456" s="4" t="n">
+        <v>-64.81999999999999</v>
+      </c>
+      <c r="Q456" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H457" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="I457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" s="2" t="n">
+        <v>9122</v>
+      </c>
+      <c r="K457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L457" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P457" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q457" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q457"/>
+  <dimension ref="A1:Q460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28255,24 +28255,24 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>300548</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="E456" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G456" s="2" t="n">
         <v>0</v>
@@ -28281,28 +28281,28 @@
         <v>0</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>270.09</v>
+        <v>151</v>
       </c>
       <c r="J456" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>108036</v>
+        <v>15100</v>
       </c>
       <c r="L456" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>10.8036</v>
+        <v>5</v>
       </c>
       <c r="N456" s="2" t="n">
-        <v>54.02</v>
+        <v>7.55</v>
       </c>
       <c r="O456" s="2" t="n">
-        <v>64.81999999999999</v>
+        <v>12.55</v>
       </c>
       <c r="P456" s="4" t="n">
-        <v>-64.81999999999999</v>
+        <v>-12.55</v>
       </c>
       <c r="Q456" s="2" t="inlineStr">
         <is>
@@ -28318,39 +28318,39 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>两融账户</t>
+          <t>两融账户+手机账户</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>002594</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G457" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H457" s="2" t="n">
-        <v>91.22</v>
+        <v>0</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>0</v>
+        <v>421.38</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>9122</v>
+        <v>0</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>0</v>
+        <v>42138</v>
       </c>
       <c r="L457" s="4" t="n">
         <v>0</v>
@@ -28359,15 +28359,204 @@
         <v>5</v>
       </c>
       <c r="N457" s="2" t="n">
-        <v>0</v>
+        <v>21.07</v>
       </c>
       <c r="O457" s="2" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="P457" s="4" t="n">
+        <v>-26.07</v>
+      </c>
+      <c r="Q457" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F458" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G458" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H458" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I458" s="2" t="n">
+        <v>270.09</v>
+      </c>
+      <c r="J458" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K458" s="2" t="n">
+        <v>108036</v>
+      </c>
+      <c r="L458" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M458" s="2" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="O458" s="2" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="P458" s="4" t="n">
+        <v>-64.81999999999999</v>
+      </c>
+      <c r="Q458" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F459" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" s="2" t="n">
+        <v>981</v>
+      </c>
+      <c r="J459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" s="2" t="n">
+        <v>98100</v>
+      </c>
+      <c r="L459" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="O459" s="2" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="P459" s="4" t="n">
+        <v>-58.86</v>
+      </c>
+      <c r="Q459" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H460" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="I460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" s="2" t="n">
+        <v>9122</v>
+      </c>
+      <c r="K460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M460" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P457" s="4" t="n">
+      <c r="N460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P460" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Q457" s="2" t="inlineStr">
+      <c r="Q460" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q460"/>
+  <dimension ref="A1:Q469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28258,10 +28258,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C456" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C456" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
@@ -28321,10 +28319,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C457" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C457" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
@@ -28384,10 +28380,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C458" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C458" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
@@ -28447,10 +28441,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C459" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C459" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
@@ -28510,10 +28502,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C460" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C460" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
@@ -28557,6 +28547,573 @@
         <v>-5</v>
       </c>
       <c r="Q460" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F461" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I461" s="2" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="J461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" s="2" t="n">
+        <v>20190</v>
+      </c>
+      <c r="L461" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M461" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N461" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O461" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="P461" s="4" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="Q461" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F462" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I462" s="2" t="n">
+        <v>404.88</v>
+      </c>
+      <c r="J462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" s="2" t="n">
+        <v>80976</v>
+      </c>
+      <c r="L462" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M462" s="2" t="n">
+        <v>8.0976</v>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="O462" s="2" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="P462" s="4" t="n">
+        <v>-48.59</v>
+      </c>
+      <c r="Q462" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F463" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G463" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H463" s="2" t="n">
+        <v>289.87</v>
+      </c>
+      <c r="I463" s="2" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="J463" s="2" t="n">
+        <v>57974</v>
+      </c>
+      <c r="K463" s="2" t="n">
+        <v>58290</v>
+      </c>
+      <c r="L463" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="M463" s="2" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="O463" s="2" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="P463" s="3" t="n">
+        <v>275.23</v>
+      </c>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F464" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" s="2" t="n">
+        <v>156.67</v>
+      </c>
+      <c r="J464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K464" s="2" t="n">
+        <v>15667</v>
+      </c>
+      <c r="L464" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M464" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="O464" s="2" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="P464" s="4" t="n">
+        <v>-12.83</v>
+      </c>
+      <c r="Q464" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F465" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G465" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H465" s="2" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="I465" s="2" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="J465" s="2" t="n">
+        <v>14920</v>
+      </c>
+      <c r="K465" s="2" t="n">
+        <v>15038</v>
+      </c>
+      <c r="L465" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="M465" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N465" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="O465" s="2" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="P465" s="3" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="Q465" s="2" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F466" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I466" s="2" t="n">
+        <v>183.39</v>
+      </c>
+      <c r="J466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" s="2" t="n">
+        <v>18339</v>
+      </c>
+      <c r="L466" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M466" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="O466" s="2" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="P466" s="4" t="n">
+        <v>-14.17</v>
+      </c>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F467" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G467" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H467" s="2" t="n">
+        <v>214.29</v>
+      </c>
+      <c r="I467" s="2" t="n">
+        <v>211.995</v>
+      </c>
+      <c r="J467" s="2" t="n">
+        <v>85716</v>
+      </c>
+      <c r="K467" s="2" t="n">
+        <v>84798</v>
+      </c>
+      <c r="L467" s="4" t="n">
+        <v>-918</v>
+      </c>
+      <c r="M467" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="O467" s="2" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="P467" s="4" t="n">
+        <v>-977.45</v>
+      </c>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>-1.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F468" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I468" s="2" t="n">
+        <v>910</v>
+      </c>
+      <c r="J468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K468" s="2" t="n">
+        <v>91000</v>
+      </c>
+      <c r="L468" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="O468" s="2" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="P468" s="4" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="F469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" s="2" t="n">
+        <v>90.8471</v>
+      </c>
+      <c r="I469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J469" s="2" t="n">
+        <v>63593</v>
+      </c>
+      <c r="K469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M469" s="2" t="n">
+        <v>6.3593</v>
+      </c>
+      <c r="N469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O469" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="P469" s="4" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="Q469" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q469"/>
+  <dimension ref="A1:Q472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28563,10 +28563,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C461" s="2" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="C461" s="2" t="n">
+        <v>300394</v>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
@@ -28626,10 +28624,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C462" s="2" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="C462" s="2" t="n">
+        <v>300502</v>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
@@ -28689,10 +28685,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C463" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C463" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28746,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C464" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C464" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
@@ -28815,10 +28807,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C465" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C465" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
@@ -28878,10 +28868,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C466" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C466" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
@@ -28941,10 +28929,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C467" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C467" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
@@ -29004,10 +28990,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C468" s="2" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="C468" s="2" t="n">
+        <v>300308</v>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
@@ -29067,10 +29051,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C469" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C469" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
@@ -29116,6 +29098,195 @@
       <c r="Q469" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F470" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G470" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H470" s="2" t="n">
+        <v>289.12</v>
+      </c>
+      <c r="I470" s="2" t="n">
+        <v>290.61</v>
+      </c>
+      <c r="J470" s="2" t="n">
+        <v>57824</v>
+      </c>
+      <c r="K470" s="2" t="n">
+        <v>58122</v>
+      </c>
+      <c r="L470" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="M470" s="2" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="O470" s="2" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="P470" s="3" t="n">
+        <v>257.35</v>
+      </c>
+      <c r="Q470" s="2" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F471" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G471" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H471" s="2" t="n">
+        <v>210.0875</v>
+      </c>
+      <c r="I471" s="2" t="n">
+        <v>207.81</v>
+      </c>
+      <c r="J471" s="2" t="n">
+        <v>42017.5</v>
+      </c>
+      <c r="K471" s="2" t="n">
+        <v>41562</v>
+      </c>
+      <c r="L471" s="4" t="n">
+        <v>-455.5</v>
+      </c>
+      <c r="M471" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="O471" s="2" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="P471" s="4" t="n">
+        <v>-486.28</v>
+      </c>
+      <c r="Q471" s="2" t="inlineStr">
+        <is>
+          <t>-1.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H472" s="2" t="n">
+        <v>210.0875</v>
+      </c>
+      <c r="I472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" s="2" t="n">
+        <v>126052.5</v>
+      </c>
+      <c r="K472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L472" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M472" s="2" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" s="2" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="P472" s="4" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="Q472" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q472"/>
+  <dimension ref="A1:Q479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29112,10 +29112,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C470" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C470" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
@@ -29175,10 +29173,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C471" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C471" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
@@ -29238,10 +29234,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C472" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C472" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
@@ -29287,6 +29281,447 @@
       <c r="Q472" s="2" t="inlineStr">
         <is>
           <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F473" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G473" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H473" s="2" t="n">
+        <v>213.205</v>
+      </c>
+      <c r="I473" s="2" t="n">
+        <v>213.68</v>
+      </c>
+      <c r="J473" s="2" t="n">
+        <v>85282</v>
+      </c>
+      <c r="K473" s="2" t="n">
+        <v>85472</v>
+      </c>
+      <c r="L473" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="M473" s="2" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="O473" s="2" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="P473" s="3" t="n">
+        <v>130.18</v>
+      </c>
+      <c r="Q473" s="2" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F474" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G474" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I474" s="2" t="n">
+        <v>213.68</v>
+      </c>
+      <c r="J474" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K474" s="2" t="n">
+        <v>128208</v>
+      </c>
+      <c r="L474" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M474" s="2" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="O474" s="2" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="P474" s="4" t="n">
+        <v>-76.92</v>
+      </c>
+      <c r="Q474" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F475" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I475" s="2" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="J475" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K475" s="2" t="n">
+        <v>38752</v>
+      </c>
+      <c r="L475" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M475" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="O475" s="2" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="P475" s="4" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q475" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F476" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G476" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H476" s="2" t="n">
+        <v>295.08</v>
+      </c>
+      <c r="I476" s="2" t="n">
+        <v>296.5167</v>
+      </c>
+      <c r="J476" s="2" t="n">
+        <v>177048</v>
+      </c>
+      <c r="K476" s="2" t="n">
+        <v>177910</v>
+      </c>
+      <c r="L476" s="3" t="n">
+        <v>862</v>
+      </c>
+      <c r="M476" s="2" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>88.95999999999999</v>
+      </c>
+      <c r="O476" s="2" t="n">
+        <v>124.46</v>
+      </c>
+      <c r="P476" s="3" t="n">
+        <v>737.54</v>
+      </c>
+      <c r="Q476" s="2" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H477" s="2" t="n">
+        <v>107.71</v>
+      </c>
+      <c r="I477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" s="2" t="n">
+        <v>10771</v>
+      </c>
+      <c r="K477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L477" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M477" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N477" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P477" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q477" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F478" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I478" s="2" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="J478" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K478" s="2" t="n">
+        <v>14055</v>
+      </c>
+      <c r="L478" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M478" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="O478" s="2" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="P478" s="4" t="n">
+        <v>-12.03</v>
+      </c>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F479" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G479" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I479" s="2" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="J479" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" s="2" t="n">
+        <v>12314</v>
+      </c>
+      <c r="L479" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M479" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O479" s="2" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="P479" s="4" t="n">
+        <v>-11.16</v>
+      </c>
+      <c r="Q479" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q479"/>
+  <dimension ref="A1:Q482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29295,10 +29295,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C473" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C473" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
@@ -29358,10 +29356,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C474" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C474" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
@@ -29421,10 +29417,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C475" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C475" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
@@ -29484,10 +29478,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C476" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C476" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
@@ -29547,10 +29539,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C477" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C477" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
@@ -29610,10 +29600,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C478" s="2" t="inlineStr">
-        <is>
-          <t>688778</t>
-        </is>
+      <c r="C478" s="2" t="n">
+        <v>688778</v>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
@@ -29673,10 +29661,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C479" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C479" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
@@ -29722,6 +29708,195 @@
       <c r="Q479" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="I480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" s="2" t="n">
+        <v>10875</v>
+      </c>
+      <c r="K480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L480" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M480" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O480" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P480" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q480" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F481" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G481" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H481" s="2" t="n">
+        <v>88.01000000000001</v>
+      </c>
+      <c r="I481" s="2" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="J481" s="2" t="n">
+        <v>8801</v>
+      </c>
+      <c r="K481" s="2" t="n">
+        <v>9010</v>
+      </c>
+      <c r="L481" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="M481" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N481" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O481" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="P481" s="3" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="Q481" s="2" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F482" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G482" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H482" s="2" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="I482" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" s="2" t="n">
+        <v>11410</v>
+      </c>
+      <c r="K482" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L482" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M482" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N482" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P482" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q482" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q482"/>
+  <dimension ref="A1:Q490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29722,10 +29722,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C480" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C480" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
@@ -29785,10 +29783,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C481" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C481" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
@@ -29848,10 +29844,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C482" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C482" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
@@ -29895,6 +29889,510 @@
         <v>-5</v>
       </c>
       <c r="Q482" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F483" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G483" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H483" s="2" t="n">
+        <v>290.47</v>
+      </c>
+      <c r="I483" s="2" t="n">
+        <v>291.66</v>
+      </c>
+      <c r="J483" s="2" t="n">
+        <v>58094</v>
+      </c>
+      <c r="K483" s="2" t="n">
+        <v>58332</v>
+      </c>
+      <c r="L483" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="M483" s="2" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="N483" s="2" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="O483" s="2" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="P483" s="3" t="n">
+        <v>197.19</v>
+      </c>
+      <c r="Q483" s="2" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F484" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G484" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" s="2" t="n">
+        <v>290.47</v>
+      </c>
+      <c r="I484" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" s="2" t="n">
+        <v>58094</v>
+      </c>
+      <c r="K484" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="N484" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O484" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="P484" s="4" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="Q484" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F485" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G485" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" s="2" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="I485" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J485" s="2" t="n">
+        <v>15574</v>
+      </c>
+      <c r="K485" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N485" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P485" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q485" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F486" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G486" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H486" s="2" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="I486" s="2" t="n">
+        <v>205.57</v>
+      </c>
+      <c r="J486" s="2" t="n">
+        <v>40870</v>
+      </c>
+      <c r="K486" s="2" t="n">
+        <v>41114</v>
+      </c>
+      <c r="L486" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="M486" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N486" s="2" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="O486" s="2" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="P486" s="3" t="n">
+        <v>213.44</v>
+      </c>
+      <c r="Q486" s="2" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" s="2" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="I487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" s="2" t="n">
+        <v>5039</v>
+      </c>
+      <c r="K487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P487" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q487" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F488" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G488" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="I488" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" s="2" t="n">
+        <v>16960</v>
+      </c>
+      <c r="K488" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N488" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P488" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q488" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H489" s="2" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="I489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" s="2" t="n">
+        <v>5685</v>
+      </c>
+      <c r="K489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L489" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M489" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O489" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P489" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q489" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H490" s="2" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="I490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" s="2" t="n">
+        <v>11404</v>
+      </c>
+      <c r="K490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P490" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q490" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q490"/>
+  <dimension ref="A1:Q495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29905,10 +29905,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C483" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C483" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
@@ -29968,10 +29966,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C484" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C484" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
@@ -30031,10 +30027,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C485" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C485" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
@@ -30094,10 +30088,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C486" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C486" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
@@ -30157,10 +30149,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C487" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C487" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
@@ -30220,10 +30210,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C488" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C488" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
@@ -30283,10 +30271,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C489" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C489" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
@@ -30346,10 +30332,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C490" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C490" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
@@ -30393,6 +30377,321 @@
         <v>-5</v>
       </c>
       <c r="Q490" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H491" s="2" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="I491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" s="2" t="n">
+        <v>5647</v>
+      </c>
+      <c r="K491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L491" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P491" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q491" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F492" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G492" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I492" s="2" t="n">
+        <v>213.27</v>
+      </c>
+      <c r="J492" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K492" s="2" t="n">
+        <v>42654</v>
+      </c>
+      <c r="L492" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M492" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N492" s="2" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="O492" s="2" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="P492" s="4" t="n">
+        <v>-26.33</v>
+      </c>
+      <c r="Q492" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F493" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G493" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>286.75</v>
+      </c>
+      <c r="I493" s="2" t="n">
+        <v>288.035</v>
+      </c>
+      <c r="J493" s="2" t="n">
+        <v>57350</v>
+      </c>
+      <c r="K493" s="2" t="n">
+        <v>57607</v>
+      </c>
+      <c r="L493" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="M493" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N493" s="2" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O493" s="2" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="P493" s="3" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="Q493" s="2" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F494" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G494" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H494" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I494" s="2" t="n">
+        <v>288.035</v>
+      </c>
+      <c r="J494" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K494" s="2" t="n">
+        <v>57607</v>
+      </c>
+      <c r="L494" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M494" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="N494" s="2" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O494" s="2" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="P494" s="4" t="n">
+        <v>-34.56</v>
+      </c>
+      <c r="Q494" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F495" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G495" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H495" s="2" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="I495" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J495" s="2" t="n">
+        <v>8928</v>
+      </c>
+      <c r="K495" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L495" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M495" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N495" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O495" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P495" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q495" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q495"/>
+  <dimension ref="A1:Q502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30393,10 +30393,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C491" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C491" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
@@ -30456,10 +30454,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C492" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C492" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
@@ -30519,10 +30515,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C493" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C493" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
@@ -30582,10 +30576,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C494" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C494" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
@@ -30645,10 +30637,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C495" s="2" t="inlineStr">
-        <is>
-          <t>600259</t>
-        </is>
+      <c r="C495" s="2" t="n">
+        <v>600259</v>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
@@ -30694,6 +30684,447 @@
       <c r="Q495" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F496" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G496" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="I496" s="2" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="J496" s="2" t="n">
+        <v>15480</v>
+      </c>
+      <c r="K496" s="2" t="n">
+        <v>15756</v>
+      </c>
+      <c r="L496" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="M496" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N496" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="O496" s="2" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="P496" s="3" t="n">
+        <v>258.12</v>
+      </c>
+      <c r="Q496" s="2" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F497" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G497" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" s="2" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="I497" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" s="2" t="n">
+        <v>9804</v>
+      </c>
+      <c r="K497" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N497" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P497" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q497" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F498" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G498" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H498" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I498" s="2" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="J498" s="2" t="n">
+        <v>2190</v>
+      </c>
+      <c r="K498" s="2" t="n">
+        <v>2199</v>
+      </c>
+      <c r="L498" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M498" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N498" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O498" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P498" s="4" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Q498" s="2" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F499" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G499" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I499" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" s="2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K499" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L499" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M499" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N499" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P499" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q499" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F500" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G500" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H500" s="2" t="n">
+        <v>222.2939</v>
+      </c>
+      <c r="I500" s="2" t="n">
+        <v>225.25</v>
+      </c>
+      <c r="J500" s="2" t="n">
+        <v>44458.78</v>
+      </c>
+      <c r="K500" s="2" t="n">
+        <v>45050</v>
+      </c>
+      <c r="L500" s="3" t="n">
+        <v>591.22</v>
+      </c>
+      <c r="M500" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N500" s="2" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="O500" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="P500" s="3" t="n">
+        <v>558.7</v>
+      </c>
+      <c r="Q500" s="2" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F501" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G501" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H501" s="2" t="n">
+        <v>222.2939</v>
+      </c>
+      <c r="I501" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" s="2" t="n">
+        <v>44458.78</v>
+      </c>
+      <c r="K501" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L501" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M501" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N501" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O501" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P501" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q501" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F502" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G502" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>294.1242</v>
+      </c>
+      <c r="I502" s="2" t="n">
+        <v>295.565</v>
+      </c>
+      <c r="J502" s="2" t="n">
+        <v>117649.7</v>
+      </c>
+      <c r="K502" s="2" t="n">
+        <v>118226</v>
+      </c>
+      <c r="L502" s="3" t="n">
+        <v>576.3</v>
+      </c>
+      <c r="M502" s="2" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="N502" s="2" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="O502" s="2" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="P502" s="3" t="n">
+        <v>493.6</v>
+      </c>
+      <c r="Q502" s="2" t="inlineStr">
+        <is>
+          <t>0.42%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q502"/>
+  <dimension ref="A1:Q506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30698,10 +30698,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C496" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C496" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
@@ -30761,10 +30759,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C497" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C497" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
@@ -30824,10 +30820,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C498" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C498" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
@@ -30887,10 +30881,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C499" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C499" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
@@ -30950,10 +30942,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C500" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C500" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
@@ -31013,10 +31003,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C501" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C501" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
@@ -31076,10 +31064,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C502" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C502" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
@@ -31125,6 +31111,258 @@
       <c r="Q502" s="2" t="inlineStr">
         <is>
           <t>0.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F503" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G503" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H503" s="2" t="n">
+        <v>212.08</v>
+      </c>
+      <c r="I503" s="2" t="n">
+        <v>212.725</v>
+      </c>
+      <c r="J503" s="2" t="n">
+        <v>169664</v>
+      </c>
+      <c r="K503" s="2" t="n">
+        <v>170180</v>
+      </c>
+      <c r="L503" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="M503" s="2" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="N503" s="2" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="O503" s="2" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="P503" s="3" t="n">
+        <v>396.93</v>
+      </c>
+      <c r="Q503" s="2" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F504" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G504" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" s="2" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="I504" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" s="2" t="n">
+        <v>3423</v>
+      </c>
+      <c r="K504" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M504" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N504" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O504" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P504" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q504" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F505" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="I505" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" s="2" t="n">
+        <v>2864</v>
+      </c>
+      <c r="K505" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N505" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P505" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q505" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F506" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G506" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H506" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" s="2" t="n">
+        <v>109.77</v>
+      </c>
+      <c r="J506" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" s="2" t="n">
+        <v>10977</v>
+      </c>
+      <c r="L506" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M506" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N506" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="O506" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="P506" s="4" t="n">
+        <v>-10.49</v>
+      </c>
+      <c r="Q506" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q506"/>
+  <dimension ref="A1:Q524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>中国稀士</t>
+          <t>中国稀土</t>
         </is>
       </c>
       <c r="E293" s="2" t="n">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>中国稀士</t>
+          <t>中国稀土</t>
         </is>
       </c>
       <c r="E294" s="2" t="n">
@@ -31125,10 +31125,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C503" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C503" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
@@ -31188,10 +31186,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C504" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C504" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
@@ -31251,10 +31247,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C505" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C505" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
@@ -31314,10 +31308,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C506" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C506" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
@@ -31363,6 +31355,1116 @@
       <c r="Q506" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="n">
+        <v>300054</v>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F507" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G507" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" s="2" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="J507" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" s="2" t="n">
+        <v>16376</v>
+      </c>
+      <c r="L507" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M507" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N507" s="2" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="O507" s="2" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="P507" s="4" t="n">
+        <v>-13.19</v>
+      </c>
+      <c r="Q507" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="n">
+        <v>601208</v>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F508" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="I508" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" s="2" t="n">
+        <v>4337</v>
+      </c>
+      <c r="K508" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L508" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M508" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N508" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P508" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q508" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="n">
+        <v>512760</v>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F509" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="I509" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" s="2" t="n">
+        <v>10670</v>
+      </c>
+      <c r="K509" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M509" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N509" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P509" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q509" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="n">
+        <v>688041</v>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F510" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" s="2" t="n">
+        <v>260.51</v>
+      </c>
+      <c r="I510" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" s="2" t="n">
+        <v>52102</v>
+      </c>
+      <c r="K510" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M510" s="2" t="n">
+        <v>5.2102</v>
+      </c>
+      <c r="N510" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="P510" s="4" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="Q510" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="n">
+        <v>600259</v>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>中稀有色</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F511" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G511" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H511" s="2" t="n">
+        <v>43.055</v>
+      </c>
+      <c r="I511" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" s="2" t="n">
+        <v>8611</v>
+      </c>
+      <c r="K511" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L511" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N511" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O511" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P511" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q511" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="n">
+        <v>2156</v>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F512" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G512" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H512" s="2" t="n">
+        <v>60.57</v>
+      </c>
+      <c r="I512" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J512" s="2" t="n">
+        <v>6057</v>
+      </c>
+      <c r="K512" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L512" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M512" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N512" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O512" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P512" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q512" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="n">
+        <v>2222</v>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F513" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G513" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" s="2" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="I513" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" s="2" t="n">
+        <v>6156</v>
+      </c>
+      <c r="K513" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M513" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N513" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P513" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q513" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="n">
+        <v>988</v>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F514" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="I514" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J514" s="2" t="n">
+        <v>11300</v>
+      </c>
+      <c r="K514" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N514" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O514" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P514" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q514" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F515" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G515" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H515" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="I515" s="2" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="J515" s="2" t="n">
+        <v>12200</v>
+      </c>
+      <c r="K515" s="2" t="n">
+        <v>12558</v>
+      </c>
+      <c r="L515" s="3" t="n">
+        <v>358</v>
+      </c>
+      <c r="M515" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N515" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="O515" s="2" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="P515" s="3" t="n">
+        <v>341.72</v>
+      </c>
+      <c r="Q515" s="2" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F516" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G516" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="I516" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" s="2" t="n">
+        <v>12200</v>
+      </c>
+      <c r="K516" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M516" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N516" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P516" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q516" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="n">
+        <v>561980</v>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F517" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" s="2" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="I517" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" s="2" t="n">
+        <v>13740</v>
+      </c>
+      <c r="K517" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N517" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P517" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q517" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="n">
+        <v>600498</v>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F518" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G518" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H518" s="2" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="I518" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" s="2" t="n">
+        <v>16476</v>
+      </c>
+      <c r="K518" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M518" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N518" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P518" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q518" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F519" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G519" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I519" s="2" t="n">
+        <v>1.1195</v>
+      </c>
+      <c r="J519" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" s="2" t="n">
+        <v>8956</v>
+      </c>
+      <c r="L519" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M519" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N519" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="O519" s="2" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="P519" s="4" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="Q519" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F520" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H520" s="2" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="I520" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" s="2" t="n">
+        <v>18252</v>
+      </c>
+      <c r="K520" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N520" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O520" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P520" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q520" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F521" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G521" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H521" s="2" t="n">
+        <v>216.31</v>
+      </c>
+      <c r="I521" s="2" t="n">
+        <v>217.56</v>
+      </c>
+      <c r="J521" s="2" t="n">
+        <v>86524</v>
+      </c>
+      <c r="K521" s="2" t="n">
+        <v>87024</v>
+      </c>
+      <c r="L521" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="M521" s="2" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="N521" s="2" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="O521" s="2" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="P521" s="3" t="n">
+        <v>439.14</v>
+      </c>
+      <c r="Q521" s="2" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F522" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G522" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" s="2" t="n">
+        <v>215.97</v>
+      </c>
+      <c r="J522" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K522" s="2" t="n">
+        <v>21597</v>
+      </c>
+      <c r="L522" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N522" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O522" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P522" s="4" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="Q522" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F523" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G523" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" s="2" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="J523" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" s="2" t="n">
+        <v>5672</v>
+      </c>
+      <c r="L523" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M523" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N523" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O523" s="2" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="P523" s="4" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="Q523" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F524" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G524" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H524" s="2" t="n">
+        <v>66.395</v>
+      </c>
+      <c r="I524" s="2" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="J524" s="2" t="n">
+        <v>13279</v>
+      </c>
+      <c r="K524" s="2" t="n">
+        <v>13564</v>
+      </c>
+      <c r="L524" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="M524" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N524" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="O524" s="2" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="P524" s="3" t="n">
+        <v>268.22</v>
+      </c>
+      <c r="Q524" s="2" t="inlineStr">
+        <is>
+          <t>2.02%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q524"/>
+  <dimension ref="A1:Q532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32101,10 +32101,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C519" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C519" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
@@ -32164,10 +32162,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C520" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C520" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
@@ -32227,10 +32223,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C521" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C521" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
@@ -32290,10 +32284,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C522" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C522" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
@@ -32353,10 +32345,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C523" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C523" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
@@ -32416,10 +32406,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C524" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C524" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
@@ -32465,6 +32453,510 @@
       <c r="Q524" s="2" t="inlineStr">
         <is>
           <t>2.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F525" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" s="2" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="I525" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="K525" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N525" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P525" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q525" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F526" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" s="2" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="I526" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" s="2" t="n">
+        <v>4147</v>
+      </c>
+      <c r="K526" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N526" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P526" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q526" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F527" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G527" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" s="2" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="J527" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" s="2" t="n">
+        <v>18478</v>
+      </c>
+      <c r="L527" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N527" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="O527" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="P527" s="4" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="Q527" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F528" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H528" s="2" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="I528" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" s="2" t="n">
+        <v>3598</v>
+      </c>
+      <c r="K528" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N528" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P528" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q528" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F529" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" s="2" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="I529" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" s="2" t="n">
+        <v>21420</v>
+      </c>
+      <c r="K529" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M529" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N529" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O529" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P529" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q529" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F530" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G530" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" s="2" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="I530" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" s="2" t="n">
+        <v>36924</v>
+      </c>
+      <c r="K530" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N530" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O530" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P530" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q530" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F531" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H531" s="2" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="I531" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" s="2" t="n">
+        <v>7777</v>
+      </c>
+      <c r="K531" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L531" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M531" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N531" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O531" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P531" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q531" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F532" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H532" s="2" t="n">
+        <v>218.81</v>
+      </c>
+      <c r="I532" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" s="2" t="n">
+        <v>43762</v>
+      </c>
+      <c r="K532" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L532" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M532" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N532" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P532" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q532" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q532"/>
+  <dimension ref="A1:Q540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32467,10 +32467,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C525" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C525" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
@@ -32530,10 +32528,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C526" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C526" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
@@ -32593,10 +32589,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C527" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C527" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
@@ -32656,10 +32650,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C528" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C528" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
@@ -32719,10 +32711,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C529" s="2" t="inlineStr">
-        <is>
-          <t>300548</t>
-        </is>
+      <c r="C529" s="2" t="n">
+        <v>300548</v>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
@@ -32782,10 +32772,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C530" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C530" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
@@ -32845,10 +32833,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C531" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C531" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
@@ -32908,10 +32894,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C532" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C532" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
@@ -32955,6 +32939,510 @@
         <v>-5</v>
       </c>
       <c r="Q532" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F533" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G533" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H533" s="2" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="I533" s="2" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="J533" s="2" t="n">
+        <v>6740</v>
+      </c>
+      <c r="K533" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="L533" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="M533" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N533" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O533" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P533" s="3" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="Q533" s="2" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F534" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G534" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H534" s="2" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="I534" s="2" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="J534" s="2" t="n">
+        <v>11816</v>
+      </c>
+      <c r="K534" s="2" t="n">
+        <v>12218</v>
+      </c>
+      <c r="L534" s="3" t="n">
+        <v>402</v>
+      </c>
+      <c r="M534" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N534" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="O534" s="2" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="P534" s="3" t="n">
+        <v>385.89</v>
+      </c>
+      <c r="Q534" s="2" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F535" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G535" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H535" s="2" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="I535" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" s="2" t="n">
+        <v>8410</v>
+      </c>
+      <c r="K535" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L535" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M535" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N535" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P535" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q535" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F536" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G536" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H536" s="2" t="n">
+        <v>203.81</v>
+      </c>
+      <c r="I536" s="2" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="J536" s="2" t="n">
+        <v>122286</v>
+      </c>
+      <c r="K536" s="2" t="n">
+        <v>122388</v>
+      </c>
+      <c r="L536" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="M536" s="2" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="N536" s="2" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="O536" s="2" t="n">
+        <v>85.66</v>
+      </c>
+      <c r="P536" s="3" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="Q536" s="2" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F537" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" s="2" t="n">
+        <v>203.81</v>
+      </c>
+      <c r="I537" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" s="2" t="n">
+        <v>40762</v>
+      </c>
+      <c r="K537" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N537" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P537" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q537" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F538" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G538" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H538" s="2" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="I538" s="2" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="J538" s="2" t="n">
+        <v>10780</v>
+      </c>
+      <c r="K538" s="2" t="n">
+        <v>11190</v>
+      </c>
+      <c r="L538" s="3" t="n">
+        <v>410</v>
+      </c>
+      <c r="M538" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N538" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O538" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P538" s="3" t="n">
+        <v>394.4</v>
+      </c>
+      <c r="Q538" s="2" t="inlineStr">
+        <is>
+          <t>3.66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F539" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G539" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H539" s="2" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="I539" s="2" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="J539" s="2" t="n">
+        <v>7008</v>
+      </c>
+      <c r="K539" s="2" t="n">
+        <v>7116</v>
+      </c>
+      <c r="L539" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="M539" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N539" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="O539" s="2" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="P539" s="3" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="Q539" s="2" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F540" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G540" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H540" s="2" t="n">
+        <v>89.8933</v>
+      </c>
+      <c r="I540" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" s="2" t="n">
+        <v>26968</v>
+      </c>
+      <c r="K540" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L540" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M540" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N540" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P540" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q540" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q540"/>
+  <dimension ref="A1:Q549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32955,10 +32955,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C533" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C533" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
@@ -33018,10 +33016,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C534" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C534" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
@@ -33081,10 +33077,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C535" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C535" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
@@ -33144,10 +33138,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C536" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C536" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
@@ -33207,10 +33199,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C537" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C537" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
@@ -33270,10 +33260,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C538" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C538" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
@@ -33333,10 +33321,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C539" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C539" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
@@ -33396,10 +33382,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C540" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C540" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
@@ -33445,6 +33429,573 @@
       <c r="Q540" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F541" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G541" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" s="2" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="I541" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" s="2" t="n">
+        <v>4087</v>
+      </c>
+      <c r="K541" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M541" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N541" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P541" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q541" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F542" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H542" s="2" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="I542" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" s="2" t="n">
+        <v>12024</v>
+      </c>
+      <c r="K542" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L542" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M542" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N542" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P542" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q542" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F543" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H543" s="2" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="I543" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" s="2" t="n">
+        <v>10970</v>
+      </c>
+      <c r="K543" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L543" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M543" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N543" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P543" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q543" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F544" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H544" s="2" t="n">
+        <v>251.84</v>
+      </c>
+      <c r="I544" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" s="2" t="n">
+        <v>50368</v>
+      </c>
+      <c r="K544" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L544" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M544" s="2" t="n">
+        <v>5.0368</v>
+      </c>
+      <c r="N544" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="P544" s="4" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="Q544" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F545" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H545" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="I545" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J545" s="2" t="n">
+        <v>4098</v>
+      </c>
+      <c r="K545" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L545" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M545" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N545" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O545" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P545" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q545" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F546" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G546" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H546" s="2" t="n">
+        <v>200.47</v>
+      </c>
+      <c r="I546" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J546" s="2" t="n">
+        <v>40094</v>
+      </c>
+      <c r="K546" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L546" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M546" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N546" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O546" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P546" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q546" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F547" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H547" s="2" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="I547" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J547" s="2" t="n">
+        <v>6624</v>
+      </c>
+      <c r="K547" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L547" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M547" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N547" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O547" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P547" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q547" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F548" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" s="2" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="I548" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" s="2" t="n">
+        <v>4834</v>
+      </c>
+      <c r="K548" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L548" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M548" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N548" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P548" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q548" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F549" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G549" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" s="2" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J549" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K549" s="2" t="n">
+        <v>8950</v>
+      </c>
+      <c r="L549" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M549" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N549" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="O549" s="2" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="P549" s="4" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="Q549" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q549"/>
+  <dimension ref="A1:Q554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33443,10 +33443,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C541" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C541" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
@@ -33506,10 +33504,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C542" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C542" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
@@ -33569,10 +33565,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C543" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C543" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
@@ -33632,10 +33626,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C544" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C544" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
@@ -33695,10 +33687,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C545" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C545" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
@@ -33758,10 +33748,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C546" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C546" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
@@ -33821,10 +33809,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C547" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C547" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
@@ -33884,10 +33870,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C548" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C548" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
@@ -33947,10 +33931,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C549" s="2" t="inlineStr">
-        <is>
-          <t>002594</t>
-        </is>
+      <c r="C549" s="2" t="n">
+        <v>2594</v>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
@@ -33996,6 +33978,321 @@
       <c r="Q549" s="2" t="inlineStr">
         <is>
           <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F550" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H550" s="2" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="I550" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" s="2" t="n">
+        <v>5843</v>
+      </c>
+      <c r="K550" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L550" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M550" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N550" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O550" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P550" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q550" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F551" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H551" s="2" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="I551" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" s="2" t="n">
+        <v>6031</v>
+      </c>
+      <c r="K551" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L551" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M551" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N551" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P551" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q551" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F552" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" s="2" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="I552" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J552" s="2" t="n">
+        <v>4842</v>
+      </c>
+      <c r="K552" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L552" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M552" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N552" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O552" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P552" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q552" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F553" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H553" s="2" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="I553" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" s="2" t="n">
+        <v>6628</v>
+      </c>
+      <c r="K553" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L553" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M553" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N553" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O553" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P553" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q553" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F554" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" s="2" t="n">
+        <v>194.2006</v>
+      </c>
+      <c r="I554" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J554" s="2" t="n">
+        <v>38840.12</v>
+      </c>
+      <c r="K554" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L554" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M554" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N554" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P554" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q554" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q554"/>
+  <dimension ref="A1:Q561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33992,10 +33992,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C550" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C550" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
@@ -34055,10 +34053,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C551" s="2" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
+      <c r="C551" s="2" t="n">
+        <v>2156</v>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
@@ -34118,10 +34114,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C552" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C552" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
@@ -34181,10 +34175,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C553" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C553" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
@@ -34244,10 +34236,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C554" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C554" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
@@ -34291,6 +34281,447 @@
         <v>-5</v>
       </c>
       <c r="Q554" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F555" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G555" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H555" s="2" t="n">
+        <v>66.61</v>
+      </c>
+      <c r="I555" s="2" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="J555" s="2" t="n">
+        <v>6661</v>
+      </c>
+      <c r="K555" s="2" t="n">
+        <v>6965</v>
+      </c>
+      <c r="L555" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="M555" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N555" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O555" s="2" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="P555" s="3" t="n">
+        <v>290.52</v>
+      </c>
+      <c r="Q555" s="2" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F556" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" s="2" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="I556" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" s="2" t="n">
+        <v>5723</v>
+      </c>
+      <c r="K556" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L556" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M556" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N556" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P556" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q556" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F557" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G557" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H557" s="2" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="I557" s="2" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="J557" s="2" t="n">
+        <v>3354</v>
+      </c>
+      <c r="K557" s="2" t="n">
+        <v>3479</v>
+      </c>
+      <c r="L557" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="M557" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N557" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O557" s="2" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="P557" s="3" t="n">
+        <v>113.26</v>
+      </c>
+      <c r="Q557" s="2" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F558" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H558" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="I558" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" s="2" t="n">
+        <v>3198</v>
+      </c>
+      <c r="K558" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L558" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M558" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N558" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O558" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P558" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q558" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F559" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G559" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H559" s="2" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="I559" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" s="2" t="n">
+        <v>2648</v>
+      </c>
+      <c r="K559" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M559" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N559" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P559" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q559" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F560" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G560" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" s="2" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="J560" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K560" s="2" t="n">
+        <v>23195</v>
+      </c>
+      <c r="L560" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M560" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N560" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O560" s="2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="P560" s="4" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="Q560" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F561" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G561" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H561" s="2" t="n">
+        <v>190.02</v>
+      </c>
+      <c r="I561" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J561" s="2" t="n">
+        <v>38004</v>
+      </c>
+      <c r="K561" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L561" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M561" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N561" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O561" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P561" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q561" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q561"/>
+  <dimension ref="A1:Q566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34297,10 +34297,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C555" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C555" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
@@ -34360,10 +34358,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C556" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C556" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
@@ -34423,10 +34419,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C557" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C557" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
@@ -34486,10 +34480,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C558" s="2" t="inlineStr">
-        <is>
-          <t>512760</t>
-        </is>
+      <c r="C558" s="2" t="n">
+        <v>512760</v>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
@@ -34549,10 +34541,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C559" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C559" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
@@ -34612,10 +34602,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C560" s="2" t="inlineStr">
-        <is>
-          <t>688778</t>
-        </is>
+      <c r="C560" s="2" t="n">
+        <v>688778</v>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
@@ -34675,10 +34663,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C561" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C561" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
@@ -34722,6 +34708,321 @@
         <v>-5</v>
       </c>
       <c r="Q561" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F562" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H562" s="2" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="I562" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J562" s="2" t="n">
+        <v>5623</v>
+      </c>
+      <c r="K562" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L562" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M562" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N562" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O562" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P562" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q562" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F563" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H563" s="2" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="I563" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" s="2" t="n">
+        <v>6853</v>
+      </c>
+      <c r="K563" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L563" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M563" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N563" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P563" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q563" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F564" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G564" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" s="2" t="n">
+        <v>64.27500000000001</v>
+      </c>
+      <c r="I564" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" s="2" t="n">
+        <v>12855</v>
+      </c>
+      <c r="K564" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M564" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N564" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O564" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P564" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q564" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F565" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G565" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H565" s="2" t="n">
+        <v>190.71</v>
+      </c>
+      <c r="I565" s="2" t="n">
+        <v>194.63</v>
+      </c>
+      <c r="J565" s="2" t="n">
+        <v>76284</v>
+      </c>
+      <c r="K565" s="2" t="n">
+        <v>77852</v>
+      </c>
+      <c r="L565" s="3" t="n">
+        <v>1568</v>
+      </c>
+      <c r="M565" s="2" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="N565" s="2" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="O565" s="2" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="P565" s="3" t="n">
+        <v>1513.66</v>
+      </c>
+      <c r="Q565" s="2" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F566" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" s="2" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="I566" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" s="2" t="n">
+        <v>6462</v>
+      </c>
+      <c r="K566" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N566" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P566" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q566" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q566"/>
+  <dimension ref="A1:Q572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34724,10 +34724,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C562" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C562" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
@@ -34787,10 +34785,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C563" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C563" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
@@ -34850,10 +34846,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C564" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C564" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
@@ -34913,10 +34907,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C565" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C565" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
@@ -34976,10 +34968,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C566" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C566" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
@@ -35025,6 +35015,384 @@
       <c r="Q566" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F567" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G567" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H567" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" s="2" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="J567" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K567" s="2" t="n">
+        <v>4955</v>
+      </c>
+      <c r="L567" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M567" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N567" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O567" s="2" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="P567" s="4" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="Q567" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F568" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G568" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H568" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I568" s="2" t="n">
+        <v>195.4167</v>
+      </c>
+      <c r="J568" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K568" s="2" t="n">
+        <v>117250</v>
+      </c>
+      <c r="L568" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M568" s="2" t="n">
+        <v>11.725</v>
+      </c>
+      <c r="N568" s="2" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="O568" s="2" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="P568" s="4" t="n">
+        <v>-70.34</v>
+      </c>
+      <c r="Q568" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F569" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G569" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H569" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I569" s="2" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="J569" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K569" s="2" t="n">
+        <v>7048</v>
+      </c>
+      <c r="L569" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M569" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N569" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O569" s="2" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="P569" s="4" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="Q569" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F570" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G570" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H570" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I570" s="2" t="n">
+        <v>66.59</v>
+      </c>
+      <c r="J570" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K570" s="2" t="n">
+        <v>6659</v>
+      </c>
+      <c r="L570" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M570" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N570" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O570" s="2" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="P570" s="4" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="Q570" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F571" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G571" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H571" s="2" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="I571" s="2" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="J571" s="2" t="n">
+        <v>12908</v>
+      </c>
+      <c r="K571" s="2" t="n">
+        <v>13068</v>
+      </c>
+      <c r="L571" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="M571" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N571" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O571" s="2" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="P571" s="3" t="n">
+        <v>143.47</v>
+      </c>
+      <c r="Q571" s="2" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F572" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G572" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H572" s="2" t="n">
+        <v>237.995</v>
+      </c>
+      <c r="I572" s="2" t="n">
+        <v>239.26</v>
+      </c>
+      <c r="J572" s="2" t="n">
+        <v>95198</v>
+      </c>
+      <c r="K572" s="2" t="n">
+        <v>95704</v>
+      </c>
+      <c r="L572" s="3" t="n">
+        <v>506</v>
+      </c>
+      <c r="M572" s="2" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="N572" s="2" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="O572" s="2" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="P572" s="3" t="n">
+        <v>439.06</v>
+      </c>
+      <c r="Q572" s="2" t="inlineStr">
+        <is>
+          <t>0.46%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q572"/>
+  <dimension ref="A1:Q582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35029,10 +35029,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C567" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C567" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
@@ -35092,10 +35090,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C568" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C568" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
@@ -35155,10 +35151,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C569" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C569" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
@@ -35218,10 +35212,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C570" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C570" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
@@ -35281,10 +35273,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C571" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C571" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
@@ -35344,10 +35334,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C572" s="2" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="C572" s="2" t="n">
+        <v>688041</v>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
@@ -35393,6 +35381,636 @@
       <c r="Q572" s="2" t="inlineStr">
         <is>
           <t>0.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F573" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G573" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H573" s="2" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="I573" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" s="2" t="n">
+        <v>4801</v>
+      </c>
+      <c r="K573" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L573" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M573" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N573" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O573" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P573" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q573" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F574" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H574" s="2" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="I574" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" s="2" t="n">
+        <v>13546</v>
+      </c>
+      <c r="K574" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L574" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M574" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N574" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O574" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P574" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q574" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F575" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G575" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H575" s="2" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="I575" s="2" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="J575" s="2" t="n">
+        <v>40010</v>
+      </c>
+      <c r="K575" s="2" t="n">
+        <v>40420</v>
+      </c>
+      <c r="L575" s="3" t="n">
+        <v>410</v>
+      </c>
+      <c r="M575" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N575" s="2" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="O575" s="2" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="P575" s="3" t="n">
+        <v>379.79</v>
+      </c>
+      <c r="Q575" s="2" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F576" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G576" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H576" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I576" s="2" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="J576" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K576" s="2" t="n">
+        <v>4042</v>
+      </c>
+      <c r="L576" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M576" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N576" s="2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O576" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="P576" s="4" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="Q576" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F577" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H577" s="2" t="n">
+        <v>63.355</v>
+      </c>
+      <c r="I577" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" s="2" t="n">
+        <v>12671</v>
+      </c>
+      <c r="K577" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L577" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M577" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N577" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O577" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P577" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q577" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F578" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H578" s="2" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="I578" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" s="2" t="n">
+        <v>6570</v>
+      </c>
+      <c r="K578" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L578" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M578" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N578" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O578" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P578" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q578" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F579" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="G579" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H579" s="2" t="n">
+        <v>196.518</v>
+      </c>
+      <c r="I579" s="2" t="n">
+        <v>197.93</v>
+      </c>
+      <c r="J579" s="2" t="n">
+        <v>157214.4</v>
+      </c>
+      <c r="K579" s="2" t="n">
+        <v>158344</v>
+      </c>
+      <c r="L579" s="3" t="n">
+        <v>1129.6</v>
+      </c>
+      <c r="M579" s="2" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="N579" s="2" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="O579" s="2" t="n">
+        <v>110.73</v>
+      </c>
+      <c r="P579" s="3" t="n">
+        <v>1018.87</v>
+      </c>
+      <c r="Q579" s="2" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H580" s="2" t="n">
+        <v>196.518</v>
+      </c>
+      <c r="I580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" s="2" t="n">
+        <v>39303.6</v>
+      </c>
+      <c r="K580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L580" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M580" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O580" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P580" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q580" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>中国稀土</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H581" s="2" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="I581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" s="2" t="n">
+        <v>5526</v>
+      </c>
+      <c r="K581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L581" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M581" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O581" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P581" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q581" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H582" s="2" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="I582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" s="2" t="n">
+        <v>6695</v>
+      </c>
+      <c r="K582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L582" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M582" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O582" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P582" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q582" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q582"/>
+  <dimension ref="A1:Q590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35395,10 +35395,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C573" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C573" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
@@ -35458,10 +35456,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C574" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C574" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
@@ -35521,10 +35517,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C575" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C575" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
@@ -35584,10 +35578,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C576" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C576" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
@@ -35647,10 +35639,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C577" s="2" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
+      <c r="C577" s="2" t="n">
+        <v>2837</v>
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
@@ -35710,10 +35700,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C578" s="2" t="inlineStr">
-        <is>
-          <t>561980</t>
-        </is>
+      <c r="C578" s="2" t="n">
+        <v>561980</v>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
@@ -35773,10 +35761,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C579" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C579" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
@@ -35836,10 +35822,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C580" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C580" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
@@ -35899,10 +35883,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C581" s="2" t="inlineStr">
-        <is>
-          <t>000831</t>
-        </is>
+      <c r="C581" s="2" t="n">
+        <v>831</v>
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
@@ -35962,10 +35944,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C582" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C582" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
@@ -36011,6 +35991,510 @@
       <c r="Q582" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F583" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G583" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H583" s="2" t="n">
+        <v>198.09</v>
+      </c>
+      <c r="I583" s="2" t="n">
+        <v>199.88</v>
+      </c>
+      <c r="J583" s="2" t="n">
+        <v>39618</v>
+      </c>
+      <c r="K583" s="2" t="n">
+        <v>39976</v>
+      </c>
+      <c r="L583" s="3" t="n">
+        <v>358</v>
+      </c>
+      <c r="M583" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N583" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="O583" s="2" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="P583" s="3" t="n">
+        <v>328.01</v>
+      </c>
+      <c r="Q583" s="2" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F584" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G584" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H584" s="2" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="I584" s="2" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="J584" s="2" t="n">
+        <v>6737</v>
+      </c>
+      <c r="K584" s="2" t="n">
+        <v>6856</v>
+      </c>
+      <c r="L584" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="M584" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="O584" s="2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="P584" s="3" t="n">
+        <v>105.57</v>
+      </c>
+      <c r="Q584" s="2" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F585" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G585" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H585" s="2" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="I585" s="2" t="n">
+        <v>69.09</v>
+      </c>
+      <c r="J585" s="2" t="n">
+        <v>13604</v>
+      </c>
+      <c r="K585" s="2" t="n">
+        <v>13818</v>
+      </c>
+      <c r="L585" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="M585" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N585" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="O585" s="2" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="P585" s="3" t="n">
+        <v>197.09</v>
+      </c>
+      <c r="Q585" s="2" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F586" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G586" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H586" s="2" t="n">
+        <v>109.12</v>
+      </c>
+      <c r="I586" s="2" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="J586" s="2" t="n">
+        <v>10912</v>
+      </c>
+      <c r="K586" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="L586" s="4" t="n">
+        <v>-31</v>
+      </c>
+      <c r="M586" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N586" s="2" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="O586" s="2" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="P586" s="4" t="n">
+        <v>-46.44</v>
+      </c>
+      <c r="Q586" s="2" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F587" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G587" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H587" s="2" t="n">
+        <v>189.82</v>
+      </c>
+      <c r="I587" s="2" t="n">
+        <v>196.27</v>
+      </c>
+      <c r="J587" s="2" t="n">
+        <v>18982</v>
+      </c>
+      <c r="K587" s="2" t="n">
+        <v>19627</v>
+      </c>
+      <c r="L587" s="3" t="n">
+        <v>645</v>
+      </c>
+      <c r="M587" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N587" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="O587" s="2" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="P587" s="3" t="n">
+        <v>625.1900000000001</v>
+      </c>
+      <c r="Q587" s="2" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F588" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G588" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H588" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="I588" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" s="2" t="n">
+        <v>8200</v>
+      </c>
+      <c r="K588" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L588" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M588" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N588" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O588" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P588" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q588" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F589" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G589" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H589" s="2" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="I589" s="2" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="J589" s="2" t="n">
+        <v>19925</v>
+      </c>
+      <c r="K589" s="2" t="n">
+        <v>20460</v>
+      </c>
+      <c r="L589" s="3" t="n">
+        <v>535</v>
+      </c>
+      <c r="M589" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N589" s="2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="O589" s="2" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="P589" s="3" t="n">
+        <v>514.77</v>
+      </c>
+      <c r="Q589" s="2" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>跨账户(两融账户+手机账户)</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F590" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G590" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H590" s="2" t="n">
+        <v>332.68</v>
+      </c>
+      <c r="I590" s="2" t="n">
+        <v>335.58</v>
+      </c>
+      <c r="J590" s="2" t="n">
+        <v>66536</v>
+      </c>
+      <c r="K590" s="2" t="n">
+        <v>67116</v>
+      </c>
+      <c r="L590" s="3" t="n">
+        <v>580</v>
+      </c>
+      <c r="M590" s="2" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="N590" s="2" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="O590" s="2" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="P590" s="3" t="n">
+        <v>533.0700000000001</v>
+      </c>
+      <c r="Q590" s="2" t="inlineStr">
+        <is>
+          <t>0.80%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q590"/>
+  <dimension ref="A1:Q593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36005,10 +36005,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C583" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C583" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
@@ -36068,10 +36066,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C584" s="2" t="inlineStr">
-        <is>
-          <t>002222</t>
-        </is>
+      <c r="C584" s="2" t="n">
+        <v>2222</v>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
@@ -36131,10 +36127,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C585" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C585" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
@@ -36194,10 +36188,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C586" s="2" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="C586" s="2" t="n">
+        <v>988</v>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
@@ -36257,10 +36249,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C587" s="2" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
+      <c r="C587" s="2" t="n">
+        <v>2384</v>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
@@ -36320,10 +36310,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C588" s="2" t="inlineStr">
-        <is>
-          <t>600498</t>
-        </is>
+      <c r="C588" s="2" t="n">
+        <v>600498</v>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
@@ -36383,10 +36371,8 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C589" s="2" t="inlineStr">
-        <is>
-          <t>002436</t>
-        </is>
+      <c r="C589" s="2" t="n">
+        <v>2436</v>
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
@@ -36446,10 +36432,8 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C590" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C590" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
@@ -36495,6 +36479,195 @@
       <c r="Q590" s="2" t="inlineStr">
         <is>
           <t>0.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F591" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G591" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H591" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I591" s="2" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J591" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K591" s="2" t="n">
+        <v>4927</v>
+      </c>
+      <c r="L591" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M591" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N591" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O591" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="P591" s="4" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="Q591" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F592" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G592" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H592" s="2" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="I592" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J592" s="2" t="n">
+        <v>13474</v>
+      </c>
+      <c r="K592" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L592" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M592" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N592" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O592" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P592" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q592" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F593" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G593" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H593" s="2" t="n">
+        <v>195.73</v>
+      </c>
+      <c r="I593" s="2" t="n">
+        <v>197.29</v>
+      </c>
+      <c r="J593" s="2" t="n">
+        <v>39146</v>
+      </c>
+      <c r="K593" s="2" t="n">
+        <v>39458</v>
+      </c>
+      <c r="L593" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="M593" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N593" s="2" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="O593" s="2" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="P593" s="3" t="n">
+        <v>282.27</v>
+      </c>
+      <c r="Q593" s="2" t="inlineStr">
+        <is>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
